--- a/runs/results/parsed/combined_batch_162305_205957_parsed_success.xlsx
+++ b/runs/results/parsed/combined_batch_162305_205957_parsed_success.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R237"/>
+  <dimension ref="A1:Q237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,20 +489,15 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>needs_summary</t>
+          <t>summary</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>summary</t>
+          <t>key_insight</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
-        <is>
-          <t>key_insight</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
         <is>
           <t>present_in_lit_review</t>
         </is>
@@ -573,20 +568,17 @@
       <c r="N2" t="b">
         <v>1</v>
       </c>
-      <c r="O2" t="b">
-        <v>1</v>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>The paper introduces a hybrid fuzzy regression model with asymmetric triangular fuzzy coefficients applied to loss reserving, showing improved predictive performance over classical GLMs on the Taylor and Ashe dataset.</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A hybrid fuzzy regression model with asymmetric triangular fuzzy coefficients and optimized h-value is applied to loss reserving using the Taylor and Ashe dataset, outperforming classical GLM in prediction error and standard deviation.</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>The hybrid fuzzy regression model improves reserve prediction accuracy and stability over classical GLM by incorporating fuzzy logic and optimized defuzzification within a generalized linear framework.</t>
-        </is>
-      </c>
-      <c r="R2" t="b">
+          <t>Optimizing the h-value in a fuzzy GLM framework reduces reserve prediction error and standard deviation compared to traditional GLMs, offering a practical, interpretable enhancement for actuarial reserving.</t>
+        </is>
+      </c>
+      <c r="Q2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -655,10 +647,17 @@
       <c r="N3" t="b">
         <v>0</v>
       </c>
-      <c r="O3" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" t="b">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>This paper focuses on optimizing light intensity for photodetector calibration in physics contexts, with no connection to actuarial claims reserving or insurance loss modeling.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>The research is entirely unrelated to general insurance reserving and offers no practical value to the IFoA Working Party's objectives.</t>
+        </is>
+      </c>
+      <c r="Q3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -727,16 +726,17 @@
       <c r="N4" t="b">
         <v>1</v>
       </c>
-      <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>The paper introduces a Bayesian hierarchical model with autoregressive latent variables to capture dependence within and across run-off triangles, offering a practical framework for improving reserve estimates by borrowing strength across lines of business.</t>
-        </is>
-      </c>
-      <c r="R4" t="b">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>This paper introduces a Bayesian hierarchical model that captures autoregressive dependence within and across run-off triangles, enabling improved reserve estimation by borrowing strength across lines of business.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Modeling autoregressive dependence via latent variables and hierarchical priors allows for more realistic and robust reserving by explicitly accounting for temporal and cross-triangle dependencies.</t>
+        </is>
+      </c>
+      <c r="Q4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -805,16 +805,17 @@
       <c r="N5" t="b">
         <v>1</v>
       </c>
-      <c r="O5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>The paper introduces a fuzzy least-squares estimation method for hybrid log-Poisson regression in loss reserving, offering a novel goodness-of-fit assessment that may improve reserve accuracy over classical methods.</t>
-        </is>
-      </c>
-      <c r="R5" t="b">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>The paper introduces a hybrid log-Poisson regression model estimated via fuzzy least squares, evaluated for goodness of fit in loss reserving using real data, offering a methodological extension to classical actuarial models.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fuzzy least-squares estimation applied to a hybrid log-Poisson model provides a statistically grounded alternative to traditional methods with potential for improved reserve accuracy and model diagnostics.</t>
+        </is>
+      </c>
+      <c r="Q5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -883,10 +884,17 @@
       <c r="N6" t="b">
         <v>0</v>
       </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" t="b">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>The paper extends ruin probability analysis in a Sparre Andersen model with investments to annuity payments and two-sided jumps, using semi-Markov processes.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>This theoretical extension of ruin probabilities under investment risk is not directly applicable to claims reserving or loss forecasting in general insurance.</t>
+        </is>
+      </c>
+      <c r="Q6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -950,20 +958,22 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
       </c>
-      <c r="O7" t="b">
-        <v>1</v>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>This paper focuses on detecting adversarial attacks in crowd counting using depth estimation, which is unrelated to actuarial claims reserving or loss prediction.</t>
+        </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>The exploresarial attack in crowd counting using depth estimation as a secondary task, showing improved detection over heuristic methods.</t>
-        </is>
-      </c>
-      <c r="R7" t="b">
+          <t>The method leverages multitask learning (crowd density and depth) to detect adversarial perturbations, but offers no practical value for insurance reserving.</t>
+        </is>
+      </c>
+      <c r="Q7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1027,15 +1037,22 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
-      <c r="O8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8" t="b">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>The paper adapts the concordance probability (C-index) for frequency-severity models in non-life insurance pricing, focusing on large datasets, but does not address claims reserving or reserve uncertainty.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>While methodologically sound for pricing applications, the paper lacks direct relevance to actuarial reserving practice or probabilistic reserve estimation.</t>
+        </is>
+      </c>
+      <c r="Q8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1104,15 +1121,17 @@
       <c r="N9" t="b">
         <v>0</v>
       </c>
-      <c r="O9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>The paper addresses new business pricing optimization under competitive market conditions, which is not directly relevant to claims or loss reserving.</t>
-        </is>
-      </c>
-      <c r="R9" t="b">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>This paper focuses on price optimization for new business in motor insurance, modeling customer acceptance under competitive market conditions, with no connection to claims reserving or loss development.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>The paper addresses pricing strategy for acquiring new customers, which is unrelated to the actuarial reserving tasks of estimating IBNR, RBNS, or claim development patterns.</t>
+        </is>
+      </c>
+      <c r="Q9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1181,15 +1200,17 @@
       <c r="N10" t="b">
         <v>0</v>
       </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>The method provides robust localization under bounded measurement errors without requiring statistical error distributions, but has no practical relevance to actuarial reserving.</t>
-        </is>
-      </c>
-      <c r="R10" t="b">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>This paper addresses robust geolocation using range measurements with bounded but unknown errors, focusing on optimization and distributed algorithms for sensor networks.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>The work provides a convex relaxation approach for localization under bounded measurement errors, but has no practical relevance to actuarial claims reserving or loss modelling.</t>
+        </is>
+      </c>
+      <c r="Q10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1258,15 +1279,17 @@
       <c r="N11" t="b">
         <v>0</v>
       </c>
-      <c r="O11" t="b">
-        <v>1</v>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>This paper focuses on robust state estimation for unstable nano aerial vehicles using control theory and genetic algorithms, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> paper introduces a robust estimator for unstable nano aerial vehicles using gap-reducing compensators and genetic algorithms, aimed at improving state under uncertainty in flight dynamics.</t>
-        </is>
-      </c>
-      <c r="R11" t="b">
+          <t>The GRMERS estimator improves flight stability for nano UAVs under uncertainty but offers no practical value or transferability to claims reserving or actuarial science.</t>
+        </is>
+      </c>
+      <c r="Q11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1335,20 +1358,17 @@
       <c r="N12" t="b">
         <v>0</v>
       </c>
-      <c r="O12" t="b">
-        <v>1</v>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>This paper focuses on Bayesian bandwidth selection for high-dimensional precision matrices, which is a statistical method with no direct application to claims reserving or loss development modeling.</t>
+        </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> paper introduces a Bayesian method for bandwidth in high-dimensional banded precision matrices, with theoretical guarantees and simulation results showing improved performance existing methods.</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>This work advances Bayesian bandwidth selection for precision matrices but lacks direct or transferable relevance to actuarial claims reserving or loss.</t>
-        </is>
-      </c>
-      <c r="R12" t="b">
+          <t>The paper advances Bayesian model selection for banded precision matrices but offers no practical value or transferability to actuarial reserving problems.</t>
+        </is>
+      </c>
+      <c r="Q12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1417,15 +1437,17 @@
       <c r="N13" t="b">
         <v>0</v>
       </c>
-      <c r="O13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Accounting for uncertainty in past data improves the calibration of future probabilistic forecasts in demographic modeling.</t>
-        </is>
-      </c>
-      <c r="R13" t="b">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>This paper extends Bayesian hierarchical models for fertility rate projections to account for uncertainty in historical data, improving prediction interval calibration for countries with unreliable vital statistics.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Incorporating uncertainty about past values into probabilistic projections improves forecast calibration, especially for data-poor settings.</t>
+        </is>
+      </c>
+      <c r="Q13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1494,15 +1516,17 @@
       <c r="N14" t="b">
         <v>0</v>
       </c>
-      <c r="O14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>By modeling real-world oscillator stability and measurement error dynamics, the paper achieves tighter local skew bounds than previously thought possible under traditional worst-case assumptions.</t>
-        </is>
-      </c>
-      <c r="R14" t="b">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>This paper addresses gradient clock synchronization in distributed systems, focusing on minimizing local clock skew under dynamic error conditions, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>The paper breaks established lower bounds on local clock skew by leveraging short-term stability of measurement and frequency errors, but offers no relevance to claims reserving or actuarial machine learning.</t>
+        </is>
+      </c>
+      <c r="Q14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1571,15 +1595,17 @@
       <c r="N15" t="b">
         <v>0</v>
       </c>
-      <c r="O15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>The paper introduces pulse-based control policies for uncertain monotone systems but has no practical relevance to actuarial claims reserving or loss modelling.</t>
-        </is>
-      </c>
-      <c r="R15" t="b">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>This paper focuses on pulse-based control for monotone systems under parametric uncertainty, primarily in biomedicine and synthetic biology contexts, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>The paper develops control policies for biological systems under uncertainty but offers no practical relevance to claims reserving, loss modeling, or actuarial machine learning applications.</t>
+        </is>
+      </c>
+      <c r="Q15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1648,20 +1674,17 @@
       <c r="N16" t="b">
         <v>0</v>
       </c>
-      <c r="O16" t="b">
-        <v>1</v>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>The paper introduces a neural network training method to minimize worst-case violations, tested on power systems, with no direct application to claims reserving or actuarial contexts.</t>
+        </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>The paper introduces neural network training method to minimize worst violations, tested on power system optimization problems, with no direct application to actuarial res.</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>This work focuses on safety-critical engineering systems and offers no practical relevance or transferability to claims reserving or actuarial modeling.</t>
-        </is>
-      </c>
-      <c r="R16" t="b">
+          <t>This is the first method to train neural networks to simultaneously optimize average performance and minimize worst-case constraint violations, but it lacks relevance to insurance reserving problems.</t>
+        </is>
+      </c>
+      <c r="Q16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1730,15 +1753,17 @@
       <c r="N17" t="b">
         <v>0</v>
       </c>
-      <c r="O17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>This work focuses on control theory for multi-agent systems under logical constraints and has no practical relevance to actuarial claims reserving or loss modelling.</t>
-        </is>
-      </c>
-      <c r="R17" t="b">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>This paper focuses on decentralized control of multi-agent systems under temporal logic constraints, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>The work is entirely unrelated to claims reserving, loss development, or any actuarial application, making it irrelevant to the IFoA working party's goals.</t>
+        </is>
+      </c>
+      <c r="Q17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1802,15 +1827,22 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
       </c>
-      <c r="O18" t="b">
-        <v>0</v>
-      </c>
-      <c r="R18" t="b">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>This paper focuses on parameter estimation in Ising models from statistical physics, with no connection to claims reserving, loss triangles, or actuarial forecasting.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>The paper provides theoretical consistency bounds for pseudolikelihood estimation in Ising models but offers no practical value for actuarial reserving research or practice.</t>
+        </is>
+      </c>
+      <c r="Q18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1879,20 +1911,17 @@
       <c r="N19" t="b">
         <v>0</v>
       </c>
-      <c r="O19" t="b">
-        <v>1</v>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>This paper introduces a quantum computing construct for while loops using weak measurements, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> paper introduces a quantum primitive for while loops using weak measurements to balance information gain and state perturbation, demonstrating its use in Grover’s search with preserved quadratic speed-up.</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Weakly measured while loops in quantum computing enable controlled trade-offs between measurement disturbance and iteration information without sacrificing algorithmic efficiency.</t>
-        </is>
-      </c>
-      <c r="R19" t="b">
+          <t>The paper advances quantum algorithm design but offers no practical relevance to claims reserving, loss modeling, or actuarial machine learning applications.</t>
+        </is>
+      </c>
+      <c r="Q19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1961,20 +1990,17 @@
       <c r="N20" t="b">
         <v>0</v>
       </c>
-      <c r="O20" t="b">
-        <v>1</v>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>This paper focuses on real-time GPU task scheduling with preemptive priority mechanisms, targeting embedded systems and real-time computing, not actuarial reserving or insurance applications.</t>
+        </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">The paper preemptive-based GPU scheduling for real tasks, improving schedulability by up to 40% on embedded platforms without major code  </t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>This work advances real-time GPU task scheduling but has no practical relevance to actuarial claims reserving or machine learning applications in insurance.</t>
-        </is>
-      </c>
-      <c r="R20" t="b">
+          <t>The paper advances real-time GPU scheduling for embedded platforms but has no practical relevance to claims reserving, loss modelling, or actuarial machine learning.</t>
+        </is>
+      </c>
+      <c r="Q20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2043,15 +2069,17 @@
       <c r="N21" t="b">
         <v>0</v>
       </c>
-      <c r="O21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Classical simulations can meaningfully approximate quantum spin dynamics in certain nonintegrable systems, even when quantum effects are expected to dominate.</t>
-        </is>
-      </c>
-      <c r="R21" t="b">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>This paper compares quantum and classical spin dynamics in lattice models, with no connection to actuarial reserving, claims development, or insurance loss prediction.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Classical simulations can meaningfully approximate quantum spin dynamics even for small quantum numbers, but this has no practical relevance to actuarial reserving or machine learning in insurance.</t>
+        </is>
+      </c>
+      <c r="Q21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2120,20 +2148,17 @@
       <c r="N22" t="b">
         <v>1</v>
       </c>
-      <c r="O22" t="b">
-        <v>1</v>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>This paper introduces a multinomial logistic regression model that leverages coverage activation patterns to predict individual claim reserves, offering granular insights into reserve dynamics across multiple coverages using real auto insurance data.</t>
+        </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>The paper introduces a multinomial logistic regression model that leverages coverage activation patterns to predict individual claim reserves, demonstrating accuracy on real auto insurance data and offering granular reserve insights per coverage.</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Modeling the activation of multiple insurance coverages over time using multinomial logistic regression enables more accurate and granular individual claim reserving, particularly valuable for portfolios with multivariate claim structures.</t>
-        </is>
-      </c>
-      <c r="R22" t="b">
+          <t>Modeling the activation and evolution of multiple insurance coverages per claim improves reserve accuracy and provides actionable, coverage-level reserve breakdowns for better portfolio management.</t>
+        </is>
+      </c>
+      <c r="Q22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2202,15 +2227,17 @@
       <c r="N23" t="b">
         <v>0</v>
       </c>
-      <c r="O23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>The paper introduces a stochastic framework for estimating rate change in general insurance portfolios using matched sampling and genetic algorithms, applied to motor premium data.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>Rate change should be treated as a statistical parameter estimated from an asymptotic population, not just measured deterministically from observed policies.</t>
         </is>
       </c>
-      <c r="R23" t="b">
+      <c r="Q23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2274,25 +2301,22 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
       </c>
-      <c r="O24" t="b">
-        <v>1</v>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>This paper focuses on validating electronic health records for biomedical research, using multi-wave sampling to correct for data quality issues in maternal-child outcome studies.</t>
+        </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>The paper develops a multi validation sampling method to correct for errors in electronic health records when estimating associations weight gain and childhood outcomes, using calibrated sampling weights and iterative influence function estimation.</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Efficient multi-wave validation sampling can correct bias in EHR-based regression estimates when full data validation is infeasible.</t>
-        </is>
-      </c>
-      <c r="R24" t="b">
+          <t>While the validation methodology is statistically sophisticated, it has minimal direct or transferable relevance to general insurance claims reserving or loss development modeling.</t>
+        </is>
+      </c>
+      <c r="Q24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2361,15 +2385,17 @@
       <c r="N25" t="b">
         <v>0</v>
       </c>
-      <c r="O25" t="b">
-        <v>1</v>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>The paper focuses on geographic ratemaking using spatial embeddings to improve pricing in areas with sparse loss data, but does not address claims reserving, IBNR/RBNS, or development triangle modelling.</t>
+        </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>The spatial embeddings construct geographic ratemaking models, enabling predictions in areas without historical loss data by leveraging complex feature representations fed into simpler models like GLMs.</t>
-        </is>
-      </c>
-      <c r="R25" t="b">
+          <t>Spatial embeddings can enhance ratemaking in data-sparse regions, but the method lacks direct applicability to actuarial reserving tasks.</t>
+        </is>
+      </c>
+      <c r="Q25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2438,15 +2464,17 @@
       <c r="N26" t="b">
         <v>0</v>
       </c>
-      <c r="O26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Quantum measurement bounds for phase gradients reveal a precision-resolution trade-off, with entangled states offering limited gains that vanish under practical optical constraints.</t>
-        </is>
-      </c>
-      <c r="R26" t="b">
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>This paper explores quantum metrology limits for optical phase gradient estimation, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>The quantum Cramér-Rao bound for phase gradient estimation is fundamentally constrained by quantum mechanics and offers no practical relevance to claims reserving or actuarial science.</t>
+        </is>
+      </c>
+      <c r="Q26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2515,15 +2543,17 @@
       <c r="N27" t="b">
         <v>0</v>
       </c>
-      <c r="O27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>The paper focuses on embedded systems optimization for hardware peripherals and has no relevance to actuarial claims reserving machine learning applications in insurance.</t>
-        </is>
-      </c>
-      <c r="R27" t="b">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>This paper focuses on optimizing energy and latency in embedded peripheral devices, with no connection to actuarial claims reserving or insurance loss modeling.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>PACER improves real-time detection of peripheral device completion to reduce energy use and latency, but offers no relevance to general insurance reserving or machine learning applications in actuarial science.</t>
+        </is>
+      </c>
+      <c r="Q27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2592,20 +2622,17 @@
       <c r="N28" t="b">
         <v>0</v>
       </c>
-      <c r="O28" t="b">
-        <v>1</v>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>This paper explores KPZ scaling and soliton behavior in Josephson junction arrays, a topic in condensed matter physics with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>The exploresZ and soliton proliferation in Josephson junction arrays using numerical simulations and analytical arguments, focusing on nonequ physics in a two-chain geometry.</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>This paper contributes to theoretical condensed matter physics and has no practical relevance to actuar claims reserving machine learning in insurance.</t>
-        </is>
-      </c>
-      <c r="R28" t="b">
+          <t>The research is entirely unrelated to claims reserving, loss modeling, or any practical actuarial application.</t>
+        </is>
+      </c>
+      <c r="Q28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2674,15 +2701,17 @@
       <c r="N29" t="b">
         <v>0</v>
       </c>
-      <c r="O29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Personalized privacy accounting via a Rényi filter can improve the privacy-utility tradeoff by actual individual privacy loss rather than worst-case bounds.</t>
-        </is>
-      </c>
-      <c r="R29" t="b">
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>The paper introduces a method for tighter privacy loss accounting in sequential data analyses using Rényi differential privacy, focusing on individual-level privacy budgets.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Personalized privacy accounting via a Rényi filter can tighten privacy-utility tradeoffs but has no direct application to claims reserving or actuarial practice.</t>
+        </is>
+      </c>
+      <c r="Q29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2751,20 +2780,17 @@
       <c r="N30" t="b">
         <v>0</v>
       </c>
-      <c r="O30" t="b">
-        <v>1</v>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>This paper investigates how GPU-level floating-point non-associativity and parallel scheduling can cause misclassification in deep learning models without adversarial input, focusing on computational reliability rather than actuarial reserving.</t>
+        </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>The paper investigates how GPU computation and floating non-ativity can cause misclassification in deep learning models without adversarial input, proposing methods to expose and mitigate vulnerability.</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>GPU-level computational non-determinism can induce model misclassification without input perturbation, a hidden vulnerability in learning systems.</t>
-        </is>
-      </c>
-      <c r="R30" t="b">
+          <t>Machine-level GPU behavior can unintentionally alter model outputs, revealing a hidden vulnerability in deep learning systems that is irrelevant to claims reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2828,20 +2854,22 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
       </c>
-      <c r="O31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>The paper provides a theoretical pricing-hedging framework for non-life liabilities but lacks direct applicability to actuarial reserving or empirical validation.</t>
-        </is>
-      </c>
-      <c r="R31" t="b">
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>The paper presents a continuous-time reduced-form framework for modeling non-life insurance liabilities, focusing on pricing and hedging under inflation and hybrid markets, but does not address claims reserving, development triangles, or practical actuarial estimation methods.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>While mathematically rigorous, the framework prioritizes financial pricing and hedging over claims reserving practice, limiting its direct usefulness to the IFoA working party.</t>
+        </is>
+      </c>
+      <c r="Q31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2905,20 +2933,22 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
       </c>
-      <c r="O32" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>While the model is interpretable and powerful, it targets pricing—not reserving—limiting its direct relevance to claims reserve estimation or development modeling.</t>
-        </is>
-      </c>
-      <c r="R32" t="b">
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>The paper presents an interpretable neural network model for insurance pricing, emphasizing transparency and predictive accuracy, but does not address claims reserving or loss development.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>While the Actuarial Neural Additive Model offers strong interpretability and performance in pricing, it lacks direct applicability to reserving tasks such as IBNR estimation or claim triangle modeling.</t>
+        </is>
+      </c>
+      <c r="Q32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2987,15 +3017,17 @@
       <c r="N33" t="b">
         <v>0</v>
       </c>
-      <c r="O33" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>While innovative in applying transformers to actuarial pricing, the paper lacks direct relevance to reserving, uncertainty quantification, or development triangle modelling.</t>
-        </is>
-      </c>
-      <c r="R33" t="b">
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>The paper explores using transformer models to enhance non-life insurance pricing, building on GLM-based neural architectures and benchmarking against traditional models.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>While technically innovative, the focus on pricing rather than reserving limits its direct practical value for claims reserve estimation or uncertainty quantification.</t>
+        </is>
+      </c>
+      <c r="Q33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3064,15 +3096,17 @@
       <c r="N34" t="b">
         <v>0</v>
       </c>
-      <c r="O34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>This research advances quantum circuit efficiency but has no practical relevance to actuarial claims reserving or machine learning applications in insurance.</t>
-        </is>
-      </c>
-      <c r="R34" t="b">
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>This paper focuses on optimizing multi-controlled quantum gates in linear nearest-neighbor architectures, with no connection to actuarial reserving or insurance applications.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>The research advances quantum circuit efficiency but offers no practical value for claims reserving or general insurance actuarial practice.</t>
+        </is>
+      </c>
+      <c r="Q34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3141,20 +3175,17 @@
       <c r="N35" t="b">
         <v>0</v>
       </c>
-      <c r="O35" t="b">
-        <v>1</v>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>The paper models IBNR claims using infinite server queues with semi-Markovian inputs, deriving moment-based asymptotics and transient expressions under specific assumptions.</t>
+        </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>The paper models IBNR claims a multidimensional infinite server queue with semi-Markov inputs, moment equations and asymptotic results for claim reporting dynamics under renewal and exponential assumptions.</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>This theoretical queueing model provides a stochastic framework for IBNR claim evolution but lacks direct practical implementation or validation against real reserving data.</t>
-        </is>
-      </c>
-      <c r="R35" t="b">
+          <t>This theoretical framework offers a stochastic foundation for modeling IBNR dynamics with state-dependent arrival and reporting delays, which could inform micro-level reserving if extended to practical calibration and prediction.</t>
+        </is>
+      </c>
+      <c r="Q35" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3223,15 +3254,17 @@
       <c r="N36" t="b">
         <v>0</v>
       </c>
-      <c r="O36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>maidrr enables transparency in complex insurance models by approximating them with interpretable GLMs while preserving predictive performance.</t>
-        </is>
-      </c>
-      <c r="R36" t="b">
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>The paper introduces a model-agnostic interpretable surrogate (maidrr) that extracts knowledge from black-box models to build transparent GLMs, demonstrated on claim frequency modeling but not directly on reserving or reserve uncertainty.</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>maidrr enables transparency in complex models by constructing accurate, interpretable GLMs via partial dependence-based feature engineering, though its direct application to claims reserving remains unexplored.</t>
+        </is>
+      </c>
+      <c r="Q36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3300,15 +3333,17 @@
       <c r="N37" t="b">
         <v>0</v>
       </c>
-      <c r="O37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Optimally allocating LLM evaluation queries based on estimated score variance reduces worst estimation error fixed computational budgets.</t>
-        </is>
-      </c>
-      <c r="R37" t="b">
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>The paper proposes a budget-efficient method for evaluating LLMs by adaptively allocating queries based on score variance, with applications in AI safety and model alignment.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Adaptive query allocation using multi-armed bandit theory reduces worst-case estimation error in LLM evaluation under fixed computational budgets.</t>
+        </is>
+      </c>
+      <c r="Q37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3377,20 +3412,17 @@
       <c r="N38" t="b">
         <v>0</v>
       </c>
-      <c r="O38" t="b">
-        <v>1</v>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>This paper details the optical design of PICO, a space mission concept for studying cosmic inflation and the early universe via high-sensitivity CMB observations.</t>
+        </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PICO a proposed NASA space mission designed to study cosmic inflation and the early universe by mapping the cosmic microwave background with unprecedented sensitivity an innovative optical design and advanced detector technology.</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>This paper describes a space-based astrophysics mission with no relevance to actuarial claims reserving or machine learning applications in insurance.</t>
-        </is>
-      </c>
-      <c r="R38" t="b">
+          <t>The paper has no relevance to actuarial claims reserving or machine learning applications in insurance.</t>
+        </is>
+      </c>
+      <c r="Q38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3459,20 +3491,17 @@
       <c r="N39" t="b">
         <v>0</v>
       </c>
-      <c r="O39" t="b">
-        <v>1</v>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>The paper addresses asset-liability management with stochastic dominance constraints, using multistage stochastic programming for P&amp;C insurers, but does not focus on claims reserving or loss development modeling.</t>
+        </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>The paper addresses asset-liability management financial intermediaries using programming and sequential stochastic dominance constraints, validated on a P&amp;C case not focused claims reserving or loss development.</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>While applied to P&amp;C, the paper focuses on portfolio optimization under risk constraints rather than improving claims res methods or reserve uncertainty estimation.</t>
-        </is>
-      </c>
-      <c r="R39" t="b">
+          <t>While the paper applies stochastic optimization to P&amp;C insurance ALM, it lacks direct relevance to actuarial reserving methods, micro-level claim modeling, or reserve uncertainty quantification.</t>
+        </is>
+      </c>
+      <c r="Q39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3502,7 +3531,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Multi-Agent Inverse Reinforcement Learning for Identifying Pareto-Efficient Coordination -- A Distributionally Robust Approach</t>
+          <t>Multi-Agent Inverse Reinforcement Learning for Identifying Pareto-Efficient Coordination - A Distributionally Robust Approach</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3541,10 +3570,17 @@
       <c r="N40" t="b">
         <v>0</v>
       </c>
-      <c r="O40" t="b">
-        <v>0</v>
-      </c>
-      <c r="R40" t="b">
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>This paper focuses on multi-agent inverse reinforcement learning to detect Pareto-efficient coordination in UAV systems, with no connection to claims reserving or actuarial practice.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>The work is methodologically sophisticated but entirely unrelated to insurance reserving, making it of negligible practical value to the IFoA working party.</t>
+        </is>
+      </c>
+      <c r="Q40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3613,20 +3649,17 @@
       <c r="N41" t="b">
         <v>1</v>
       </c>
-      <c r="O41" t="b">
-        <v>1</v>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>This paper introduces a Bayesian nowcasting model for IBNR data breach incidents, with empirical and synthetic validation showing improved reserve estimation for actuarial use.</t>
+        </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>A Bayesian nowcasting model is proposed to predict IBNR data breach incidents, integrating time and heterogeneous effects, with validation via synthetic and empirical studies showing improved reserve estimation for actuarial use.</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>The paper introduces a Bayesian nowcasting framework that effectively models IBNR delays in data breaches, offering practical value for reserving by improving predictive accuracy and reserve estimation in a niche but growing P&amp;C line.</t>
-        </is>
-      </c>
-      <c r="R41" t="b">
+          <t>The Bayesian nowcasting framework effectively models reporting delays in IBNR incidents, offering a transferable method for actuarial reserving in non-traditional lines like cyber risk.</t>
+        </is>
+      </c>
+      <c r="Q41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3695,15 +3728,17 @@
       <c r="N42" t="b">
         <v>0</v>
       </c>
-      <c r="O42" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>This theoretical game theory work on multi-dimensional payoffs has no clear or direct application to actuarial claims reserving or loss estimation.</t>
-        </is>
-      </c>
-      <c r="R42" t="b">
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>The paper introduces a theoretical framework for zero-sum matrix games with multi-dimensional payoffs, focusing on set-based optimization and equilibrium concepts.</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>This work offers no practical connection to claims reserving, IBNR/RBNS estimation, or actuarial forecasting, making it largely irrelevant to the working party's goals.</t>
+        </is>
+      </c>
+      <c r="Q42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3772,20 +3807,17 @@
       <c r="N43" t="b">
         <v>0</v>
       </c>
-      <c r="O43" t="b">
-        <v>1</v>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>The paper introduces bivariate gamma mixture of experts models to capture dependence between insurance claim categories, improving prediction by clustering policyholders and modeling covariate-dependent correlations.</t>
+        </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>The paper bivariate gamma mixture of experts models to capture between insurance claim categories, using covariates in both gating and expert networks to improve claim prediction through model-based clustering.</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Modeling inter-category claim dependence via bivariate gamma mixtures with covariate-driven clustering improves prediction accuracy, even when overall dataset dependence is weak.</t>
-        </is>
-      </c>
-      <c r="R43" t="b">
+          <t>Modeling inter-category claim dependencies via covariate-driven clustering in a bivariate gamma framework can enhance predictive accuracy, though its direct applicability to reserving rather than ratemaking is limited.</t>
+        </is>
+      </c>
+      <c r="Q43" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3854,20 +3886,17 @@
       <c r="N44" t="b">
         <v>0</v>
       </c>
-      <c r="O44" t="b">
-        <v>1</v>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>The paper focuses on probabilistic robust control design using Gaussian processes for dynamical systems, with no direct application to claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>The proposes a probabilistic robust for linearized Gaussian process dynamics, using posterior uncertainty to improve trade-offs between performance and stability, outperforming worst-case and certainty-equivalence methods.</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>This work advances learning-based control with probabilistic robustness guarantees but has no direct or transferable application to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R44" t="b">
+          <t>While the paper advances Bayesian control theory with probabilistic robustness guarantees, it lacks any connection to insurance reserving, claim development, or actuarial modeling.</t>
+        </is>
+      </c>
+      <c r="Q44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3936,20 +3965,17 @@
       <c r="N45" t="b">
         <v>0</v>
       </c>
-      <c r="O45" t="b">
-        <v>1</v>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>The paper addresses suboptimal function estimation under bounded noise using basis functions and worst-case optimization, with an online iterative implementation, but does not connect to claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Theopt estimation from using functions and worst-case optimization, with an online iterative method that converges to the true optimizer under mild assumptions.</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>The method provides a safe, convergent approach to suboptimization under bounded noise but lacks direct application to claims res or actuarial loss modeling.</t>
-        </is>
-      </c>
-      <c r="R45" t="b">
+          <t>The method provides safe, convergent suboptimization under noisy data but lacks any application or transferability to insurance reserving problems.</t>
+        </is>
+      </c>
+      <c r="Q45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4018,20 +4044,17 @@
       <c r="N46" t="b">
         <v>0</v>
       </c>
-      <c r="O46" t="b">
-        <v>1</v>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>The paper introduces a variable screening method for estimating covariate-dependent extreme value indices, with applications in extreme value analysis but no direct link to claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>The paper introduces a variable screening method for estimating the extreme value index in the presence of covariates, using a conditional Pickands estimator a single-index model validated via simulations and real data.</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>This work advances covariate selection for extreme value index estimation but lacks direct connection claims res or actuar loss modeling.</t>
-        </is>
-      </c>
-      <c r="R46" t="b">
+          <t>While methodologically sound for extreme value theory, the paper lacks practical relevance to general insurance reserving, IBNR/RBNS estimation, or probabilistic reserve forecasting.</t>
+        </is>
+      </c>
+      <c r="Q46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4100,20 +4123,17 @@
       <c r="N47" t="b">
         <v>0</v>
       </c>
-      <c r="O47" t="b">
-        <v>1</v>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>This paper addresses theoretical stability properties of monotone cellular automata with intrinsic randomness, using Peierls bounds and random contours, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>This paper extends Toom stability results for monotone cellularata to with intrinsic randomness, using random contours to estimate Peierls sums, and identifies limitations where the method fails despite expected stability.</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>The paper develops a contour-based method to analyze stability in stochastic cellular automata but reveals its limitations in certain perturbation regimes.</t>
-        </is>
-      </c>
-      <c r="R47" t="b">
+          <t>The paper advances theoretical understanding of stability in stochastic cellular automata but offers no practical relevance to claims reserving, loss modeling, or actuarial machine learning applications.</t>
+        </is>
+      </c>
+      <c r="Q47" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4182,20 +4202,17 @@
       <c r="N48" t="b">
         <v>0</v>
       </c>
-      <c r="O48" t="b">
-        <v>1</v>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>This paper focuses on energy-efficient real-time scheduling in multiprocessor systems using feedback control, with no connection to actuarial claims reserving or insurance loss modelling.</t>
+        </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>The a feedback-based real-time scheduling for multiprocessor systems to minimize energy consumption under uncertain task execution times, using linear programming and McNaughton’s wrap-around algorithm.</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Feedback scheduling can reduce energy consumption by up to 40% in real-time multiprocessor systems by adapting to task execution uncertainties.</t>
-        </is>
-      </c>
-      <c r="R48" t="b">
+          <t>The paper's feedback-based scheduling framework for minimizing energy consumption in computing systems has no practical relevance to general insurance reserving or actuarial methodology.</t>
+        </is>
+      </c>
+      <c r="Q48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4264,15 +4281,17 @@
       <c r="N49" t="b">
         <v>0</v>
       </c>
-      <c r="O49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Copula averaging offers a unified way to estimate tail dependence across multiple models, which may help better quantify extreme losses across business lines.</t>
-        </is>
-      </c>
-      <c r="R49" t="b">
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>The paper explores copula-based methods for estimating tail dependence in insurance claims, using Bayesian model averaging to unify estimates across multiple copula models, tested on simulated and real loss data.</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bayesian model averaging over copulas provides a robust way to estimate tail dependence for extreme losses, which may inform reserve uncertainty in multi-line catastrophe scenarios.</t>
+        </is>
+      </c>
+      <c r="Q49" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4341,20 +4360,17 @@
       <c r="N50" t="b">
         <v>0</v>
       </c>
-      <c r="O50" t="b">
-        <v>1</v>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>This paper models COVID-19 disease progression and vaccination impact using compartmental epidemiological methods, with no connection to claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>The compartment to assess impact of on COVID-19 progression in the Philippines, estimating herd immunity timelines vaccination rates and warning potential second peaks with increased transmission.</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Vaccination rate and transmission dynamics critically determine the timing of herd immunity and risk of secondary infection waves in the modeled population.</t>
-        </is>
-      </c>
-      <c r="R50" t="b">
+          <t>The model estimates herd immunity timelines based on vaccination rates but offers no relevance to insurance reserving, claim development, or loss forecasting.</t>
+        </is>
+      </c>
+      <c r="Q50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4423,20 +4439,17 @@
       <c r="N51" t="b">
         <v>0</v>
       </c>
-      <c r="O51" t="b">
-        <v>1</v>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>This paper focuses on credit risk and downgrade prediction using financial news and neural embeddings, with no direct application to general insurance claims reserving or loss reserve estimation.</t>
+        </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>The paper develops a neural model using financial news embeddings to predict credit rating downgrades, improving benchmark quantitative models by over 5% in AUC recall.</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Financial news data can enhance credit risk downgrade prediction when used as a feature in neural network models, but the work has minimal relevance to general insurance claims reserving.</t>
-        </is>
-      </c>
-      <c r="R51" t="b">
+          <t>The model improves credit downgrade prediction using news data but offers no practical value for actuarial reserving in general insurance.</t>
+        </is>
+      </c>
+      <c r="Q51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4505,20 +4518,17 @@
       <c r="N52" t="b">
         <v>0</v>
       </c>
-      <c r="O52" t="b">
-        <v>1</v>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>The paper introduces an R package for estimating nested partially-latent class models under case-control designs, primarily useful for epidemiological or survey data analysis, with no direct application to claims reserving or loss development.</t>
+        </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>The baker R package implements partially-latent class models forivariate binary responses under case-control designs, with Bayesian inference via JAG and tools for diagnostics and visualization.</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>This package is designed for epidemiological or social science case-control studies and lacks direct applicability to claims reserving, individual claim modeling, or loss triangle forecasting.</t>
-        </is>
-      </c>
-      <c r="R52" t="b">
+          <t>While methodologically sound, the package's focus on case-control binary response modeling offers minimal practical value for actuarial reserving tasks such as IBNR estimation or claim triangle forecasting.</t>
+        </is>
+      </c>
+      <c r="Q52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4587,20 +4597,17 @@
       <c r="N53" t="b">
         <v>1</v>
       </c>
-      <c r="O53" t="b">
-        <v>1</v>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>This paper addresses a practical challenge in stochastic loss reserving—modeling dependence via common shocks when data is unbalanced across triangles or cells—and proposes a Tweedie-based solution that balances shock impact and retains tractability.</t>
+        </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>The addresses challenges in stochastic loss reserving when dealing with unbalanced data and negative claim amounts by introducing a common shock Tweedie model that better balances shock proportions and maintains distributional tractability.</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>A common shock Tweedie model effectively handles unbalanced claim data in loss reserving while parsimony and distributional tractability.</t>
-        </is>
-      </c>
-      <c r="R53" t="b">
+          <t>The common shock Tweedie model effectively scales common shocks to unbalanced claim data, preserving interpretability and distributional tractability while improving realism in stochastic reserving.</t>
+        </is>
+      </c>
+      <c r="Q53" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4669,15 +4676,17 @@
       <c r="N54" t="b">
         <v>0</v>
       </c>
-      <c r="O54" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>The Lightning Network’s current economic model is unsustainable for most, and its privacy protections are weak due to the small-world nature of payment paths.</t>
-        </is>
-      </c>
-      <c r="R54" t="b">
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>This paper analyzes the economic and privacy properties of Bitcoin's Lightning Network using traffic simulation, with no connection to actuarial claims reserving or insurance loss modeling.</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>The Lightning Network's current fee structure and routing topology make economic participation irrational for most nodes and offer limited privacy despite onion routing.</t>
+        </is>
+      </c>
+      <c r="Q54" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4746,20 +4755,17 @@
       <c r="N55" t="b">
         <v>0</v>
       </c>
-      <c r="O55" t="b">
-        <v>1</v>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>This paper addresses challenges in modeling neutrino distribution functions in neutron star merger simulations, which is unrelated to actuarial claims reserving or general insurance.</t>
+        </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>The paper discusses challenges in modelingino distribution functions in neutron star merger simulations, highlighting limitations of current Monte Carlo methods and proposing adjustments to better respect fermionic constraints.</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Current Monte Carlo methods in neutron star simulations fail to accurately capture neutrino distribution due to fermionic blocking effects, requiring novel weighting and smoothing techniques for physically consistent results.</t>
-        </is>
-      </c>
-      <c r="R55" t="b">
+          <t>The paper highlights computational and physical limitations in simulating fermionic neutrino behavior in astrophysical contexts, with no applicability to reserving or actuarial science.</t>
+        </is>
+      </c>
+      <c r="Q55" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4828,20 +4834,17 @@
       <c r="N56" t="b">
         <v>1</v>
       </c>
-      <c r="O56" t="b">
-        <v>1</v>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>The paper introduces a Bayesian model using skew-heavy-tailed distributions for loss reserving, validated on runoff triangle data and shown to outperform traditional models under skewed, heavy-tailed claim conditions.</t>
+        </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>The paper introduces a Bayesian model using skew-heavy-tailed distributions for loss reserving, validated on runoff triangle data and shown to outperform traditional models under skewness and heavy tails.</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Bayesian skew-heavy-tailed modelling improves reserve estimation accuracy in the presence of non-normal claim liabilities, offering a practical alternative to standard actuarial methods.</t>
-        </is>
-      </c>
-      <c r="R56" t="b">
+          <t>Bayesian skew-heavy-tailed modelling improves reserve estimation accuracy in the presence of non-normal claim liabilities, offering practical value for actuarial reserving where tail risk and asymmetry are critical.</t>
+        </is>
+      </c>
+      <c r="Q56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4905,25 +4908,22 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" t="b">
         <v>0</v>
       </c>
-      <c r="O57" t="b">
-        <v>1</v>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>This paper focuses on view selection and geometric uncertainty modeling in 3D reconstruction from aerial imagery, with no connection to claims reserving or actuarial science.</t>
+        </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>The paper addresses selection 3D reconstruction from aerial, showing that a small subset of views can approximate full-view uncertainty bounds, with applications in farm and orchard monitoring.</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>A small, strategically chosen set of camera views can nearly match the reconstruction accuracy of using all possible views, faster 3D scene reconstruction.</t>
-        </is>
-      </c>
-      <c r="R57" t="b">
+          <t>The paper provides provably efficient view selection for 3D scene reconstruction but offers no relevance to insurance reserving, loss modeling, or actuarial applications.</t>
+        </is>
+      </c>
+      <c r="Q57" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4992,20 +4992,17 @@
       <c r="N58" t="b">
         <v>0</v>
       </c>
-      <c r="O58" t="b">
-        <v>1</v>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>The paper examines when complete case analysis is valid for regression models with right-censored covariates, using simulations and a medical example, but does not address claims reserving or actuarial applications.</t>
+        </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>The paper examines when complete case analysis is valid for regression models with right-censored covariates, clarifying assumptions and demonstrating performance via and a example.</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Complete case analysis can yield consistent estimates under specific censoring assumptions, but its relevance to actuarial reserving is minimal without direct application to claims or reserve modeling.</t>
-        </is>
-      </c>
-      <c r="R58" t="b">
+          <t>Complete case analysis can yield consistent estimates under specific censoring assumptions, but the findings are not directly applicable to insurance reserving contexts.</t>
+        </is>
+      </c>
+      <c r="Q58" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5035,7 +5032,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>A geometric approximation of $δ$-interactions by Neumann Laplacians</t>
+          <t>A geometric approximation of δ-interactions by Neumann Laplacians</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5074,20 +5071,17 @@
       <c r="N59" t="b">
         <v>0</v>
       </c>
-      <c r="O59" t="b">
-        <v>1</v>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>This paper explores mathematical approximations of quantum mechanical operators using Neumann Laplacians in narrow domains, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> paper explores mathematical convergenceumann Laplacians on narrow domains to Schdinger operators with δ-interactions, focusing on spectral properties and rate estimates in a theoretical physics context.</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>This is a pure mathematical physics paper with no to actuarial reserving, claims development, or machine learning applications in insurance.</t>
-        </is>
-      </c>
-      <c r="R59" t="b">
+          <t>The work is purely theoretical and focused on spectral convergence in quantum mechanics, offering no practical value for claims reserving or machine learning applications in actuarial science.</t>
+        </is>
+      </c>
+      <c r="Q59" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5156,15 +5150,17 @@
       <c r="N60" t="b">
         <v>0</v>
       </c>
-      <c r="O60" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>This theoretical physics paper has no practical relevance to actuarial claims res or machine learning applications in insurance.</t>
-        </is>
-      </c>
-      <c r="R60" t="b">
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>This paper explores quantum phase transitions in a staggered Su-Schrieffer-Heeger ladder model, focusing on topological order and critical phenomena in condensed matter physics.</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>The study reveals how interactions near a quantum critical point lead to emergent topological phases and solitonic excitations, with no connection to actuarial reserving or insurance loss modelling.</t>
+        </is>
+      </c>
+      <c r="Q60" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5233,15 +5229,17 @@
       <c r="N61" t="b">
         <v>0</v>
       </c>
-      <c r="O61" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>The paper introduces a privacy-preserving federated aggregation framework for ephemeral user data, with direct application to claimserving or actuarial modeling.</t>
-        </is>
-      </c>
-      <c r="R61" t="b">
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>The paper introduces Mayfly, a federated analytics system for computing private aggregate statistics from ephemeral on-device data streams, with no direct connection to claims reserving or actuarial practice.</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Mayfly enables privacy-preserving aggregate analytics on transient user data but offers no practical relevance to general insurance reserving or loss estimation.</t>
+        </is>
+      </c>
+      <c r="Q61" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5310,20 +5308,17 @@
       <c r="N62" t="b">
         <v>0</v>
       </c>
-      <c r="O62" t="b">
-        <v>1</v>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>The paper focuses on type-based analysis for bounding expected execution costs in probabilistic programs, with no direct connection to actuarial reserving or claims development modeling.</t>
+        </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> paper introduces a type-based method to derive upper on expected execution cost for probabilistic programs, using amortized analysis and symbolic probabilities, with applications program termination and sample complexity estimation.</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>This work advances theoretical resource analysis for probabilistic programs but has no direct or transferable relevance to actuarial claims reserving or loss reserve modeling.</t>
-        </is>
-      </c>
-      <c r="R62" t="b">
+          <t>This work advances theoretical resource analysis for probabilistic programming but offers no practical value or transferability to general insurance claims reserving.</t>
+        </is>
+      </c>
+      <c r="Q62" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5392,20 +5387,17 @@
       <c r="N63" t="b">
         <v>0</v>
       </c>
-      <c r="O63" t="b">
-        <v>1</v>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>This paper examines how caste-group diversity in India influenced the spread of COVID-19 during lockdowns, finding slower infection growth in more homogeneous districts.</t>
+        </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>The paper examines how caste diversity in India the spread of COVID-19 during lockdowns, finding that homogeneous districts experienced slower infection growth, potentially due to stronger community health worker engagement.</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Caste-group homogeneity in Indian districts correlated with slower COVID-19 spread lockdowns, possibly due to more effective local health coordination.</t>
-        </is>
-      </c>
-      <c r="R63" t="b">
+          <t>Caste-group homogeneity is associated with slower pandemic spread, likely due to stronger community coordination and health worker engagement.</t>
+        </is>
+      </c>
+      <c r="Q63" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5474,20 +5466,17 @@
       <c r="N64" t="b">
         <v>1</v>
       </c>
-      <c r="O64" t="b">
-        <v>1</v>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>The paper introduces diagnostic tests to evaluate serial dynamics and dependence in longitudinal actuarial data, offering practical guidance for model selection in reserving contexts.</t>
+        </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>The paper introduces diagnostic tests serial dynamics and dependence structures longitudinal insurance data before modeling, challenging assumptions in actuarial practice and offering guidance for more appropriate model selection.</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Diagnostic testing for serial dynamics and correlation in longitudinal claims data can reveal hidden dependencies that invalidate standard actial modeling, leading to better-informed reserving models.</t>
-        </is>
-      </c>
-      <c r="R64" t="b">
+          <t>Validating assumptions about temporal dependence before modeling can significantly improve the reliability of reserving models by preventing misspecification.</t>
+        </is>
+      </c>
+      <c r="Q64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5551,25 +5540,22 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
       </c>
-      <c r="O65" t="b">
-        <v>1</v>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>The paper focuses on mean-field game theory for investment and hedging under relative performance concerns, using stochastic differential equations with jumps, but does not address claims reserving, loss triangles, or actuarial reserving methods.</t>
+        </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>The constructs mean-field equilibria competitive and hedging under exponential utility, using random measures to model common noise, with applications to games rather than insurance reserving.</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>This work advances mean-field game theory for financial hedging under relative performance concerns but has no direct or transferable relevance to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R65" t="b">
+          <t>This work is mathematically rigorous in financial game theory but has no practical relevance to general insurance claims reserving or actuarial practice.</t>
+        </is>
+      </c>
+      <c r="Q65" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5638,15 +5624,17 @@
       <c r="N66" t="b">
         <v>0</v>
       </c>
-      <c r="O66" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>The paper is speculative and theoretical, offering no direct or transferable value to actuarial claims reserving practice or research.</t>
-        </is>
-      </c>
-      <c r="R66" t="b">
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>This paper explores the theoretical potential of quantum computing in insurance and actuarial science but lacks concrete applications to claims reserving or practical methodologies for actuaries.</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Quantum computing is framed as a future possibility for insurance, but no actionable reserving techniques, models, or empirical results are provided for current actuarial practice.</t>
+        </is>
+      </c>
+      <c r="Q66" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5715,20 +5703,17 @@
       <c r="N67" t="b">
         <v>1</v>
       </c>
-      <c r="O67" t="b">
-        <v>1</v>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>This paper provides theoretical justification and improvement for the Mack bootstrap method in claims reserving, addressing its limitations in capturing estimation uncertainty and proposing a superior alternative with empirical validation.</t>
+        </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>The paper provides the first theoretical justification for Mack’s bootstrap in claims reserving, identifies its limitations in capturing estimation uncertainty, and proposes an improved alternative with superior performance in simulations.</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Mack’s bootstrap correctly captures process uncertainty only if development factor distributions are correctly specified, but fails to capture estimation uncertainty—prompting a new bootstrap variant that addresses this gap.</t>
-        </is>
-      </c>
-      <c r="R67" t="b">
+          <t>The paper proves that the standard Mack bootstrap fails to capture estimation uncertainty and introduces an improved version that correctly models both process and estimation uncertainty components.</t>
+        </is>
+      </c>
+      <c r="Q67" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5797,15 +5782,17 @@
       <c r="N68" t="b">
         <v>0</v>
       </c>
-      <c r="O68" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>This paper focuses on wireless communication channel estimation no relevance to actuarial claims reserving or loss modelling.</t>
-        </is>
-      </c>
-      <c r="R68" t="b">
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>This paper focuses on low-complexity channel estimation for MIMO-OFDM wireless communication systems and has no connection to actuarial claims reserving or insurance loss modelling.</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>The research is entirely unrelated to general insurance reserving, offering no practical value or transferable methodology for the IFoA Working Party's objectives.</t>
+        </is>
+      </c>
+      <c r="Q68" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5869,25 +5856,22 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
       </c>
-      <c r="O69" t="b">
-        <v>1</v>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>The paper explores skewed link regression models for imbalanced binary outcomes in life insurance mortality prediction, using Bayesian methods and real data to show improved performance over standard GLMs.</t>
+        </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>The paper proposes link models for imbalanced binary outcomes life insurance mortality prediction, using Bayesian methods and real data to show improved performance over standard logistic/probit models.</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Skewed link GLMs under a Bayesian framework outperform standard binary models for rare-event mortality prediction in life insurance, but the focus is not on general insurance reserving.</t>
-        </is>
-      </c>
-      <c r="R69" t="b">
+          <t>Skewed link functions in Bayesian GLMs can better model rare mortality events in life insurance, but the focus on mortality rather than general insurance claims reserving limits its direct applicability to the working party's goals.</t>
+        </is>
+      </c>
+      <c r="Q69" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5956,20 +5940,17 @@
       <c r="N70" t="b">
         <v>0</v>
       </c>
-      <c r="O70" t="b">
-        <v>1</v>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>This paper focuses on automated defect detection in industrial radiography using a modified U-Net model, with no connection to insurance claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>The paper presents an-based framework using a modified U-Net model to automatically detect and categorize defects in radiographic images of airplane welds, leveraging data augmentation and achieving high detection accuracy with low false call rates.</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>This research focuses on industrial non-destructive testing and has no practical relevance to actuarial claims reserving or loss prediction.</t>
-        </is>
-      </c>
-      <c r="R70" t="b">
+          <t>The research is entirely unrelated to claims reserving, loss modelling, or any actuarial application, making it of negligible relevance to the working party.</t>
+        </is>
+      </c>
+      <c r="Q70" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6038,15 +6019,17 @@
       <c r="N71" t="b">
         <v>0</v>
       </c>
-      <c r="O71" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>While potentially useful for claim documentation analysis, the paper lacks direct connection to claims reserving methodology, probabilistic forecasting, or actuarial model development.</t>
-        </is>
-      </c>
-      <c r="R71" t="b">
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>This paper develops a text classification system to identify semantic aspects in legal depositions, primarily for summarization and information retrieval in tort litigation contexts.</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>While potentially useful for insurance claim agents reviewing deposition transcripts, the paper lacks direct application to claims reserving, reserve uncertainty, or predictive modeling of claim development.</t>
+        </is>
+      </c>
+      <c r="Q71" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6115,20 +6098,17 @@
       <c r="N72" t="b">
         <v>1</v>
       </c>
-      <c r="O72" t="b">
-        <v>1</v>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>DeepTriangle introduces a deep learning framework for loss reserving that jointly models paid losses and claims outstanding, requiring minimal feature engineering and outperforming traditional stochastic methods.</t>
+        </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>The paper introduces DeepTriangle a deep learning framework for loss reserving that jointly models paid losses and claims outstanding accommodating heterogeneous inputs, demonstrating improved predictive accuracy over traditional stochastic methods with minimal feature engineering.</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>DeepTriangle offers a practical, automated deep learning solution for loss reserving that outperforms traditional stochastic methods while requiring little expert input or feature engineering.</t>
-        </is>
-      </c>
-      <c r="R72" t="b">
+          <t>The model's ability to automate forecasts and improve accuracy across lines of business makes it highly practical for actuarial reserving workflows.</t>
+        </is>
+      </c>
+      <c r="Q72" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6197,20 +6177,17 @@
       <c r="N73" t="b">
         <v>1</v>
       </c>
-      <c r="O73" t="b">
-        <v>1</v>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>This paper introduces a copula-based model to capture dependencies in IBNR claim timing and delay, validated via simulation and real auto insurer data, with comparison to the classical chain ladder method.</t>
+        </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>The copula-based model to capture dependencies betweenNR variables—time between occurrences and delay time—and validates it via simulation and real-world auto insurer data, benchmarking against the classical chain ladder model.</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>Copula modeling improves IBNR estimation by explicitly capturing dependency structures between claim timing variables, offering a practical alternative to traditional methods.</t>
-        </is>
-      </c>
-      <c r="R73" t="b">
+          <t>Copula modeling of IBNR claim timing dependencies offers a practical, interpretable alternative to traditional methods with empirical validation against chain ladder.</t>
+        </is>
+      </c>
+      <c r="Q73" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6279,20 +6256,17 @@
       <c r="N74" t="b">
         <v>0</v>
       </c>
-      <c r="O74" t="b">
-        <v>1</v>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>This paper explores theoretical improvements in quantum simulation using product formulas, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> paper analyzes the average performance of product formulas (rotterization) in quantum simulation, showing they often outperform worst bounds for typical input states, with implications for gate complexity in quantum algorithms.</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Product formulas in quantum simulation perform significantly better on average than worst-case estimates suggest, especially for highly connected systems and specific input state distributions.</t>
-        </is>
-      </c>
-      <c r="R74" t="b">
+          <t>The paper demonstrates that product formulas for quantum simulation perform better on average-case inputs than worst-case bounds suggest, but this has no practical relevance to claims reserving.</t>
+        </is>
+      </c>
+      <c r="Q74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6361,20 +6335,17 @@
       <c r="N75" t="b">
         <v>1</v>
       </c>
-      <c r="O75" t="b">
-        <v>1</v>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>The paper applies functional data analysis to loss development triangles in workers' compensation, offering a probabilistic forecasting method with uncertainty quantification that outperforms Chain Ladder.</t>
+        </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>The paper applies functional data to loss development patterns in’ compensation, using PCA and bootstrapping to forecast incomplete ILR curves and quantify uncertainty, outperforming Chain Ladder in probabilistic scoring.</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Functional data methods enable accurate probabilistic forecasting of loss development curves with joint uncertainty quant, offering a practical alternative to traditional-based reserving.</t>
-        </is>
-      </c>
-      <c r="R75" t="b">
+          <t>Functional bootstrapping combined with PCA-based regression enables accurate joint uncertainty quantification for incomplete loss development curves, directly advancing practical reserving methodology.</t>
+        </is>
+      </c>
+      <c r="Q75" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6443,15 +6414,17 @@
       <c r="N76" t="b">
         <v>0</v>
       </c>
-      <c r="O76" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>The method enables efficient parameter estimation under complex missingness patterns by integrating pre-trained AI models into semiparametric inference, with guaranteed asymptotic efficiency regardless model accuracy.</t>
-        </is>
-      </c>
-      <c r="R76" t="b">
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>The paper introduces a semiparametric inference method for blockwise missing data using AI models, but it is not focused on claims reserving or insurance applications.</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>The IBM(RAY) estimator improves efficiency over complete-case analysis for blockwise missing data, regardless of AI model accuracy, but lacks direct relevance to actuarial reserving contexts.</t>
+        </is>
+      </c>
+      <c r="Q76" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6520,20 +6493,17 @@
       <c r="N77" t="b">
         <v>1</v>
       </c>
-      <c r="O77" t="b">
-        <v>1</v>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>This paper introduces a time-varying copula framework for granular, claim-level reserving to address limitations of aggregated triangle methods, with potential for improved reserve estimation across multiple lines of business.</t>
+        </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>The paper addresses limitations of aggregate triangle methods by proposing a granular, claim-level reserving approach using time-varying copulas to model dependencies and improve reserve estimation.</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Time-varying copulas applied at the individual claim level offer a flexible, dependency-aware framework to overcome information loss and instability inherent in traditional aggregated triangle reserving.</t>
-        </is>
-      </c>
-      <c r="R77" t="b">
+          <t>The proposed copula-based approach enables dynamic, micro-level reserving by modeling dependencies in individual claim development, offering a practical alternative to traditional aggregate methods.</t>
+        </is>
+      </c>
+      <c r="Q77" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6602,20 +6572,17 @@
       <c r="N78" t="b">
         <v>1</v>
       </c>
-      <c r="O78" t="b">
-        <v>1</v>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>The paper introduces a nonparametric method for modeling insurance cash flows and estimating reserves including IBNR, validated against traditional actuarial methods using real Russian non-life data.</t>
+        </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>The paper introduces a nonparametric method for modeling insurance cash flows and reserves using individual claim data, validated against traditional methods like chain-ladder and Bornhuetter-Ferguson, with applications in reserve redistribution and IAS 17 compliance.</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>The proposed additive, claim-level nonparametric approach yields reserve estimates comparable to traditional actuarial methods while enabling granular portfolio and time-interval analysis.</t>
-        </is>
-      </c>
-      <c r="R78" t="b">
+          <t>The additive, claim-level estimation approach enables flexible reserve redistribution and financial reporting alignment while maintaining accuracy comparable to chain-ladder and Bornhuetter-Ferguson methods.</t>
+        </is>
+      </c>
+      <c r="Q78" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6684,20 +6651,17 @@
       <c r="N79" t="b">
         <v>0</v>
       </c>
-      <c r="O79" t="b">
-        <v>1</v>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>This paper explores the Mott transition in condensed matter physics using the Gutzwiller wavefunction and does not address claims reserving, actuarial science, or machine learning applications in insurance.</t>
+        </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> paper the Mott in condensed matter physics using Gutzwiller wavefunction and Monte Carlo methods, focusing on electronicitation behavior across lattice structures and challenging conventional Fermi-liquid interpretations.</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
           <t>The Mott transition is better understood as freezing of charge degrees of freedom while spin remains active, even under Fermi-liquid-like ground states.</t>
         </is>
       </c>
-      <c r="R79" t="b">
+      <c r="Q79" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6766,20 +6730,17 @@
       <c r="N80" t="b">
         <v>0</v>
       </c>
-      <c r="O80" t="b">
-        <v>1</v>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>This paper focuses on improving stochastic estimators for fermion traces in lattice QCD, with no connection to actuarial reserving, claims development, or insurance loss modeling.</t>
+        </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> paper-splitting estimators to reduce variance in lattice QCD calculations of single-propagator traces, achieving significant computational efficiency gains for specific ferm bilinears and disconnected correlation functions.</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Frequency-splitting estimators drastically reduce computational cost in lattice QCD by minimizing-induced variance, enabling more efficient calculation of disconnected diagrams relevant to particle physics.</t>
-        </is>
-      </c>
-      <c r="R80" t="b">
+          <t>The proposed frequency-splitting estimators significantly reduce computational cost in quantum chromodynamics simulations but offer no practical value for general insurance reserving research.</t>
+        </is>
+      </c>
+      <c r="Q80" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6848,20 +6809,17 @@
       <c r="N81" t="b">
         <v>0</v>
       </c>
-      <c r="O81" t="b">
-        <v>1</v>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>The paper develops conservative standard errors for calibrated structural models using only variances of empirical moments, with applications in macroeconomics, but does not address claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>The derives conservative standard for calibrated structural models using only variances of empirical moments, applicable to over-identified models and moment selection, with applications in macroeconomic pricing models.</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>The paper provides a method to compute valid confidence intervals for calibrated parameters without requiring full correlation structure estimates, but it lacks direct application to claims reserving oruarial practice.</t>
-        </is>
-      </c>
-      <c r="R81" t="b">
+          <t>Conservative standard errors can be derived without estimating moment correlations, offering robust inference under worst-case assumptions, though not tailored to reserving contexts.</t>
+        </is>
+      </c>
+      <c r="Q81" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6925,25 +6883,22 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
       </c>
-      <c r="O82" t="b">
-        <v>1</v>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>The paper introduces a gradient boosting framework for spatial panel models with fixed and random effects, applicable to non-life insurance data at a district level, though not focused on claims reserving or development triangles.</t>
+        </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>The paper introduces a gradient boosting algorithm for spatial panel models with and fixed effects, applicable to high and demonstrated on non-life insurance data in Italian districts among other domains.</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>While the method is adaptable and includes an insurance application, it lacks direct focus on claims reserving mechanics, its practical value to actuarial reserving limited without further adaptation.</t>
-        </is>
-      </c>
-      <c r="R82" t="b">
+          <t>Gradient boosting can handle high-dimensional spatial panel data with interpretable results and implicit regularization, offering potential for actuarial applications in geographically stratified loss modeling.</t>
+        </is>
+      </c>
+      <c r="Q82" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7012,15 +6967,17 @@
       <c r="N83" t="b">
         <v>0</v>
       </c>
-      <c r="O83" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>The square root rule performs best for reserve estimation with sufficient data, while simultaneous estimation excels with small samples, bulk distribution choice significantly affects results—especially in heavy-tailed cases.</t>
-        </is>
-      </c>
-      <c r="R83" t="b">
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>This paper explores composite models for extreme claims using threshold selection methods and evaluates their impact on reserve estimation, with a focus on bulk distribution choice and sample size effects.</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>The square root rule performs best for reserve estimation with sufficient data, while simultaneous estimation excels in small samples, and bulk distribution choice significantly affects results—especially under heavy tails.</t>
+        </is>
+      </c>
+      <c r="Q83" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7089,20 +7046,17 @@
       <c r="N84" t="b">
         <v>0</v>
       </c>
-      <c r="O84" t="b">
-        <v>1</v>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>This paper focuses on traffic signal control using multi-agent reinforcement learning and distributional robustness, with no connection to claims reserving, loss development, or actuarial modeling.</t>
+        </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Theally robust multi-agent reinforcement learning method for traffic signal, trained on real and synthetic traffic scenarios to improve performance under adversarial conditions, with significant gains in queue reduction and speed increase.</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>This research focuses on traffic control optimization using reinforcement learning under demand uncertainty and has no relevance to actuarial claims reserving or loss reserving.</t>
-        </is>
-      </c>
-      <c r="R84" t="b">
+          <t>The research advances robust traffic control under uncertain demand but offers no practical value or transferability to general insurance reserving.</t>
+        </is>
+      </c>
+      <c r="Q84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7171,20 +7125,17 @@
       <c r="N85" t="b">
         <v>1</v>
       </c>
-      <c r="O85" t="b">
-        <v>1</v>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>This paper introduces robust bootstrap methods for the chain-ladder technique to improve reserve estimation under outlier contamination, with applications to one-year risk measures and validation on real and simulated data.</t>
+        </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>The introduces robust bootstrap methods for the-ladder reserving technique to handle outliers in claims data, evaluating their performance on simulated and real datasets while enabling better uncertainty quantification for one-year risk measures.</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Robust bootstrap procedures improve the reliability of reserve estimates and uncertainty quantification in the presence of outliers, making them practically valuable for actuarial reserving practice.</t>
-        </is>
-      </c>
-      <c r="R85" t="b">
+          <t>Robust bootstrap procedures can meaningfully enhance the reliability of stochastic reserve estimates in the presence of outliers, offering practical value for actuarial reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q85" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7253,15 +7204,17 @@
       <c r="N86" t="b">
         <v>0</v>
       </c>
-      <c r="O86" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>The proposed measure ζ(t) quantifies spin-charge separation and may serve as an order parameter for Mott insulating phases in 2D Hubbard systems.</t>
-        </is>
-      </c>
-      <c r="R86" t="b">
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>This paper introduces a quantitative measure for spin-charge separation in the 2D Hubbard model, focusing on condensed matter physics and non-equilibrium dynamics, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>The paper's focus on quantum many-body systems and Mott insulators has no practical relevance to general insurance claims reserving or machine learning applications in actuarial science.</t>
+        </is>
+      </c>
+      <c r="Q86" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7330,20 +7283,17 @@
       <c r="N87" t="b">
         <v>0</v>
       </c>
-      <c r="O87" t="b">
-        <v>1</v>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>This paper studies the asymptotic length of increasing trails and paths in randomly edge-labeled Erdős–Rényi graphs, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>This studies the length of the longest increasing trail or path in random graphs with randomly assigned edge labels, focusing on asymptotic behavior in Erdős-Rényi graphs and complete graphs.</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>The paper establishes asymptotically tight bounds for the length of the longest increasing trail in random-labeled graphs, but has no practical relevance actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R87" t="b">
+          <t>The paper provides theoretical results on random graph labelings and trail lengths, which are mathematically interesting but irrelevant to claims reserving or machine learning applications in actuarial science.</t>
+        </is>
+      </c>
+      <c r="Q87" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7412,20 +7362,17 @@
       <c r="N88" t="b">
         <v>0</v>
       </c>
-      <c r="O88" t="b">
-        <v>1</v>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>The paper focuses on yield curve generators and interest rate risk for P&amp;C insurers, with emphasis on bond valuation and capital impacts under GAAP, not claims reserving or loss development.</t>
+        </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>This paper focuses on yield curve for P&amp;C insurers to assess interest rate risk, emphasizing model testing against historical and evolving market behavior, but does not address claimserving or loss forecasting.</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>The paper addresses interest rate risk modeling for P&amp;C insurers’ bond portfolios, which is tangential to reserving and lacks direct applicability to the working party’s focus.</t>
-        </is>
-      </c>
-      <c r="R88" t="b">
+          <t>This work addresses asset-side interest rate risk modeling for P&amp;C insurers, which is tangential to the working party's focus on liability-side claims reserving and predictive modeling.</t>
+        </is>
+      </c>
+      <c r="Q88" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7494,20 +7441,17 @@
       <c r="N89" t="b">
         <v>1</v>
       </c>
-      <c r="O89" t="b">
-        <v>1</v>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>This paper frames reserving as a reinforcement learning problem under macroeconomic regimes, using CVaR-constrained PPO to optimize reserve adequacy and solvency while aligning with regulatory frameworks like Solvency II.</t>
+        </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>The frames reserving a sequential decision problem using reinforcement learning with CVaR constraints to manage tail risk and solvency macroeconomic, showing improved risk control over classical methods.</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Reinforcement learning with CVaR constraints can enhance reserve adequacy and solvency governance by dynamically adapting to macroeconomic regimes while penalizing tail-risk exposure.</t>
-        </is>
-      </c>
-      <c r="R89" t="b">
+          <t>Reinforcement learning with CVaR constraints can improve tail-risk control in reserving decisions under macroeconomic stress, offering a governance-aligned alternative to classical actuarial methods.</t>
+        </is>
+      </c>
+      <c r="Q89" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7576,20 +7520,17 @@
       <c r="N90" t="b">
         <v>0</v>
       </c>
-      <c r="O90" t="b">
-        <v>1</v>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>This paper explores confinement properties in the Schwinger-Thirring model from a theoretical physics perspective, with no connection to actuarial science or claims reserving.</t>
+        </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>The investigates confinement and screening in the Schwinger-Thirring model, analyzing effects of interactions and gauge field dimensions, with potential experimental realization using ultracold atoms.</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Confinement or screening in 1+1 dimensional models is determined by the dimensionality of matter fields, not gauge fields, and remains robust under added interactions or higher-dimensional gauge fields.</t>
-        </is>
-      </c>
-      <c r="R90" t="b">
+          <t>The paper's findings on quantum field theory and string tension have no practical relevance to general insurance reserving or machine learning applications in actuarial practice.</t>
+        </is>
+      </c>
+      <c r="Q90" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7658,20 +7599,17 @@
       <c r="N91" t="b">
         <v>0</v>
       </c>
-      <c r="O91" t="b">
-        <v>1</v>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>This paper addresses astrophysical micro-lensing effects in quasar observations and has no connection to actuarial claims reserving or insurance loss modelling.</t>
+        </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> paper examines worst-case micro-lensing effects in astrophysical observations of lensed quasars, focusing on magnification uncertainties under specific gravitational lensing models.</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>Worst-case micro-lensing fluctuations are bounded for macro-minima and saddles under certain stellar fraction conditions, but demagnifications at saddles can become unbounded as macro-magnification approaches zero.</t>
-        </is>
-      </c>
-      <c r="R91" t="b">
+          <t>The paper quantifies worst-case micro-lensing uncertainties in astronomical imaging, which is entirely unrelated to general insurance reserving practice or methodology.</t>
+        </is>
+      </c>
+      <c r="Q91" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7740,20 +7678,17 @@
       <c r="N92" t="b">
         <v>1</v>
       </c>
-      <c r="O92" t="b">
-        <v>1</v>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>The paper introduces a non-convex regularization method (LAAD penalty) to stabilize loss development factor estimation in claims reserving, demonstrating promising results on real P&amp;C data with a provably convergent algorithm.</t>
+        </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>The paper introduces a non-convex regularization method (LAAD penalty) to stabilize loss development factor estimation in claims reserving, on real P&amp;C data with a provably convergent coordinate descent algorithm.</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>Non-conv LAAD regularization improves stability and variable selection in estimating loss development factors, offering a practical alternative traditional regression models in reserving.</t>
-        </is>
-      </c>
-      <c r="R92" t="b">
+          <t>LAAD-penalized regression improves stability and variable selection in estimating loss development factors, offering a practical, statistically grounded alternative to traditional methods for actuarial reserving.</t>
+        </is>
+      </c>
+      <c r="Q92" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7822,20 +7757,17 @@
       <c r="N93" t="b">
         <v>0</v>
       </c>
-      <c r="O93" t="b">
-        <v>1</v>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>The paper introduces ALTIS, a satellite-based flood damage assessment system for property-level triage, aimed at reducing manual claims inspections but not directly addressing reserving or reserve estimation.</t>
+        </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>ALT satellite-based using SAR imagery to generate property-level flood damage scores for faster claims triage, to reduce inspections by52% while maintaining high recall of severe claims.</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>The system prioritizes operational efficiency in postlood claims handling rather than reserve estimation or development modeling, limiting its relevance touarial reserving research.</t>
-        </is>
-      </c>
-      <c r="R93" t="b">
+          <t>ALTIS improves post-flood claims triage efficiency using SAR data but does not contribute to claims reserving, IBNR/RBNS estimation, or probabilistic reserve forecasting.</t>
+        </is>
+      </c>
+      <c r="Q93" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7904,15 +7836,17 @@
       <c r="N94" t="b">
         <v>0</v>
       </c>
-      <c r="O94" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>SAFE bootstrap simplifies variance estimation for sizes in meta-analysis through simulation, but offers direct relevance to actuarial claims reserving or loss reserve uncertainty quantification.</t>
-        </is>
-      </c>
-      <c r="R94" t="b">
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>The paper introduces a simulation-based bootstrap method (SAFE) for deriving bias-corrected effect size estimates and sampling variances in meta-analysis, primarily targeting statistical practitioners rather than actuarial reserving contexts.</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SAFE bootstrap simplifies variance estimation for arbitrary effect sizes via simulation, but lacks direct applicability to claims reserving, IBNR, or loss development modeling.</t>
+        </is>
+      </c>
+      <c r="Q94" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7976,25 +7910,22 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N95" t="b">
-        <v>0</v>
-      </c>
-      <c r="O95" t="b">
         <v>1</v>
       </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>The paper explores using graphical models to represent actuarial judgment and probabilistic learning in non-life insurance claims, with potential for integrating telematics and dynamic data.</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>The using graphical models to represent actial models incorporate actuarial judgment, particularly with dynamic data like telematics, though it lacks direct reserving applications or empirical validation.</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>Graphical models offer a framework to integrate actuarial judgment with probabilistic learning, but the paper does not demonstrate concrete reserving use cases or practical improvements over existing methods.</t>
-        </is>
-      </c>
-      <c r="R95" t="b">
+          <t>Graphical models offer a structured, intuitive way to embed actuarial judgment into probabilistic reserving frameworks while enabling scalable inference on complex, interdependent claim variables.</t>
+        </is>
+      </c>
+      <c r="Q95" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8063,20 +7994,17 @@
       <c r="N96" t="b">
         <v>1</v>
       </c>
-      <c r="O96" t="b">
-        <v>1</v>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>This paper presents a statistically robust state space modeling framework for IBNR reserving, complete with Kalman filtering, smoothing, and simulation methods, demonstrated on real data with reproducible SAS code.</t>
+        </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>This paper presents state space framework stochastic claims res, using Kalman filtering and smoothing to estimate IBNR reserves and their uncertainty, with reproducible SAS code and real data illustrations.</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>State space models offer a statistically robust, transparent, and comput tractable approach to stochastic reserving with built-in uncertainty quantification, directly to actuarial practice.</t>
-        </is>
-      </c>
-      <c r="R96" t="b">
+          <t>State space models offer a transparent, probabilistic, and computationally tractable approach to claims reserving that integrates model fitting, diagnostics, and uncertainty quantification in a unified framework.</t>
+        </is>
+      </c>
+      <c r="Q96" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8145,20 +8073,17 @@
       <c r="N97" t="b">
         <v>0</v>
       </c>
-      <c r="O97" t="b">
-        <v>1</v>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>The paper introduces a mixed criticality extension to Monte-Carlo Tree Search for embedded systems with uncertain resource costs, but it has no direct or transferable application to actuarial claims reserving.</t>
+        </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>The paper extends Monte Carlo Tree Search with Criticality concepts to handle uncertain resource costs in embedded systems, focusing on real-time decision-making under uncertainty for tasks of criticality.</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>The proposed (MC)²TS method improves resource allocation under cost uncertainty by adapting task criticality levels, but it has no direct or transferable application to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R97" t="b">
+          <t>The method optimizes resource allocation under uncertainty in real-time systems, which is unrelated to insurance reserving problems.</t>
+        </is>
+      </c>
+      <c r="Q97" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8222,25 +8147,22 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N98" t="b">
         <v>0</v>
       </c>
-      <c r="O98" t="b">
-        <v>1</v>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>The paper explores multivariate zero-inflated and zero-modified models for modeling correlated claim frequencies across insurance lines, with empirical applications to automobile insurance data.</t>
+        </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Theivariate zero-inflated and-modified models for modeling correlated claim frequencies in auto insurance, particularly addressing excess or deficient common zeros, using Spanish data.</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>Multivariate zero-modified models offer a flexible approach to handle both zeroflation and zero-deflation in correlated claim frequency data, which may inform reserving when frequency drives severity or exposure adjustments.</t>
-        </is>
-      </c>
-      <c r="R98" t="b">
+          <t>Multivariate zero-modified models offer a flexible and robust approach to handling excess or deficient common zeros in correlated claim frequency data, which can improve reserving accuracy when modeling multiple lines of business.</t>
+        </is>
+      </c>
+      <c r="Q98" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8309,15 +8231,17 @@
       <c r="N99" t="b">
         <v>0</v>
       </c>
-      <c r="O99" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>Schnieper’s model provides a consistent Poisson-based foundation for estimating claim frequencies above a priority, with Negative Binomial offering comparable results and bootstrap enhancing uncertainty assessment.</t>
-        </is>
-      </c>
-      <c r="R99" t="b">
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>The paper addresses frequency modeling above a priority level in reinsurance, incorporating IBNR and using Schnieper's framework with Poisson and Negative Binomial distributions, plus bootstrap uncertainty quantification.</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Schnieper's model provides a consistent Poisson-based foundation for estimating claim frequencies above a priority, with bootstrap methods enhancing parameter uncertainty assessment in IBNR-inclusive settings.</t>
+        </is>
+      </c>
+      <c r="Q99" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8386,15 +8310,17 @@
       <c r="N100" t="b">
         <v>0</v>
       </c>
-      <c r="O100" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>The method enables better modeling of dependence structures in censored claims data, which can support more accurate reserve estimation when integrated into broader reserving frameworks.</t>
-        </is>
-      </c>
-      <c r="R100" t="b">
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>The paper extends a non-parametric copula estimator to handle censored data and applies it to model dependence between correlated insurance coverages, with potential use in claims reserving workflows.</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Modeling dependence structures under flexible censoring using non-parametric copulas can enhance the realism of multilevel claims reserving models, especially when claim activation delays are correlated.</t>
+        </is>
+      </c>
+      <c r="Q100" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8424,7 +8350,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fermi surface as a quantum critical manifold: gaplessness, order parameter, and scaling in $d$-dimensions</t>
+          <t>Fermi surface as a quantum critical manifold: gaplessness, order parameter, and scaling in d-dimensions</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8463,20 +8389,17 @@
       <c r="N101" t="b">
         <v>0</v>
       </c>
-      <c r="O101" t="b">
-        <v>1</v>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>This paper explores quantum criticality and Fermi surfaces in fermionic systems, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>The paper explores quantum criticality in d-dimensionalionic systems focusing on Fermi surfaces as gapless manifolds and their role in Lifshitz transitions, with analysis of scaling behavior and universality classes in free and interacting systems.</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>Fermi surfaces act quantum critical manifolds governing gapless metallic phases and universal scaling behavior across dimensions, independent of interactions.</t>
-        </is>
-      </c>
-      <c r="R101" t="b">
+          <t>The paper advances theoretical condensed matter physics by characterizing gapless phases via geometric order parameters and scaling laws near Lifshitz transitions, but offers no practical value for claims reserving.</t>
+        </is>
+      </c>
+      <c r="Q101" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8545,20 +8468,17 @@
       <c r="N102" t="b">
         <v>0</v>
       </c>
-      <c r="O102" t="b">
-        <v>1</v>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>This paper introduces sum-rank Hamming and simplex codes for error correction in multishot matrix-multiplicative channels, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>This introduces sum-rank Ham and simplex codes for correction in multishot matrix-multiplicative channels, with theoretical bounds and decoding algorithms, but has no connection to actuarial reserving or insurance loss modelling.</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>The paper advances coding theory for matrix channels but offers no relevance claims reserving, probabilistic forecasting, or actuarial machine learning applications.</t>
-        </is>
-      </c>
-      <c r="R102" t="b">
+          <t>The work is purely theoretical coding theory with no practical relevance to claims reserving, loss forecasting, or actuarial machine learning applications.</t>
+        </is>
+      </c>
+      <c r="Q102" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8627,15 +8547,17 @@
       <c r="N103" t="b">
         <v>0</v>
       </c>
-      <c r="O103" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>The paper introduces a graph-based multi-path reasoning system for automated fact-checking, which has no direct or transferable relevance to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R103" t="b">
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>The paper introduces GraphCheck, a framework for multi-hop fact-checking using entity-relationship graphs, which is unrelated to claims reserving or actuarial modeling.</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>This research focuses on automated textual fact-checking and offers no practical value or transferability to general insurance claims reserving.</t>
+        </is>
+      </c>
+      <c r="Q103" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8704,20 +8626,17 @@
       <c r="N104" t="b">
         <v>1</v>
       </c>
-      <c r="O104" t="b">
-        <v>1</v>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>This paper reinterprets the chain-ladder method in continuous time using hazard functions and proposes kernel-smoothed alternatives, offering a theoretically grounded improvement with empirical validation on real data.</t>
+        </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>The introduces a continuous-time framework for claims reserving thatinterprets chain-ladder development factors as estimators of a cost-weighted hazard function, proposing kernel-smoothed alternatives and validating them with real data and simulations.</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>Chain-ladder can be viewed as a histogram estimator in continuous time, and replacing it with kernel smoothers improves reserve prediction under aggregation limits.</t>
-        </is>
-      </c>
-      <c r="R104" t="b">
+          <t>Chain-ladder development factors can be viewed as histogram estimators of a cost-weighted hazard function, and replacing them with kernel smoothers improves consistency and predictive performance in reserving.</t>
+        </is>
+      </c>
+      <c r="Q104" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8786,20 +8705,17 @@
       <c r="N105" t="b">
         <v>0</v>
       </c>
-      <c r="O105" t="b">
-        <v>1</v>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>The paper addresses minimax estimation for abstract Neumann problems in Hilbert spaces with uncertain inputs, which is mathematically rigorous but unrelated to actuarial reserving or insurance claim modeling.</t>
+        </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>The paper derivesax for abstract Neumann problems inbert space under uncertain inputs and noisy observations, with a focus on theoretical robustness and asymptotic exactness, illustrated via a 2D Poisson equation example.</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>This work provides theoreticalax estimation for abstract PDEs under uncertainty but has no practical connection to actuarial claims reserving or loss modelling.</t>
-        </is>
-      </c>
-      <c r="R105" t="b">
+          <t>This theoretical work on partial differential equations and robust estimation has no practical application to claims reserving, IBNR, or machine learning in actuarial science.</t>
+        </is>
+      </c>
+      <c r="Q105" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8868,20 +8784,17 @@
       <c r="N106" t="b">
         <v>1</v>
       </c>
-      <c r="O106" t="b">
-        <v>1</v>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>This paper analyzes the sensitivity of loss reserving methods, particularly Mack's model and Bornhuetter-Ferguson, to outliers using impact functions, with empirical validation on real insurer data.</t>
+        </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>This paper analyzes how outliers affect reserve estimates and prediction errors under Mack’s Model and Bornhuetter-Ferguson, using impact functions derived from derivatives of statistics with respect to observations, illustrated with real insurer data.</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>Outliers can significantly distort reserve estimates in Mack’s Model and Bornhuet-Ferguson, with impact varying across the loss triangle and depending on other cells’ values.</t>
-        </is>
-      </c>
-      <c r="R106" t="b">
+          <t>Outliers disproportionately affect reserve estimates in Mack's model depending on their position in the triangle, highlighting the need for robustness checks in actuarial practice.</t>
+        </is>
+      </c>
+      <c r="Q106" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8945,25 +8858,22 @@
         </is>
       </c>
       <c r="M107" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
       </c>
-      <c r="O107" t="b">
-        <v>1</v>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>The paper examines parameter uncertainty in reserve risk under Solvency II, critiquing bootstrapping and proposing an adapted method that better aligns with required confidence levels for solvency capital.</t>
+        </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> paper examines parameter uncertainty Solvency II reserve risk, arguing that classical reserving methods are inadequate for capturing economic loss risk and proposing an adapted method that better meets required confidence levels.</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>Standard bootstrapping fails to meet Solvency II’s confidence level requirements for reserve risk, and an adapted Froehlich-style method offers a more appropriate approach to parameter uncertainty modelling.</t>
-        </is>
-      </c>
-      <c r="R107" t="b">
+          <t>Standard bootstrapping is inadequate for modeling parameter uncertainty under Solvency II, and a modified Froehlich-style approach better achieves the required confidence level for reserve risk capital.</t>
+        </is>
+      </c>
+      <c r="Q107" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9032,20 +8942,17 @@
       <c r="N108" t="b">
         <v>1</v>
       </c>
-      <c r="O108" t="b">
-        <v>1</v>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>The paper introduces a multistate reserving model for disability insurance that accounts for real-time claim evolution and information delays, with parametric estimators and a real-data application.</t>
+        </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>The paper introduces a real-time individual reserving model for disability insurance that accounts for reporting and adjudication delays, extending classic multistate models with practical parametric estimators and a real-data application.</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>By decoupling available information from the underlying biometric process, the model enables more accurate real-time reserving in disability insurance despite significant claim delays.</t>
-        </is>
-      </c>
-      <c r="R108" t="b">
+          <t>By decoupling available information from the underlying biometric process, the model enables more accurate individual-level reserving in disability insurance despite reporting and adjudication delays.</t>
+        </is>
+      </c>
+      <c r="Q108" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9114,20 +9021,17 @@
       <c r="N109" t="b">
         <v>0</v>
       </c>
-      <c r="O109" t="b">
-        <v>1</v>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>The paper extends Bonus-Malus models to incorporate multi-product claim scores for dynamic risk classification, focusing on pricing rather than reserving.</t>
+        </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>The paper extends-M models to incorporate dynamic, multi-product claim scores for risk classification, using non-linear effects and real-world Dutch P&amp;C data show profitability from leveraging cross-product claims history.</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>Incorporating dynamic, cross-product claim scores risk classification can improve, but the focus is on and a posteriori risk segmentation rather than reserving or reserve uncertainty.</t>
-        </is>
-      </c>
-      <c r="R109" t="b">
+          <t>Incorporating cross-product claim history improves risk classification for pricing but does not address claims reserving, IBNR, or reserve uncertainty.</t>
+        </is>
+      </c>
+      <c r="Q109" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9196,20 +9100,17 @@
       <c r="N110" t="b">
         <v>1</v>
       </c>
-      <c r="O110" t="b">
-        <v>1</v>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>This paper proposes a stacked machine learning model combining Gradient Boosting, Random Forest, and ANNs to improve runoff prediction in claims reserving, calibrated with a log-normal approach for uncertainty quantification.</t>
+        </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>The paper proposes a stacked machine learning model combining Gradient Boosting, Random Forest, and Artificial Neural Networks to improve runoff prediction in reserving, enhanced with a log-normal approach for uncertainty quantification.</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>Stacking multiple ML models with a log-normal error structure improves reserve accuracy and risk assessment over traditional Bayesian and Chain Ladder methods.</t>
-        </is>
-      </c>
-      <c r="R110" t="b">
+          <t>Stacking traditional actuarial models with ML algorithms can enhance reserve accuracy and risk assessment while maintaining interpretability through hybrid calibration.</t>
+        </is>
+      </c>
+      <c r="Q110" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9278,20 +9179,17 @@
       <c r="N111" t="b">
         <v>1</v>
       </c>
-      <c r="O111" t="b">
-        <v>1</v>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>This paper bridges macro-level Chain-Ladder with micro-level data using inverse probability weighting, offering a statistically grounded extension that retains practicality for actuaries.</t>
+        </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>The paper introduces a micro-Ladder method using inverse probability weighting to incorporate individual claim data, providing a statistically grounded extension of the traditional macro-level approach while preserving practicality for actuaries.</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>By framing reserving as a population sampling problem, the paper Chain-Ladder to leverage granular claim data through inverse probability weights, bridging micro and macro reserving with statistical rigor.</t>
-        </is>
-      </c>
-      <c r="R111" t="b">
+          <t>The Chain-Ladder method is reinterpreted as a special case of an inverse probability weighted estimator, enabling incorporation of individual claim characteristics without sacrificing interpretability or statistical rigor.</t>
+        </is>
+      </c>
+      <c r="Q111" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9360,20 +9258,17 @@
       <c r="N112" t="b">
         <v>1</v>
       </c>
-      <c r="O112" t="b">
-        <v>1</v>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>This paper introduces a flexible hierarchical reserving model that integrates claim-specific covariates and development history, bridging aggregate and individual reserving approaches with practical validation on real and simulated data.</t>
+        </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>The paper introduces a flexible hierarchical reserving model that integrates claim-specific covariates and development history, bridging aggregate and individual reserving approaches using statistical or learning methods, validated on real and simulated data.</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>The hierarchical framework enables data-driven selection between aggregate and individual reserving by modeling claim events with covates, offering practical flexibility and robustness for actuarial practice.</t>
-        </is>
-      </c>
-      <c r="R112" t="b">
+          <t>The hierarchical framework enables data-driven selection between aggregate and individual reserving while incorporating machine learning methods to improve predictive accuracy and interpretability for non-life claims.</t>
+        </is>
+      </c>
+      <c r="Q112" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9442,20 +9337,17 @@
       <c r="N113" t="b">
         <v>0</v>
       </c>
-      <c r="O113" t="b">
-        <v>1</v>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>This paper proves the existence of a flat band in the chiral model of twisted bilayer graphene at a specific twist angle, using mathematical analysis and computer-assisted proofs.</t>
+        </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>This paper proves the existence of a magic angle in the ch model of twisted bilayer graphene by rigorously validating a formal expansion, using computer-ass proofs on finite-dimensional projections and polynomial sign analysis.</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>The paper provides a mathematically rigorous proof that at least one magic angle the chiral model of bilayer graphene, confirming prior heuristic results through controlled numerical and analytical methods.</t>
-        </is>
-      </c>
-      <c r="R113" t="b">
+          <t>The work confirms a theoretical prediction about electronic band structure in graphene physics, with no connection to actuarial reserving or machine learning applications in insurance.</t>
+        </is>
+      </c>
+      <c r="Q113" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9485,7 +9377,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Individual claims reserving using the Aalen--Johansen estimator</t>
+          <t>Individual claims reserving using the Aalen-Johansen estimator</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -9524,20 +9416,17 @@
       <c r="N114" t="b">
         <v>1</v>
       </c>
-      <c r="O114" t="b">
-        <v>1</v>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>The paper introduces a novel individual claims reserving method using the conditional Aalen-Johansen estimator, reinterpreting multi-state models to predict claim size development curves with validation on real and simulated data.</t>
+        </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>The paper introduces individual claims reserving model using the conditional Aalenohansen estimator, treating claim size as the state variable and modeling development via multi transitions to an absorbing state, validated on real and simulated data with probabilistic scoring.</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>Reinterpreting multi-state models around claim size rather than time enables accurate individual-level reserve prediction with full distributional output and strong empirical validation.</t>
-        </is>
-      </c>
-      <c r="R114" t="b">
+          <t>By treating claim size as the state variable in a multi-state model, this approach enables probabilistic forecasting of individual claim development paths, offering strong transferability to micro-level reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q114" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9601,25 +9490,22 @@
         </is>
       </c>
       <c r="M115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
       </c>
-      <c r="O115" t="b">
-        <v>1</v>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>The paper models loan default risk over time using multistate regression techniques, with implications for IFRS 9 loss reserves in banking, but is not directly focused on general insurance claims reserving.</t>
+        </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>The models loan default risk over time using multistate regression techniques, comparing Markov chains, beta regression, and multinomial logistic regression on mortgage data to IFRS 9 loss reserves.</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>More complex regression-based multistate models outperform simpler ones in estimating lifetime loan default risk under IFRS 9, though the context is banking rather than general insurance reserving.</t>
-        </is>
-      </c>
-      <c r="R115" t="b">
+          <t>While the multistate regression framework and diagnostics offer transferable methodological value, the focus on banking loan defaults under IFRS 9 limits its direct applicability to P&amp;C claims reserving.</t>
+        </is>
+      </c>
+      <c r="Q115" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9688,15 +9574,17 @@
       <c r="N116" t="b">
         <v>0</v>
       </c>
-      <c r="O116" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>While the synthetic dataset may be useful for pricing or underwriting research, it lacks direct applicability to actuarial reserving tasks such as IBNR estimation, claim development modeling, or reserve uncertainty quantification.</t>
-        </is>
-      </c>
-      <c r="R116" t="b">
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>The paper generates a synthetic telematics dataset for usage-based insurance risk modeling, using neural networks and SMOTE to simulate claims counts and amounts, with validation against real data using GLMs.</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>While the synthetic dataset could support reserving research if adapted, its primary focus on pricing/underwriting via telematics limits direct applicability to claims reserving without further methodological extension.</t>
+        </is>
+      </c>
+      <c r="Q116" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9765,20 +9653,17 @@
       <c r="N117" t="b">
         <v>1</v>
       </c>
-      <c r="O117" t="b">
-        <v>1</v>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>This paper provides a theoretical justification for Mack's chain ladder estimator under compound Poisson models via large exposure asymptotics, strengthening its practical validity in reserving without requiring distribution-free assumptions.</t>
+        </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>The paper shows that Mack’s chain ladder estimator and its prediction formula can be justified under large exposure asymptotics in compound Poisson models, even though classical compound Poisson assumptions don’t align with Mack’s distribution-free framework.</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>Mack’s estimator for chain ladder prediction is theoretically grounded under large exposure limits in compound Poisson settings, strengthening its practical validity without requiring strict distribution-free assumptions.</t>
-        </is>
-      </c>
-      <c r="R117" t="b">
+          <t>Mack's estimator can be rigorously derived and applied to compound Poisson loss models in the large exposure limit, offering a more defensible foundation for uncertainty quantification in traditional triangle-based reserving.</t>
+        </is>
+      </c>
+      <c r="Q117" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9847,20 +9732,17 @@
       <c r="N118" t="b">
         <v>1</v>
       </c>
-      <c r="O118" t="b">
-        <v>1</v>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>The paper develops a network-augmented GLMM for trade credit insurance data to jointly model claim probability and reporting delays, with applications to reserving and ratemaking.</t>
+        </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>The develops a network-amented GLMM for trade credit insurance data jointly model claim probability and reporting delays, using scalable SEM estimation and demonstrating improved performance over benchmarks for ratemaking and reserving.</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>Incorporating network structure and random effects a bivariate GLMM significantly improves predictive accuracy for TCI claims, offering practical value for reserving in specialized lines with complex dependencies.</t>
-        </is>
-      </c>
-      <c r="R118" t="b">
+          <t>Incorporating network structure and random effects into a bivariate GLMM improves predictive accuracy for TCI reserving, offering a transferable framework for micro-level reserving in complex, relational insurance lines.</t>
+        </is>
+      </c>
+      <c r="Q118" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9929,20 +9811,17 @@
       <c r="N119" t="b">
         <v>0</v>
       </c>
-      <c r="O119" t="b">
-        <v>1</v>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>The paper introduces a new type of non-parametric credible interval that blends Bayesian and frequentist properties, using only one-dimensional priors for simplicity and practicality.</t>
+        </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>The introduces a new type statistical interval that blends Bayesian and frequentist properties, using one-dimensional priors for non-parametric estimation of CDFs and means, offering practical advantages without high-dimensional prior specification.</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>The proposed intervals provide a middle ground between Bayesian and frequentist approaches by requiring only one-dimensional priors while maintaining credible belief after observing the interval, useful for non-parametric inference.</t>
-        </is>
-      </c>
-      <c r="R119" t="b">
+          <t>This method offers a computationally simpler alternative to full Bayesian intervals while preserving interpretability and calibration, potentially useful for uncertainty quantification in reserving when high-dimensional priors are impractical.</t>
+        </is>
+      </c>
+      <c r="Q119" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10011,20 +9890,17 @@
       <c r="N120" t="b">
         <v>1</v>
       </c>
-      <c r="O120" t="b">
-        <v>1</v>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>The paper introduces a survival analysis-based machine learning approach to forecast IBNR frequencies using individual claims data, with methods including Cox models, neural networks, and XGBoost, validated via simulation and real-world data.</t>
+        </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>The paper proposes machine learning-enhanced survival analysis methods to forecast IBNR frequencies using individual claim data, with development factors derived from hazard functions estimated via Cox models, neural networks, and XGBoost.</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>Machine learning methods applied to survival analysis can improve IBNR frequency forecasting by leveraging granular claim features while maintaining coherence across time granularities.</t>
-        </is>
-      </c>
-      <c r="R120" t="b">
+          <t>Modeling IBNR frequencies through hazard functions estimated via machine learning offers a flexible, granular, and coherent approach that improves upon traditional actuarial assumptions while maintaining practical interpretability.</t>
+        </is>
+      </c>
+      <c r="Q120" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10093,15 +9969,17 @@
       <c r="N121" t="b">
         <v>0</v>
       </c>
-      <c r="O121" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>Neural Bayesimators enable fast, robust posterior inference for sparse administrative data in social science contexts, but lack applicability to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R121" t="b">
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>The paper introduces neural Bayesian estimators for Multiple Systems Estimation to handle sparse, censored data in social science contexts like estimating hidden populations, but does not address claims reserving or insurance loss estimation.</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Neural Bayes and Posterior Estimators offer fast, robust inference for sparse administrative data in sociology, but lack direct applicability to actuarial reserving problems.</t>
+        </is>
+      </c>
+      <c r="Q121" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10170,20 +10048,17 @@
       <c r="N122" t="b">
         <v>0</v>
       </c>
-      <c r="O122" t="b">
-        <v>1</v>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>This paper evaluates time-series forecasting models, including LSTM and SARIMAX, for predicting chickenpox incidence in Hungary, with a focus on county- and national-level forecasts.</t>
+        </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>The paper evaluates-series forecasting, including LSTM and SARAX, for predicting chickenpox incidence in Hungary, finding LSTM superior at county level SAR at national level, with a proposed preprocessing method outperforming traditional ones.</t>
-        </is>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>LSTM and SARAX show varying effectiveness by geographic scale disease forecasting, but the application lacks direct relevance to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R122" t="b">
+          <t>While the paper demonstrates LSTM's superiority at county level and SARIMAX at national level, its health-domain application offers only weak transferability to actuarial claims reserving without adaptation.</t>
+        </is>
+      </c>
+      <c r="Q122" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10252,15 +10127,17 @@
       <c r="N123" t="b">
         <v>0</v>
       </c>
-      <c r="O123" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>Regret-optimal filters balance robustness and performance by minimizing worst-case deviation from an ideal non-causal estimator but lack direct application to actuarial reserving problems.</t>
-        </is>
-      </c>
-      <c r="R123" t="b">
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>The paper introduces regret-optimal filtering for signal estimation, positioning it between Kalman and H∞ filters, but does not connect to claims reserving, loss triangles, or actuarial forecasting.</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Regret-optimal filters offer a middle ground between average-case and worst-case performance but lack any application or transferability to actuarial reserving problems.</t>
+        </is>
+      </c>
+      <c r="Q123" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10324,20 +10201,22 @@
         </is>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N124" t="b">
         <v>0</v>
       </c>
-      <c r="O124" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>The parsimonious convolution quadrature method reduces computational cost to O(√N log N) or O(log² N) evaluations for certain operators, but has no direct relevance to actuarial claims reserving or loss modelling.</t>
-        </is>
-      </c>
-      <c r="R124" t="b">
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>The paper introduces a computational method for accelerating convolution quadrature in Laplace-domain operator approximations, primarily targeting wave scattering problems in physics and engineering.</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>This method reduces computational cost for time-domain simulations in physical systems but has no direct or transferable application to actuarial claims reserving or loss modelling.</t>
+        </is>
+      </c>
+      <c r="Q124" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10406,20 +10285,17 @@
       <c r="N125" t="b">
         <v>1</v>
       </c>
-      <c r="O125" t="b">
-        <v>1</v>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>This paper extends the log-normal chain-ladder model with asymptotic theory for distribution forecasting, offering improved uncertainty quantification and calibration compared to traditional methods like bootstrap or over-dispersed Poisson.</t>
+        </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> paperotic theory for forecasting distributions in the-normal chain-ladder model, addressing convolution challenges and estimation error, with results yielding t-distributed forecasts and validated via simulations and empirical data.</t>
-        </is>
-      </c>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>The generalized log-normal chain-ladder provides analytically tractable, uncertainty-aware reserve forecasts that differ from traditional Poisson or bootstrap methods, offering a theoretically grounded alternative for aggregate triangle reserving.</t>
-        </is>
-      </c>
-      <c r="R125" t="b">
+          <t>The generalized log-normal chain-ladder model produces t-distributed forecast distributions under small σ asymptotics, providing a theoretically grounded alternative for reserve uncertainty estimation in aggregate triangle reserving.</t>
+        </is>
+      </c>
+      <c r="Q125" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10488,15 +10364,17 @@
       <c r="N126" t="b">
         <v>0</v>
       </c>
-      <c r="O126" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>The band structures of edge magnetoplasmon crystals are determined by ch propagation and localized standing wave modes, with geometric deformations acting as gauge shifts rather than altering the band structure.</t>
-        </is>
-      </c>
-      <c r="R126" t="b">
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>This paper explores the band structures of edge magnetoplasmon crystals in condensed matter physics, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>The research is entirely unrelated to claims reserving, machine learning applications in actuarial science, or any practical insurance context.</t>
+        </is>
+      </c>
+      <c r="Q126" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10565,20 +10443,17 @@
       <c r="N127" t="b">
         <v>1</v>
       </c>
-      <c r="O127" t="b">
-        <v>1</v>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>This paper introduces a unified statistical framework for claim reserving based on population sampling theory, bridging macro- and micro-level approaches while addressing sampling bias in partially observed claims data.</t>
+        </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>The paper introduces a unified statistical framework for claimerving based on population sampling theory, reconciling macro- and micro-level approaches via augmented inverse probability weighting, while addressing sampling bias in partially observed claims data using double-robust estimators and synthetic data generation.</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>Claimerving can be unified under a population sampling framework that bridges aggregate and individual models while correcting for sampling bias, enhancing both flexibility and accuracy.</t>
-        </is>
-      </c>
-      <c r="R127" t="b">
+          <t>The paper's AIPW-based framework enables seamless integration of aggregate and individual claim models, offering actuaries more flexible, accurate, and statistically robust reserving tools.</t>
+        </is>
+      </c>
+      <c r="Q127" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10647,20 +10522,17 @@
       <c r="N128" t="b">
         <v>1</v>
       </c>
-      <c r="O128" t="b">
-        <v>1</v>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>This paper extends GLMs for claims reserving by allowing dynamic, multi-dimensional factor evolution and cross-line dependence, using adaptive particle filtering for estimation, validated on real insurer data.</t>
+        </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>The introduces multivariate evolutionary GLM for claims reserving that allows dynamic, two-dimensional factor evolution across accident and calendar years, incorporating cross dependencies via common shocks and using particle filtering for adaptive estimation.</t>
-        </is>
-      </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>This framework enhances traditional GLMs by enabling recursive, multi-dimensional factor adaptation and cross-line dependency modeling, offering a practical, statistically grounded approach to improve reserve accuracy in complex, real-world settings.</t>
-        </is>
-      </c>
-      <c r="R128" t="b">
+          <t>The model's recursive, adaptive estimation of evolving factors across accident and calendar years improves reserve accuracy by capturing temporal dynamics and inter-line dependencies not addressed in traditional GLMs.</t>
+        </is>
+      </c>
+      <c r="Q128" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10729,20 +10601,17 @@
       <c r="N129" t="b">
         <v>1</v>
       </c>
-      <c r="O129" t="b">
-        <v>1</v>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>SPLICE is a synthetic simulator for incurred loss estimates and claim revisions over time, designed to generate realistic individual-claim data for reserving research and model validation.</t>
+        </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>SPLICE is a synthetic simulator for individual claim incurred loss estimates and revisions over time, built on SynthETIC, enabling realistic reserving data generation with dependencies reflecting real-world case estimate behavior.</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>SPLICE fills a critical gap by generating synthetic, micro-level incurred loss data with realistic revision patterns, enabling robust testing and benchmarking of reserving models without relying on scarce or sensitive real data.</t>
-        </is>
-      </c>
-      <c r="R129" t="b">
+          <t>SPLICE fills a critical gap by simulating case estimate dynamics and their dependencies on payments and ultimate claim size, enabling robust testing of micro-level reserving models.</t>
+        </is>
+      </c>
+      <c r="Q129" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10811,20 +10680,17 @@
       <c r="N130" t="b">
         <v>1</v>
       </c>
-      <c r="O130" t="b">
-        <v>1</v>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>The paper introduces discrete-time Cox models with Dirichlet-driven reporting delays to improve IBNR claim count estimation, offering a flexible micro-level framework validated on auto-insurance data.</t>
+        </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>The paper introduces discrete-time Cox models with Dirichlet-driven reporting delays to improve IBNR claim count estimation, showing superior performance over continuous-time versions on auto-insurance data.</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>Discretized Cox models incorporating Dirichlet-distributed reporting delays offer a practical, flexible framework for more accurate IBNR reserving by jointly modeling delay and frequency at the micro level.</t>
-        </is>
-      </c>
-      <c r="R130" t="b">
+          <t>Discrete-time Cox models incorporating Dirichlet-distributed reporting delays outperform continuous-time versions by jointly modeling delay and frequency, enhancing IBNR reserving accuracy.</t>
+        </is>
+      </c>
+      <c r="Q130" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10888,25 +10754,22 @@
         </is>
       </c>
       <c r="M131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
       </c>
-      <c r="O131" t="b">
-        <v>1</v>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>The paper extends Dynamic Financial Analysis to incorporate climate change impacts on general insurers' assets and liabilities, using stochastic simulations and Australian data to benchmark against traditional DFA.</t>
+        </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>The paper extends Dynamic Financial Analysis (DFA) to incorporate change risks for general insurers, using stochastic simulations and Australian data to show how physical and climate impacts alter long-term financial projections compared to traditional stationary DFA.</t>
-        </is>
-      </c>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>Climate-dependent DFA reveals that the interaction between economic growth and physical risk significantly reshapes insurers’ risk-return profiles under climate, but the framework is not focused on claims reserving or loss prediction.</t>
-        </is>
-      </c>
-      <c r="R131" t="b">
+          <t>Climate-dependent DFA reveals that physical and economic risk interactions significantly alter insurers' long-term risk-return profiles, but the framework is not directly applicable to claims reserving or loss development modeling.</t>
+        </is>
+      </c>
+      <c r="Q131" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10975,20 +10838,17 @@
       <c r="N132" t="b">
         <v>0</v>
       </c>
-      <c r="O132" t="b">
-        <v>1</v>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>This paper studies nonlocal variational problems and ground states for the Choquard equation, with no connection to actuarial reserving, claims development, or insurance loss modeling.</t>
+        </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>The paper investigates nonnegativeizers of aagliardo-Nirenberg-type inequality involving nonlocal Riesz, with applications to the Thomas-Fermi for Choquard equations, and characterizes maximizer properties across parameter regimes.</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>This work advances mathematical analysis of nonlocal variational problems and Choquard equations but has no practical relevance to actuarial claims reserving or machine learning in reserving.</t>
-        </is>
-      </c>
-      <c r="R132" t="b">
+          <t>The work is purely mathematical and theoretical, focused on PDEs and functional inequalities, offering no practical value for claims reserving or actuarial machine learning applications.</t>
+        </is>
+      </c>
+      <c r="Q132" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11057,20 +10917,17 @@
       <c r="N133" t="b">
         <v>0</v>
       </c>
-      <c r="O133" t="b">
-        <v>1</v>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>This paper analyzes the near-infrared transit spectrum of exoplanet HAT-P-32b using Hubble Space Telescope data, focusing on atmospheric composition and retrieval methods.</t>
+        </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>This paper analyzes the near-in of exoplan HAT-P-32b using Hubble Space Telescope data, comparing parametric and non-parametric methods to infer atmospheric composition, including water vapor and clouds.</t>
-        </is>
-      </c>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>The study finds evidence of water vapor and cloud in HAT-P-32b’s atmosphere but offers no relevance to actuarial claims reserving or machine learning applications in insurance.</t>
-        </is>
-      </c>
-      <c r="R133" t="b">
+          <t>The study provides no relevance to actuarial claims reserving, as it is entirely focused on exoplanetary atmospheric science with no transferable methodology or application to insurance reserving.</t>
+        </is>
+      </c>
+      <c r="Q133" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11139,15 +10996,17 @@
       <c r="N134" t="b">
         <v>1</v>
       </c>
-      <c r="O134" t="b">
-        <v>1</v>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>The paper addresses dependence modeling in loss reserving using a modified continuous generalised method of moments to estimate parameters for complex distributions where MLE is impractical, with applications to stable and Tweedie-like models.</t>
+        </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>The modeling in reserving using additive background risk models and proposes a continuous generalised method of moments (CGMM) to estimate parameters maximum likelihood is impractical, particularly for distributions like Tweedie or Stable that lack closed-form densities.</t>
-        </is>
-      </c>
-      <c r="R134" t="b">
+          <t>CGMM provides a practical non-Bayesian estimation alternative for complex dependence structures in reserving when traditional likelihood-based methods fail.</t>
+        </is>
+      </c>
+      <c r="Q134" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11216,20 +11075,17 @@
       <c r="N135" t="b">
         <v>1</v>
       </c>
-      <c r="O135" t="b">
-        <v>1</v>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>This paper presents a unified micro-level stochastic framework for modeling loss reserves, IBNR, and unearned premium risk with dependence, inflation, and discounting, implemented via an Aggregate Trend Renewal Process and validated on medical malpractice data.</t>
+        </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>This paper presents a unified micro-level stochastic framework for modeling loss reserves, IBNR, and unearned premium risk, incorporating dependence, inflation, and discounting, with practical application to long-tailed lines like medical malpractice.</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>The unified micro-model enables joint, forward-looking reserve and premium risk assessment by integrating claim dynamics, financial adjustments, and uncertainty—directly advancing actuarial practice in complex reserving environments.</t>
-        </is>
-      </c>
-      <c r="R135" t="b">
+          <t>The unified micro-model enables joint, forward-looking reserve and premium risk assessment under real-world dynamics like delay, inflation, and dependence—directly advancing practical reserving for long-tailed lines.</t>
+        </is>
+      </c>
+      <c r="Q135" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11293,21 +11149,22 @@
         </is>
       </c>
       <c r="M136" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
       </c>
-      <c r="O136" t="b">
-        <v>0</v>
-      </c>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>The paper introduces a GLM-based model that replicates chain-ladder by modeling averaged hazard rates in reverse development time, reducing parameter complexity and enabling flexible extensions, with practical implementation via the clmplus R-package.</t>
-        </is>
-      </c>
-      <c r="R136" t="b">
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>The paper introduces a GLM-based model that replicates chain-ladder by modeling averaged hazard rates in reverse development time, reducing parameter complexity and enabling flexible extensions, with an accompanying R package for practical use on run-off triangles.</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Modeling claim development via reversed-time hazard rates in a GLM framework offers a simpler, more interpretable alternative to traditional claim-amount modeling while preserving chain-ladder logic and enabling richer extensions.</t>
+        </is>
+      </c>
+      <c r="Q136" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11376,20 +11233,17 @@
       <c r="N137" t="b">
         <v>0</v>
       </c>
-      <c r="O137" t="b">
-        <v>1</v>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>This paper addresses endpoint estimates for maximal operators in the context of the wave equation, a topic in harmonic analysis with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>This estimates for maximal operators related to the wave equation in harmonic analysis, focusing on Sobolev and Lebesgue space bounds. It resolves an open problem regarding critical exponents but has no connection to actuarial reserving or insurance applications.</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>The paper proves endpoint maximal estimates for the wave operator critical Sobolev spaces, advancing pure harmonic analysis with no relevance to claims reserving or actuarial science.</t>
-        </is>
-      </c>
-      <c r="R137" t="b">
+          <t>The paper resolves open endpoint bounds for maximal operators associated with the wave equation, but offers no practical relevance to claims reserving or machine learning applications in actuarial science.</t>
+        </is>
+      </c>
+      <c r="Q137" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11458,20 +11312,17 @@
       <c r="N138" t="b">
         <v>1</v>
       </c>
-      <c r="O138" t="b">
-        <v>1</v>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>The paper models data breach frequency and IBNR estimation across U.S. states using notification laws, offering transferable methods for actuarial reserving in cyber insurance.</t>
+        </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>The paper analyzes data breach reporting patterns across U.S. states to estimate IBNR and assess frequency trends, with implications for cyber insurance reserving.</t>
-        </is>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>By controlling for state notification laws, the study reliably estimates IBNR and reveals a post-2020 increase in data breach frequency, offering transferable methods for actuarial reserving in cyber risk.</t>
-        </is>
-      </c>
-      <c r="R138" t="b">
+          <t>By controlling for reporting patterns and state-specific notification laws, the paper provides a reliable method to estimate IBNR and trend shifts in cyber risk, which is directly applicable to reserving in cyber insurance.</t>
+        </is>
+      </c>
+      <c r="Q138" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11540,20 +11391,17 @@
       <c r="N139" t="b">
         <v>1</v>
       </c>
-      <c r="O139" t="b">
-        <v>1</v>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>The paper applies the Explainable Boosting Machine (EBM) to car insurance claim frequency and severity, offering strong interpretability and performance compared to GLMs and XGBoost, with potential transferability to reserving contexts.</t>
+        </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>The introduces the Explainableing Machine (EBM) for predicting car insurance claim frequency and severity, emphasizing interpretability alongside performance, and compares it with GLM, GAM, CART, and XGBoost.</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>EBM offers a high-performing intrinsically interpretable alternative to traditional and black-box models for actuar pricing tasks, with potential transferability to reserving through its explainability and feature interaction modeling.</t>
-        </is>
-      </c>
-      <c r="R139" t="b">
+          <t>EBM provides a high-performing, intrinsically interpretable alternative to traditional actuarial models, making it a practical candidate for enhancing transparency in claim prediction tasks relevant to reserving.</t>
+        </is>
+      </c>
+      <c r="Q139" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11622,16 +11470,17 @@
       <c r="N140" t="b">
         <v>1</v>
       </c>
-      <c r="O140" t="b">
-        <v>0</v>
-      </c>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>The Dirichlet model unifies Chain-Ladder and Bornhuetter-Ferguson under a single statistical framework, automatically selecting the appropriate method based on available data, which enhances practical reserving flexibility and interpretability.</t>
-        </is>
-      </c>
-      <c r="R140" t="b">
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>The paper introduces a Dirichlet model that unifies Chain-Ladder and Bornhuetter-Ferguson methods under a single statistical framework, offering flexible inference based on available data and validated on real workers' compensation claims.</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>The Dirichlet model provides a statistically principled bridge between two classic reserving methods, enabling data-driven selection and improving interpretability and consistency in reserve forecasting.</t>
+        </is>
+      </c>
+      <c r="Q140" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11661,7 +11510,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>$κ$-Explorer: A Unified Framework for Active Model Estimation in MDPs</t>
+          <t>κ-Explorer: A Unified Framework for Active Model Estimation in MDPs</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -11700,15 +11549,17 @@
       <c r="N141" t="b">
         <v>0</v>
       </c>
-      <c r="O141" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>κ-Explorer improves model estimation in MDPs by adaptively prioritizing underexplored, high-variance transitions through a curvature-parameterized objective function, but has no direct application to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R141" t="b">
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>The paper introduces κ-Explorer, an active exploration algorithm for Markov decision processes that optimizes state-action visitation based on estimation complexity, with applications in reinforcement learning but no direct link to claims reserving.</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>κ-Explorer improves model estimation in MDPs by prioritizing high-variance, underexplored transitions, but offers no practical value or transferability to actuarial reserving problems.</t>
+        </is>
+      </c>
+      <c r="Q141" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11777,20 +11628,17 @@
       <c r="N142" t="b">
         <v>0</v>
       </c>
-      <c r="O142" t="b">
-        <v>1</v>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>The paper evaluates gradient boosting methods for zero-inflated claim frequency modeling, proposing a new zero-inflated Poisson boosted tree model and finding CatBoost performs best on telematics data.</t>
+        </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>The paper evaluates CatBoostGBoost, andGBM for zero-inflated insurance claim frequency modeling, proposing a new zero-inflated Poisson boosted tree model that leverages CatBoost’s feature interaction tools, particularly with telematics data.</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>CatBoost outperforms other gradient boosters for zero-inflated auto claim frequency modeling, especially when combined with a custom zero-inflated Poisson structure that exploits its interpretability tools.</t>
-        </is>
-      </c>
-      <c r="R142" t="b">
+          <t>CatBoost-based zero-inflated Poisson models offer improved predictive performance for auto claim frequency, particularly with telematics data, though the focus is on frequency rather than reserving or severity.</t>
+        </is>
+      </c>
+      <c r="Q142" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11859,15 +11707,17 @@
       <c r="N143" t="b">
         <v>0</v>
       </c>
-      <c r="O143" t="b">
-        <v>1</v>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>The paper introduces a sieve MLE estimator for semiparametric multivariate models with known marginals, showing improved efficiency and robustness over QMLE and misspecified full MLE, with an insurance application involving censored claim loss data.</t>
+        </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>The paper introduces sieve MLE estimator for semiparam multivariate models with known marginals, improving efficiency over QMLE while avoiding thepecification risks of full MLE; it demonstrates practical value in insurance by building a flexible claim loss model with censored variables.</t>
-        </is>
-      </c>
-      <c r="R143" t="b">
+          <t>The sieve MLE estimator offers a practical, robust alternative for parameter estimation in multivariate insurance models with censored variables, improving precision without requiring full copula specification.</t>
+        </is>
+      </c>
+      <c r="Q143" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11936,20 +11786,17 @@
       <c r="N144" t="b">
         <v>1</v>
       </c>
-      <c r="O144" t="b">
-        <v>1</v>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>This paper introduces a sparse SUR copula mixed model for multivariate loss reserving that improves reserve accuracy and risk diversification while preserving interpretability of dependencies across lines of business and companies.</t>
+        </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>The a Sparse Seingly Unrelated Regression (SSUR) copula mixed model for multivariate loss reserving that improves reserve accuracy and divers while preserving interpretability through shrinkage and random effects, validated on real insurance data.</t>
-        </is>
-      </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>The SSUR copula mixed model enhances multivariate reserving by combining interpretability, dependence modeling, and robustness via LASSO shrinkage and random effects, outperforming prior SUR models in predictive accuracy and capital efficiency.</t>
-        </is>
-      </c>
-      <c r="R144" t="b">
+          <t>The model combines random effects, LASSO shrinkage, and copula-based dependence to deliver interpretable, robust, and accurate multivariate reserve estimates with quantified risk capital benefits.</t>
+        </is>
+      </c>
+      <c r="Q144" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12018,20 +11865,17 @@
       <c r="N145" t="b">
         <v>1</v>
       </c>
-      <c r="O145" t="b">
-        <v>1</v>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>This paper introduces a recurrent neural network (Deep Triangle) and GAN-based extension for multivariate loss reserving, capturing dependencies across lines of business and generating predictive reserve distributions with improved performance over copula models.</t>
+        </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>The paper introduces the Extended Deep Triangle (EDT), a recurrent neural network combined with GANs, to model multivariate loss reserving and risk capital by capturing dependencies across lines of business, outperforming copula regression models on real and simulated data.</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>EDT leverages RNNs and GANs to jointly model multivariate reserve dependencies and generate predictive distributions, yielding more accurate reserves and revealing greater diversification benefits than traditional copula methods.</t>
-        </is>
-      </c>
-      <c r="R145" t="b">
+          <t>The extended Deep Triangle framework outperforms traditional copula regression in predicting total loss reserves and reveals greater diversification benefits through more accurate risk capital estimates.</t>
+        </is>
+      </c>
+      <c r="Q145" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12100,16 +11944,17 @@
       <c r="N146" t="b">
         <v>1</v>
       </c>
-      <c r="O146" t="b">
-        <v>0</v>
-      </c>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>The paper introduces a hierarchical generalized linear model for loss reserving with a bootstrap-based error estimator, offering practical uncertainty quantification and reproducible R code for actuarial implementation.</t>
-        </is>
-      </c>
-      <c r="R146" t="b">
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>This paper applies hierarchical generalized linear models to loss reserving and introduces a bootstrap estimator for prediction error, with full R code provided for reproducibility.</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>The bootstrap-based error estimation offers a practical, interpretable way to quantify reserve uncertainty in HGLMs, directly addressing actuarial needs for robust prediction intervals.</t>
+        </is>
+      </c>
+      <c r="Q146" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12178,20 +12023,17 @@
       <c r="N147" t="b">
         <v>1</v>
       </c>
-      <c r="O147" t="b">
-        <v>1</v>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>This paper applies LSTM networks to micro-level reserving by modeling individual claim payments and recoveries over time, with adjustments for extreme values, and benchmarks against chain-ladder on real and simulated data.</t>
+        </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>The paper introduces an LSTM-based micro-level reserving framework that uses individual claim data to predict payments and recoveries, outperforming chain-ladder on real and simulated datasets while adjusting for extreme values via a generalized Pareto model.</t>
-        </is>
-      </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>LSTM networks can effectively model individual claim development dynamics and improve reserve accuracy by leveraging granular data and tail adjustments.</t>
-        </is>
-      </c>
-      <c r="R147" t="b">
+          <t>LSTM networks can effectively model granular claim dynamics at the individual level, offering a practical, data-driven alternative to aggregate triangle methods while explicitly handling tail risk.</t>
+        </is>
+      </c>
+      <c r="Q147" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12260,20 +12102,17 @@
       <c r="N148" t="b">
         <v>0</v>
       </c>
-      <c r="O148" t="b">
-        <v>1</v>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>The paper explores pricing rules under partial information in jump-diffusion models, focusing on contingent claims and labor income streams, with no direct application to actuarial reserving or claim development.</t>
+        </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>The paper explores pricing rules for income streams or contingent liabilities under varying levels of insider information about asset jumps, quantifying the value of partial information in financial contexts.</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>The value of partial information about jump sizes can be explicitly quantified in pricing models, but this has minimal direct relevance to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R148" t="b">
+          <t>Partial information about jumps alters pricing for contingent liabilities, but the framework lacks connection to claims reserving, IBNR/RBNS estimation, or practical actuarial modeling.</t>
+        </is>
+      </c>
+      <c r="Q148" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12337,25 +12176,22 @@
         </is>
       </c>
       <c r="M149" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
       </c>
-      <c r="O149" t="b">
-        <v>1</v>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>The paper extends XGBoost to support non-convex and multivariate loss functions, with examples in non-life insurance pricing, offering potential transferability to reserving if adapted to claim development or uncertainty modeling.</t>
+        </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>The paper extends XGBoost to support non-convex and multivariate loss functions, enabling modeling of multiple distribution parameters, with examples in non-life insurance pricing.</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>Generalized XGBoost allows flexible loss functions and multi-parameter modeling, but its focus on pricing limits direct relevance to claims reserving.</t>
-        </is>
-      </c>
-      <c r="R149" t="b">
+          <t>Generalized XGBoost enables flexible, multi-parameter modeling of probability distributions using tree boosting, which could be repurposed for actuarial reserving tasks like IBNR estimation or probabilistic forecasting.</t>
+        </is>
+      </c>
+      <c r="Q149" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12424,20 +12260,17 @@
       <c r="N150" t="b">
         <v>1</v>
       </c>
-      <c r="O150" t="b">
-        <v>1</v>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>This paper evaluates neural network architectures for individual loss reserving using payment and case estimate data, finding that case estimates significantly improve predictions while recurrent structures offer only marginal gains.</t>
+        </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>This paper evaluates neural network architectures for individual loss reserving using payment and case estimate data, finding that case estimates significantly improve predictions while recurrent structures offer only marginal gains.</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>Case estimates substantially enhance predictive accuracy in neural network reserving models, whereas adding memory via RNNs yields only minor improvements despite handling full claim histories.</t>
-        </is>
-      </c>
-      <c r="R150" t="b">
+          <t>Case estimates provide substantial predictive value in individual reserving models, whereas adding memory via RNNs yields minimal improvement over feed-forward networks.</t>
+        </is>
+      </c>
+      <c r="Q150" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12506,20 +12339,17 @@
       <c r="N151" t="b">
         <v>0</v>
       </c>
-      <c r="O151" t="b">
-        <v>1</v>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>This paper investigates the disconnect between image synthesis quality and depth estimation accuracy in self-supervised learning, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>The paper investigates how optimizing image synthesis loss in self-supervised depth estimation does not necessarily improve depth prediction accuracy, due to aleatoric uncertainty, and finds this issue persists across datasets and architectures.</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>Optimizing for image synthesis in self-supervised depth estimation can degrade depth prediction performance due to inherent data uncertainties, regardless of dataset or model architecture.</t>
-        </is>
-      </c>
-      <c r="R151" t="b">
+          <t>Optimizing for image synthesis does not improve depth estimation and may even degrade it due to aleatoric uncertainty, a finding irrelevant to claims reserving.</t>
+        </is>
+      </c>
+      <c r="Q151" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12588,20 +12418,17 @@
       <c r="N152" t="b">
         <v>0</v>
       </c>
-      <c r="O152" t="b">
-        <v>1</v>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>This paper models user-click behavior to predict insurance purchase intent using neural networks, but it focuses on marketing and underwriting rather than claims reserving or loss development.</t>
+        </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>This paper models user-click behavior to predict purchase intent for non-life insurance products using feed-forward and recurrent neural networks, showing click-based features outperform demographic ones.</t>
-        </is>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>User navigation patterns on websites can predict purchase intent better than demographic data, but this has minimal direct relevance to claims reserving or loss forecasting.</t>
-        </is>
-      </c>
-      <c r="R152" t="b">
+          <t>User-click patterns can predict purchase intent better than demographic data, but this has minimal direct relevance to actuarial reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q152" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12670,20 +12497,17 @@
       <c r="N153" t="b">
         <v>0</v>
       </c>
-      <c r="O153" t="b">
-        <v>1</v>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>This paper focuses on multi-UAV collision avoidance using control barrier functions and has no connection to actuarial claims reserving or loss modelling.</t>
+        </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>The paper introduces a feasibility-enhanced control barrier function method to improve collision avoidance in dense multi-UAV environments by addressing constraint incompatibility through sign-consistency and slack variables, validated via simulations and real-world tests.</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>This work advances UAV collision avoidance but has no practical relevance to actuarial claims reserving or loss modelling.</t>
-        </is>
-      </c>
-      <c r="R153" t="b">
+          <t>The research addresses technical feasibility in UAV control systems and offers no practical value for general insurance reserving or actuarial machine learning applications.</t>
+        </is>
+      </c>
+      <c r="Q153" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12747,25 +12571,22 @@
         </is>
       </c>
       <c r="M154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
       </c>
-      <c r="O154" t="b">
-        <v>1</v>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>The paper addresses incentive design in randomized controlled trials, focusing on balancing exploration and exploitation for participant engagement, with no connection to claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>The paper addresses incentivizing participation in randomized controlled trials by modeling the tradeoff between exploration and exploitation, using information asymmetry to design incentive-compatible mechanisms with worst-case performance guarantees.</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>The paper proposes incentive mechanisms for RCTs that balance exploration and agent preferences, but has no practical relevance to actuarial claims reserving or loss modelling.</t>
-        </is>
-      </c>
-      <c r="R154" t="b">
+          <t>The paper proposes an incentive-compatible mechanism for RCTs that minimizes worst-case estimation error under adversarial outcomes, but offers no relevance to insurance reserving or actuarial modeling.</t>
+        </is>
+      </c>
+      <c r="Q154" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12834,20 +12655,17 @@
       <c r="N155" t="b">
         <v>0</v>
       </c>
-      <c r="O155" t="b">
-        <v>1</v>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>The paper introduces a Dynamic Poisson State Space model for updating claim frequency predictions over time using smoothing splines, applied to Chinese auto insurance data with improved accuracy over existing methods.</t>
+        </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>The paper introduces a Dynamic Poisson State Space model for updating claim frequency predictions over time using smoothing splines and batch updates, showing improved accuracy on Chinese auto insurance data.</t>
-        </is>
-      </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>The DPSS model enables continuous parameter updates for claim frequency prediction with smooth time-varying coefficients, offering better accuracy than static models but not directly addressing reserving or reserve uncertainty.</t>
-        </is>
-      </c>
-      <c r="R155" t="b">
+          <t>While the model offers dynamic updating and improved prediction for claim frequency, its focus on pricing-related frequency modeling rather than reserving or loss development limits its direct practical value to the IFoA reserving working party.</t>
+        </is>
+      </c>
+      <c r="Q155" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12916,20 +12734,17 @@
       <c r="N156" t="b">
         <v>1</v>
       </c>
-      <c r="O156" t="b">
-        <v>1</v>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>The paper addresses model error in loss reserving using Bayesian model averaging and LASSO-based methods, offering a practical framework to quantify uncertainty beyond traditional parameter and process errors.</t>
+        </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>The paper addresses model error in loss reserving, decomposing it into estimable (internal) and non-estimable (external) components, and proposes Bayesian model averaging with LASSO-based priors to estimate internal model error and parameter error jointly, illustrated with insurance data.</t>
-        </is>
-      </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>Model error in reserving can be estimated via Bayesian model averaging using LASSO priors, though parameter and model errors are inherently entangled and may not be meaningfully separated.</t>
-        </is>
-      </c>
-      <c r="R156" t="b">
+          <t>Internal model error can be estimated via Bayesian model averaging with bootstrapped LASSO, providing a more complete picture of reserve uncertainty that is directly applicable to actuarial practice.</t>
+        </is>
+      </c>
+      <c r="Q156" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12998,20 +12813,17 @@
       <c r="N157" t="b">
         <v>1</v>
       </c>
-      <c r="O157" t="b">
-        <v>1</v>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>This paper applies Mixture Density Networks to loss reserving, delivering both accurate central estimates and flexible quantile forecasts, with extensions for hybrid GLM integration and actuarial judgment constraints.</t>
+        </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>The paper applies Mixture Density Networks (MDNs) to loss reserving, enabling accurate central estimates and flexible quantile forecasting, and introduces a hybrid GLM-MDN model (ResMDN) that balances interpretability with performance, validated on both simulated and real aggregate loss triangles.</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>MDNs and their hybrid extension ResMDN outperform classical models in both point and distributional forecasts for aggregate loss reserving, while allowing actuarial judgment to be embedded via projection constraints.</t>
-        </is>
-      </c>
-      <c r="R157" t="b">
+          <t>MDNs provide a practical, distributionally rich framework for aggregate triangle reserving that outperforms classical models while allowing for actuarial input and interpretability.</t>
+        </is>
+      </c>
+      <c r="Q157" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13080,20 +12892,17 @@
       <c r="N158" t="b">
         <v>0</v>
       </c>
-      <c r="O158" t="b">
-        <v>1</v>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>The paper introduces JADE, a dynamic evaluation framework for agentic AI in professional tasks, using expert-grounded criteria and claim-level assessment, but it is not focused on claims reserving or actuarial applications.</t>
+        </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>JADE is a two-layer evaluation framework for agentic AI that combines expert-grounded criteria with dynamic, claim-level assessment to improve stability and uncover failure modes in open-ended professional tasks.</t>
-        </is>
-      </c>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>JADE improves AI evaluation reliability by grounding assessments in expert knowledge while dynamically adapting to diverse reasoning strategies at the claim level.</t>
-        </is>
-      </c>
-      <c r="R158" t="b">
+          <t>JADE improves evaluation stability for open-ended professional tasks by combining predefined expert skills with flexible, evidence-gated claim-level analysis, though it lacks direct relevance to actuarial reserving.</t>
+        </is>
+      </c>
+      <c r="Q158" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13162,20 +12971,17 @@
       <c r="N159" t="b">
         <v>0</v>
       </c>
-      <c r="O159" t="b">
-        <v>1</v>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>This paper introduces Bayesian NMF methods with correlated mutation type probabilities for cancer mutational signature analysis, which is unrelated to actuarial claims reserving.</t>
+        </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>This paper extends Bayesian Non-Negative Matrix Factorization to model dependencies between mutation types in cancer genomics, using multivariate priors and hierarchical structures for improved accuracy and biological insight.</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>The paper introduces dependency-aware Bayesian NMF for mutational signature analysis in cancer research, with no direct relevance to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R159" t="b">
+          <t>The paper advances cancer genomics by modeling dependencies in mutation signatures but offers no practical value or transferability to general insurance reserving.</t>
+        </is>
+      </c>
+      <c r="Q159" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13205,7 +13011,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Privacy-Enhancing Collaborative Information Sharing through Federated Learning -- A Case of the Insurance Industry</t>
+          <t>Privacy-Enhancing Collaborative Information Sharing through Federated Learning - A Case of the Insurance Industry</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -13244,20 +13050,17 @@
       <c r="N160" t="b">
         <v>0</v>
       </c>
-      <c r="O160" t="b">
-        <v>1</v>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>The paper explores federated learning for collaborative claims loss modeling across insurers without sharing raw data, addressing data scarcity and privacy concerns.</t>
+        </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>The paper explores Federated Learning (FL) to improve claims loss modeling by enabling collaborative model training across insurers without sharing raw data, addressing data scarcity and privacy concerns.</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>Federated Learning allows insurers to collaboratively train more effective claims loss models while preserving data privacy, though its direct applicability to core reserving tasks remains indirect.</t>
-        </is>
-      </c>
-      <c r="R160" t="b">
+          <t>Federated learning enables improved claims loss forecasting by aggregating insights from multiple insurers' private datasets while preserving data privacy.</t>
+        </is>
+      </c>
+      <c r="Q160" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13326,20 +13129,17 @@
       <c r="N161" t="b">
         <v>0</v>
       </c>
-      <c r="O161" t="b">
-        <v>1</v>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>The paper introduces a latent Markovian model for joint frequency-severity experience rating in auto insurance, focusing on dynamic risk profiling rather than reserving.</t>
+        </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>The paper introduces a latent Markovian model to jointly model frequency and severity in experience rating, allowing for dynamic risk profiles that evolve with claims history, applied to auto insurance data.</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>The model improves customer risk differentiation by capturing time-varying frequency-severity dependence through latent Markov states, but is not directly applicable to claims reserving.</t>
-        </is>
-      </c>
-      <c r="R161" t="b">
+          <t>While innovative for pricing and segmentation, the paper's focus on premium calculation via latent risk profiles offers limited direct value to claims reserving or reserve uncertainty quantification.</t>
+        </is>
+      </c>
+      <c r="Q161" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13408,20 +13208,17 @@
       <c r="N162" t="b">
         <v>0</v>
       </c>
-      <c r="O162" t="b">
-        <v>1</v>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>The paper explores a modified Bonus-Malus System that incorporates multi-year claim history and frequency-severity dependence, primarily for premium rating rather than claims reserving.</t>
+        </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>The paper revisits a modified Bonus-Malus System that incorporates multi-year claim-free history to refine premium adjustments, using statistical models and real data to compare it with classical BMS.</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>The paper enhances premium rating fairness in auto insurance by extending Bonus-Malus levels based on consecutive claim-free years, but does not address claims reserving or loss prediction.</t>
-        </is>
-      </c>
-      <c r="R162" t="b">
+          <t>While methodologically interesting, the paper focuses on pricing and risk classification, not on estimating future claims reserves or modelling claim development patterns relevant to actuarial reserving.</t>
+        </is>
+      </c>
+      <c r="Q162" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13451,7 +13248,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Error analysis for 2D stochastic Navier--Stokes equations in bounded domains with Dirichlet data</t>
+          <t>Error analysis for 2D stochastic Navier-Stokes equations in bounded domains with Dirichlet data</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -13490,20 +13287,17 @@
       <c r="N163" t="b">
         <v>0</v>
       </c>
-      <c r="O163" t="b">
-        <v>1</v>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>This paper focuses on numerical analysis of stochastic Navier-Stokes equations in fluid dynamics, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>The paper presents a finite-element space-time discretisation method for 2D stochastic Navier-Stokes equations with Dirichlet boundary conditions, proving optimal convergence rates by introducing discrete stopping times to overcome limitations in energy estimates.</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>The paper advances numerical analysis for stochastic fluid dynamics but has no practical relevance to actuarial claims reserving or loss modelling.</t>
-        </is>
-      </c>
-      <c r="R163" t="b">
+          <t>The work advances finite-element discretisation for stochastic PDEs in bounded domains but offers no practical relevance to claims reserving or general insurance actuarial practice.</t>
+        </is>
+      </c>
+      <c r="Q163" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13572,20 +13366,17 @@
       <c r="N164" t="b">
         <v>0</v>
       </c>
-      <c r="O164" t="b">
-        <v>1</v>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>This paper presents a numerical method for solving tensor Sylvester equations with specific matrix structures, focusing on computational efficiency and theoretical error bounds.</t>
+        </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>The paper presents a nested divide-and-conquer algorithm for solving tensor Sylvester equations with hierarchically semiseparable coefficients, achieving quasi-optimal computational cost and validated on 2D/3D cases.</t>
-        </is>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>This work advances numerical methods for structured linear systems but has no direct or transferable relevance to actuarial claims reserving or loss modelling.</t>
-        </is>
-      </c>
-      <c r="R164" t="b">
+          <t>The proposed nested divide-and-conquer algorithm achieves quasi-optimal complexity for solving structured tensor linear systems but has no direct or transferable application to actuarial claims reserving.</t>
+        </is>
+      </c>
+      <c r="Q164" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13654,20 +13445,17 @@
       <c r="N165" t="b">
         <v>0</v>
       </c>
-      <c r="O165" t="b">
-        <v>1</v>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>This paper explores ruin probability under neutral net profit conditions in classical and generalized renewal risk models, focusing on theoretical guarantees of ruin rather than claims reserving or loss forecasting.</t>
+        </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>The paper examines ruin probability in renewal risk models under a neutral net profit condition, showing that ruin is unavoidable when claims and premiums balance on average, across discrete-time, Cramér-Lundberg, and Sparre Andersen models.</t>
-        </is>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>Ruin is guaranteed in renewal risk models when the net profit condition is neutral, even without degenerate claim or premium distributions.</t>
-        </is>
-      </c>
-      <c r="R165" t="b">
+          <t>The paper proves that ruin is inevitable under a neutral net profit condition in certain renewal risk models, but offers no practical tools or insights for actuarial reserving or probabilistic reserve estimation.</t>
+        </is>
+      </c>
+      <c r="Q165" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13736,20 +13524,17 @@
       <c r="N166" t="b">
         <v>1</v>
       </c>
-      <c r="O166" t="b">
-        <v>1</v>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>This paper introduces negative binomial models for predicting outstanding claim counts in development triangles, explicitly addressing overdispersion and dependence across development years with Bayesian inference.</t>
+        </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>The paper introduces negative binomial models for predicting outstanding claims in development triangles, addressing overdispersion and extending to account for dependence across development years, with Bayesian inference and validation on real and simulated data.</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>Negative binomial models offer a flexible, parametric approach to modeling claim counts in reserving triangles, particularly useful for handling overdispersion and temporal dependence while supporting Bayesian inference.</t>
-        </is>
-      </c>
-      <c r="R166" t="b">
+          <t>Negative binomial models offer a flexible, parametric alternative to chain ladder and overdispersed Poisson for modeling claim counts in triangles, with explicit handling of overdispersion and temporal dependence.</t>
+        </is>
+      </c>
+      <c r="Q166" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13818,20 +13603,17 @@
       <c r="N167" t="b">
         <v>1</v>
       </c>
-      <c r="O167" t="b">
-        <v>1</v>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>The paper extends Schnieper's IBNR/IBNER decomposition with a continuous-time stochastic model and bootstrap method for reserve uncertainty, offering a practical, distributional approach aligned with actuarial reserving principles.</t>
+        </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>The paper extends Schnieper’s IBNR/IBNER decomposition with a continuous-time stochastic model using Poisson processes and Brownian motion, and introduces a bootstrap method to estimate reserve predictive distributions while preserving non-negativity and asymmetry.</t>
-        </is>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>A continuous-time stochastic framework with bootstrap inference improves the realism and uncertainty quantification of Schnieper-style reserving by naturally enforcing actuarial constraints without ad hoc assumptions.</t>
-        </is>
-      </c>
-      <c r="R167" t="b">
+          <t>A continuous-time framework with Poisson and Brownian drivers enables realistic, non-negative, asymmetric reserve distributions without ad hoc assumptions, directly enhancing Schnieper-based reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q167" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13900,20 +13682,17 @@
       <c r="N168" t="b">
         <v>0</v>
       </c>
-      <c r="O168" t="b">
-        <v>1</v>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>This paper focuses on locally private algorithms for frequency estimation and heavy hitters identification, with no connection to claims reserving, loss development, or actuarial modeling.</t>
+        </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>The paper introduces two new locally differentially private algorithms for frequency estimation and heavy hitters identification, improving on prior work in error bounds and efficiency.</t>
-        </is>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>The proposed algorithms achieve asymptotically optimal error bounds for local differential privacy in frequency estimation and heavy hitters problems, with efficient user and server computation.</t>
-        </is>
-      </c>
-      <c r="R168" t="b">
+          <t>The paper advances differential privacy techniques for frequency estimation but offers no practical value or transferability to actuarial reserving research or practice.</t>
+        </is>
+      </c>
+      <c r="Q168" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13982,20 +13761,17 @@
       <c r="N169" t="b">
         <v>0</v>
       </c>
-      <c r="O169" t="b">
-        <v>1</v>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>This paper presents a quantum Monte Carlo method for calculating excited-state energies in molecular systems, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>The paper introduces a quantum Monte Carlo method for computing excited-state energies in large molecular systems, achieving high accuracy without dot products of random vectors, and validates it on several complex chemical systems.</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>This quantum chemistry method has no practical relevance to actuarial claims reserving or machine learning applications in insurance.</t>
-        </is>
-      </c>
-      <c r="R169" t="b">
+          <t>The method improves accuracy in quantum chemistry simulations but offers no practical value for claims reserving or general insurance actuarial research.</t>
+        </is>
+      </c>
+      <c r="Q169" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14064,20 +13840,17 @@
       <c r="N170" t="b">
         <v>1</v>
       </c>
-      <c r="O170" t="b">
-        <v>1</v>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>This paper reinterprets the chain-ladder method to enable direct projection of latest claims to ultimate, creating a bridge to individual-claim reserving with neural networks.</t>
+        </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>The paper restructures the chain-ladder method to project latest claims directly to ultimate values, enabling machine learning applications at the individual claim level, demonstrated via a neural network proof of concept.</t>
-        </is>
-      </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>Reframing chain-ladder as a direct projection from latest to ultimate claims unlocks practical ML integration for individual-claim reserving.</t>
-        </is>
-      </c>
-      <c r="R170" t="b">
+          <t>Reframing chain-ladder as multi-period direct projection unlocks practical machine learning applications for individual claim reserving while preserving actuarial interpretability.</t>
+        </is>
+      </c>
+      <c r="Q170" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14146,20 +13919,17 @@
       <c r="N171" t="b">
         <v>0</v>
       </c>
-      <c r="O171" t="b">
-        <v>1</v>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>This paper introduces a fact-checking benchmark for COVID-19 news claims using scientific evidence, with no connection to actuarial reserving or insurance claim development.</t>
+        </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>The paper introduces Check-COVID, a benchmark for fact-checking COVID-19 news claims using scientific evidence, highlighting challenges in aligning informal news text with formal academic sources.</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>This research focuses on fact-checking news claims against scientific literature and has no practical relevance to actuarial claims reserving or loss reserving.</t>
-        </is>
-      </c>
-      <c r="R171" t="b">
+          <t>The research focuses on natural language processing for fact-checking in public health and has no practical relevance to claims reserving or general insurance actuarial practice.</t>
+        </is>
+      </c>
+      <c r="Q171" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14228,20 +13998,17 @@
       <c r="N172" t="b">
         <v>0</v>
       </c>
-      <c r="O172" t="b">
-        <v>1</v>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>This paper studies theoretical convergence and boundedness properties of multi-agent learning dynamics in drone swarms, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>The paper analyzes bounded learning dynamics in tri-hierarchical drone swarms, focusing on stability and error bounds across three learning timescales, with no connection to actuarial reserving or insurance claims modeling.</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>The paper establishes theoretical guarantees for bounded error and non-accumulation in multi-timescale AI learning systems for drone swarms, but offers no relevance to claims reserving or actuarial practice.</t>
-        </is>
-      </c>
-      <c r="R172" t="b">
+          <t>The paper provides formal guarantees for stability in tri-hierarchical AI learning systems but offers no practical relevance to claims reserving, loss modeling, or actuarial applications.</t>
+        </is>
+      </c>
+      <c r="Q172" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14310,20 +14077,17 @@
       <c r="N173" t="b">
         <v>1</v>
       </c>
-      <c r="O173" t="b">
-        <v>1</v>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>This paper frames individual claims reserving as a reinforcement learning problem, enabling sequential updates to reserve estimates using all claim trajectories—including open claims—and introduces actuarial-friendly components like rolling-settlement tuning and importance weighting for large claims.</t>
+        </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>The paper frames individual claims reserving as a Markov decision process using reinforcement learning, enabling sequential updates of liability estimates and learning from open claims to avoid selection bias. It introduces actuarial-friendly components like rolling-settlement tuning and importance weighting, achieving strong performance on synthetic datasets, especially for immature claims.</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>Reinforcement learning enables dynamic, claim-level reserve updates using all claim trajectories—including open claims—improving accuracy and stability while addressing actuarial practicalities like portfolio underestimation and temporal consistency.</t>
-        </is>
-      </c>
-      <c r="R173" t="b">
+          <t>Reinforcement learning can improve micro-level reserving by learning from incomplete claim histories and producing stable, accurate reserve revisions over time, especially for immature claims.</t>
+        </is>
+      </c>
+      <c r="Q173" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14392,20 +14156,17 @@
       <c r="N174" t="b">
         <v>0</v>
       </c>
-      <c r="O174" t="b">
-        <v>1</v>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>This paper focuses on the computational complexity of persistence barcodes in topological data analysis, with no connection to claims reserving, actuarial science, or insurance loss modeling.</t>
+        </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>The paper analyzes the expected computational complexity of computing persistence barcodes for random filtrations using matrix reduction, providing bounds on fill-in and runtime for Čech, Vietoris–Rips, and Erdős–Rényi complexes.</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>The study provides tighter-than-worst-case expected complexity bounds for persistence barcode computation in topological data analysis, but has no direct or transferable relevance to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R174" t="b">
+          <t>The paper provides theoretical bounds on matrix reduction complexity for random filtrations in topological data analysis, which has no practical relevance to actuarial reserving.</t>
+        </is>
+      </c>
+      <c r="Q174" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14474,15 +14235,17 @@
       <c r="N175" t="b">
         <v>0</v>
       </c>
-      <c r="O175" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>The paper fits extreme value distributions to non-life insurance premium data in India, which is not directly relevant to claims reserving or loss development modeling.</t>
-        </is>
-      </c>
-      <c r="R175" t="b">
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>The paper fits extreme value distributions to non-life insurance premium data in India, with no focus on claims reserving, development triangles, or reserve uncertainty.</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Generalized Extreme Value distribution best fits Indian non-life premium data, but the analysis lacks relevance to actuarial reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q175" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14551,15 +14314,17 @@
       <c r="N176" t="b">
         <v>0</v>
       </c>
-      <c r="O176" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>The paper computes critical exponents for Lee-Yang and percolation theory using six-loop renormalization group methods, with no connection to actuarial reserving or insurance claims modeling.</t>
-        </is>
-      </c>
-      <c r="R176" t="b">
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>This paper focuses on theoretical physics, specifically critical exponent analysis in Lee-Yang and percolation theory using renormalization group methods, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>The paper advances theoretical physics through six-loop renormalization analysis but offers no practical relevance to claims reserving, loss modeling, or actuarial machine learning.</t>
+        </is>
+      </c>
+      <c r="Q176" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14589,7 +14354,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Existence of a classical solution to the integro-differential equation arising in the Cramér--Lundberg non-life insurance model with proportional investment</t>
+          <t>Existence of a classical solution to the integro-differential equation arising in the Cramér-Lundberg non-life insurance model with proportional investment</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -14628,15 +14393,17 @@
       <c r="N177" t="b">
         <v>0</v>
       </c>
-      <c r="O177" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>The paper proves the existence of a classical solution to an integro-differential equation for survival probability in a Cramér-Lundberg model with proportional investment, under minimal moment conditions on claim sizes.</t>
-        </is>
-      </c>
-      <c r="R177" t="b">
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>The paper proves the existence of a classical solution to an integro-differential equation in a Cramér–Lundberg model with proportional investment, focusing on survival probability under minimal moment conditions.</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>While mathematically rigorous, the paper addresses ruin theory and investment dynamics rather than claims reserving, making it of limited practical relevance to the IFoA working party's focus.</t>
+        </is>
+      </c>
+      <c r="Q177" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14705,20 +14472,17 @@
       <c r="N178" t="b">
         <v>0</v>
       </c>
-      <c r="O178" t="b">
-        <v>1</v>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>This paper focuses on extremum seeking control with adaptive gain for dynamic systems, unrelated to claims reserving or actuarial modeling.</t>
+        </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>The paper introduces an adaptive extremum seeking control algorithm that adjusts step size based on gradient estimation error, ensuring stability and performance across numerical examples.</t>
-        </is>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>This control theory method optimizes systems with uncertain gradients but has no direct or transferable application to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R178" t="b">
+          <t>The method improves controller stability using gradient estimation error but has no practical application to insurance reserving or loss prediction.</t>
+        </is>
+      </c>
+      <c r="Q178" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14787,20 +14551,17 @@
       <c r="N179" t="b">
         <v>0</v>
       </c>
-      <c r="O179" t="b">
-        <v>1</v>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>This paper focuses on fairness and bias mitigation in motor insurance pricing, not claims reserving or loss estimation.</t>
+        </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>This paper focuses on measuring and mitigating ethical biases in motor insurance pricing, emphasizing regulatory compliance, fairness, and transparency in premium setting.</t>
-        </is>
-      </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>The paper addresses bias mitigation in insurance pricing, not claims reserving, making it of limited relevance to the IFoA reserving working party.</t>
-        </is>
-      </c>
-      <c r="R179" t="b">
+          <t>The study provides tools to measure and mitigate ethical biases in pricing but offers no practical value for actuarial reserving research or practice.</t>
+        </is>
+      </c>
+      <c r="Q179" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14869,20 +14630,17 @@
       <c r="N180" t="b">
         <v>0</v>
       </c>
-      <c r="O180" t="b">
-        <v>1</v>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>This paper focuses on robust state estimation for autonomous vehicles under uncertainty, with no direct application to actuarial claims reserving or loss development modeling.</t>
+        </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>The paper introduces a distributionally robust method for state and input estimation in autonomous vehicles, designed to handle model uncertainty and measurement outliers using moment-based ambiguity sets.</t>
-        </is>
-      </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>This work focuses on robust state estimation for autonomous driving systems and has no direct or transferable relevance to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R180" t="b">
+          <t>The method improves resilience in dynamic systems but lacks transferability to insurance reserving contexts.</t>
+        </is>
+      </c>
+      <c r="Q180" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14951,20 +14709,17 @@
       <c r="N181" t="b">
         <v>0</v>
       </c>
-      <c r="O181" t="b">
-        <v>1</v>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>This paper studies ruin probabilities for an insurer with life and non-life branches investing in risky assets, deriving smoothness properties and differential equations for ruin probability under exponential jumps.</t>
+        </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>The paper examines ruin probabilities for an insurer with life and non-life branches investing in risky assets, deriving smoothness properties and differential equations for ruin probability under exponential jump assumptions.</t>
-        </is>
-      </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>Ruin probability decays similarly to one-sided jump models when investments follow geometric Brownian motion and claims are exponentially distributed.</t>
-        </is>
-      </c>
-      <c r="R181" t="b">
+          <t>The paper provides theoretical results on ruin probability decay under investment risk but does not address claims reserving, IBNR/RBNS, or practical actuarial forecasting methods.</t>
+        </is>
+      </c>
+      <c r="Q181" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15033,20 +14788,17 @@
       <c r="N182" t="b">
         <v>0</v>
       </c>
-      <c r="O182" t="b">
-        <v>1</v>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>This paper introduces an asymmetric fitting function for Raman spectroscopy in condensed matter physics, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>The paper introduces an asymmetric pseudo-Voigt function to better fit Raman spectroscopy data with asymmetric peaks, improving parameter estimation over symmetric models across various condensed matter systems.</t>
-        </is>
-      </c>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>This work advances spectral fitting in physics but has no relevance to actuarial claims reserving or machine learning applications in insurance.</t>
-        </is>
-      </c>
-      <c r="R182" t="b">
+          <t>The proposed asymmetric pseudo-Voigt function improves spectral peak fitting in materials science but offers no practical value for claims reserving or actuarial machine learning.</t>
+        </is>
+      </c>
+      <c r="Q182" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15115,20 +14867,17 @@
       <c r="N183" t="b">
         <v>0</v>
       </c>
-      <c r="O183" t="b">
-        <v>1</v>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>The paper models ruin probabilities under bonus-malus systems with delayed by-claims, focusing on premium adjustments and correlation effects rather than reserving methodology or claim development.</t>
+        </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>The paper models ruin probabilities in a discrete-time risk framework with delayed by-claims and time-varying premiums, comparing premium principles based on reported versus settled claims.</t>
-        </is>
-      </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>Premiums based on settled claims lead to higher ruin probabilities than those based on reported claims, especially when by-claim delays are frequent.</t>
-        </is>
-      </c>
-      <c r="R183" t="b">
+          <t>Delayed settlement of by-claims can paradoxically reduce ruin probabilities, but the paper's focus on pricing and risk models limits its direct applicability to claims reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q183" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15197,20 +14946,17 @@
       <c r="N184" t="b">
         <v>0</v>
       </c>
-      <c r="O184" t="b">
-        <v>1</v>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>This paper focuses on background radiation estimation for a gamma-ray satellite mission and has no connection to actuarial claims reserving or insurance loss modeling.</t>
+        </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>This paper focuses on estimating background radiation for a proposed gamma-ray satellite mission (CAMELOT), with no connection to actuarial reserving, claims development, or insurance loss modeling.</t>
-        </is>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>The paper is entirely unrelated to general insurance claims reserving and offers no practical value to the IFoA Working Party.</t>
-        </is>
-      </c>
-      <c r="R184" t="b">
+          <t>The research is entirely unrelated to general insurance reserving, machine learning applications in actuarial science, or any practical reserving methodology.</t>
+        </is>
+      </c>
+      <c r="Q184" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15274,25 +15020,22 @@
         </is>
       </c>
       <c r="M185" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N185" t="b">
         <v>0</v>
       </c>
-      <c r="O185" t="b">
-        <v>1</v>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>The paper presents a model monitoring framework for non-life insurance pricing, focusing on concept drift detection using Gini scores and calibration tests, with limited direct application to claims reserving.</t>
+        </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>The paper presents a model monitoring framework for non-life insurance pricing, using concept drift detection and statistical tests like Gini score decomposition to guide model recalibration decisions.</t>
-        </is>
-      </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>The framework helps detect when pricing models degrade due to data shifts, but it is not directly applicable to claims reserving or reserve uncertainty quantification.</t>
-        </is>
-      </c>
-      <c r="R185" t="b">
+          <t>While methodologically rigorous, the paper's focus on pricing model monitoring offers only indirect relevance to reserving, as it does not address claim development, IBNR/RBNS, or reserve uncertainty quantification.</t>
+        </is>
+      </c>
+      <c r="Q185" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15361,20 +15104,17 @@
       <c r="N186" t="b">
         <v>0</v>
       </c>
-      <c r="O186" t="b">
-        <v>1</v>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>This paper disproves a theoretical conjecture in average-case complexity related to low-degree moments and distinguishing algorithms, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>The paper disproves the low-degree conjecture in average-case complexity by constructing counterexamples where vanishing low-degree advantage does not imply computational hardness, using list-decoding techniques and eigenvalue-based distinguishers.</t>
-        </is>
-      </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>Vanishing low-degree advantage does not reliably indicate computational hardness, challenging a foundational heuristic in average-case complexity theory.</t>
-        </is>
-      </c>
-      <c r="R186" t="b">
+          <t>The paper demonstrates that vanishing low-degree advantage does not imply computational hardness, challenging a foundational heuristic in theoretical computer science but offering no practical value for claims reserving.</t>
+        </is>
+      </c>
+      <c r="Q186" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15443,20 +15183,17 @@
       <c r="N187" t="b">
         <v>0</v>
       </c>
-      <c r="O187" t="b">
-        <v>1</v>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>The paper introduces a conditional Archimedean copula generator estimation method for censored data, applied to claims reserving to better capture dependence structures influenced by covariates.</t>
+        </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>The paper introduces a conditional Archimedean copula generator estimation method for censored data, allowing covariates to influence dependence structure, with applications including claims reserving.</t>
-        </is>
-      </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>Modeling dependence via conditional copula generators with covariates can improve accuracy in actuarial contexts like claims reserving by relaxing rigid dependence assumptions.</t>
-        </is>
-      </c>
-      <c r="R187" t="b">
+          <t>Modeling dependence via conditional copula generators with covariates can improve the accuracy of reserving models by relaxing rigid dependence assumptions.</t>
+        </is>
+      </c>
+      <c r="Q187" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15525,20 +15262,17 @@
       <c r="N188" t="b">
         <v>0</v>
       </c>
-      <c r="O188" t="b">
-        <v>1</v>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>This paper focuses on detecting AI-generated fake images using a novel regularization technique, with no connection to claims reserving, loss modelling, or actuarial applications.</t>
+        </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>The paper introduces SimLBR, a method for detecting AI-generated images by learning to identify real images and treating fakes as outliers, achieving strong generalization and efficiency on challenging benchmarks.</t>
-        </is>
-      </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>Detecting fake images is reframed as learning the boundary of real image distributions, with significant gains in cross-generator robustness and efficiency.</t>
-        </is>
-      </c>
-      <c r="R188" t="b">
+          <t>The method improves fake image detection by learning a tight boundary around real image distributions, but offers no practical value for actuarial reserving research or practice.</t>
+        </is>
+      </c>
+      <c r="Q188" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15607,20 +15341,17 @@
       <c r="N189" t="b">
         <v>0</v>
       </c>
-      <c r="O189" t="b">
-        <v>1</v>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>This paper examines how scientific reputation of universities correlates with Wikipedia attention, using Leiden Ranking indicators and analyzing regional and linguistic variations.</t>
+        </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>The paper examines how scientific performance metrics of universities correlate with their visibility on Wikipedia, finding that research productivity and impact influence public attention, but other non-scientific factors may also play a role.</t>
-        </is>
-      </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>Scientific reputation influences Wikipedia attention for universities, but the relationship is curvilinear and likely mediated by non-academic factors.</t>
-        </is>
-      </c>
-      <c r="R189" t="b">
+          <t>Scientific productivity, impact, and collaboration show curvilinear effects on public attention, suggesting non-reputational factors also drive societal interest in universities.</t>
+        </is>
+      </c>
+      <c r="Q189" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15689,20 +15420,17 @@
       <c r="N190" t="b">
         <v>0</v>
       </c>
-      <c r="O190" t="b">
-        <v>1</v>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>This paper focuses on distributed control systems and communication scheduling in cyber-physical systems, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>The paper proposes a distributed model-predictive control framework that uses predicted communication delays (Age of Information) to improve cyber-physical system stability, demonstrated in vehicle platooning.</t>
-        </is>
-      </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>This work focuses on control theory and network scheduling for cyber-physical systems, with no relevance to actuarial claims reserving or loss modelling.</t>
-        </is>
-      </c>
-      <c r="R190" t="b">
+          <t>The paper advances robust distributed control using age-of-information forecasts but offers no practical value for claims reserving or actuarial applications.</t>
+        </is>
+      </c>
+      <c r="Q190" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15771,20 +15499,17 @@
       <c r="N191" t="b">
         <v>0</v>
       </c>
-      <c r="O191" t="b">
-        <v>1</v>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>The paper introduces a statistical test for comparing matrix distributions using Laplace transforms, with applications demonstrated on insurance data, but does not focus on claims reserving or reserve estimation.</t>
+        </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>The paper introduces a statistical test for comparing matrix distributions using Laplace transforms, validated on financial and non-life insurance data, but does not focus on claims reserving or reserve estimation.</t>
-        </is>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>The paper proposes a novel statistical test for matrix distribution equality with applications in insurance data, but lacks direct relevance to actuarial reserving practice.</t>
-        </is>
-      </c>
-      <c r="R191" t="b">
+          <t>While applicable to insurance data, the method lacks direct relevance to actuarial reserving tasks such as IBNR estimation, claim development modeling, or probabilistic forecasting.</t>
+        </is>
+      </c>
+      <c r="Q191" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15853,20 +15578,17 @@
       <c r="N192" t="b">
         <v>0</v>
       </c>
-      <c r="O192" t="b">
-        <v>1</v>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>This paper presents a stochastic optimization method using subsampling and line-search for nonconvex problems, with theoretical guarantees and empirical results on general machine learning tasks.</t>
+        </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>The paper introduces a stochastic optimization method using subsampled data and line-search techniques to achieve second-order convergence, particularly useful for nonconvex problems like deep learning training.</t>
-        </is>
-      </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>This optimization method enables efficient escape from saddle points in nonconvex machine learning problems using subsampled gradients, but offers no direct application to actuarial reserving.</t>
-        </is>
-      </c>
-      <c r="R192" t="b">
+          <t>The method enables efficient escape from saddle points in nonconvex optimization using subsampled gradients and Newton-type directions, but offers no direct application or validation in claims reserving contexts.</t>
+        </is>
+      </c>
+      <c r="Q192" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15935,20 +15657,17 @@
       <c r="N193" t="b">
         <v>0</v>
       </c>
-      <c r="O193" t="b">
-        <v>1</v>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>The paper introduces SkewD, a causal discovery method for location-scale noise models that handles skewed noise distributions, improving reliability over normal-distribution-based approaches in bivariate settings.</t>
+        </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>The paper introduces SkewD, a causal discovery method for location-scale noise models that handles skewed noise distributions, improving reliability over normal-distribution-based methods in bivariate settings.</t>
-        </is>
-      </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>SkewD enables robust causal inference in bivariate models with skewed noise, but offers no direct application to claims reserving or actuarial loss modeling.</t>
-        </is>
-      </c>
-      <c r="R193" t="b">
+          <t>SkewD enables more robust causal inference in bivariate models under skewed noise, but offers minimal direct or transferable value to actuarial claims reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q193" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16017,20 +15736,17 @@
       <c r="N194" t="b">
         <v>0</v>
       </c>
-      <c r="O194" t="b">
-        <v>1</v>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>The paper introduces a distributionally robust stratified sampling method for stochastic simulations under uncertain input models, using bi-level optimization and Bayesian methods to minimize worst-case variance.</t>
+        </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>The paper introduces a distributionally robust stratified sampling method for stochastic simulations under multiple uncertain input models, using bi-level optimization and Bayesian methods to minimize worst-case variance, validated via wind turbine case studies.</t>
-        </is>
-      </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>This method improves simulation robustness under input model uncertainty but lacks direct application or transferability to claims reserving or loss reserve estimation.</t>
-        </is>
-      </c>
-      <c r="R194" t="b">
+          <t>This approach improves simulation robustness under input model uncertainty but lacks direct application or validation in claims reserving contexts.</t>
+        </is>
+      </c>
+      <c r="Q194" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16099,20 +15815,17 @@
       <c r="N195" t="b">
         <v>1</v>
       </c>
-      <c r="O195" t="b">
-        <v>1</v>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>The paper introduces a CTGAN-based workflow to generate synthetic insurance datasets, evaluated for ML efficacy and statistical fidelity, with an R interface to encourage adoption by actuaries.</t>
+        </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>The paper introduces a CTGAN-based workflow to synthesize realistic insurance datasets for general and life insurance, evaluated on ML efficacy, variable distributions, and model stability, with an R interface to encourage adoption.</t>
-        </is>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>Synthetic insurance datasets generated via CTGAN can support actuarial research by enabling reproducible experiments where real data is unavailable or restricted.</t>
-        </is>
-      </c>
-      <c r="R195" t="b">
+          <t>Synthetic insurance datasets generated via CTGAN can support actuarial research and model development when real data is unavailable, provided they preserve key statistical properties and model stability.</t>
+        </is>
+      </c>
+      <c r="Q195" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16181,20 +15894,17 @@
       <c r="N196" t="b">
         <v>0</v>
       </c>
-      <c r="O196" t="b">
-        <v>1</v>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>The paper develops a theoretical framework for regular variation of random-length sequences and applies it to risk measures, including a brief mention of non-life insurance applications.</t>
+        </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>The paper develops a regular variation framework for random-length sequences of random variables, with applications to risk measures like ruin probability and tail index, including an illustration in non-life insurance.</t>
-        </is>
-      </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>The paper provides asymptotic risk indicators for random-length sequences applicable to non-life insurance but lacks direct connection to claims reserving methodology or practical actuarial implementation.</t>
-        </is>
-      </c>
-      <c r="R196" t="b">
+          <t>While the paper touches on non-life insurance, its focus is on abstract asymptotic theory with limited direct applicability to practical claims reserving or model development.</t>
+        </is>
+      </c>
+      <c r="Q196" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16263,20 +15973,17 @@
       <c r="N197" t="b">
         <v>0</v>
       </c>
-      <c r="O197" t="b">
-        <v>1</v>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>This paper focuses on safety function response times in industrial automation using private 5G and IO-Link Wireless, with no connection to actuarial claims reserving or loss modelling.</t>
+        </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>The paper evaluates safety function response times in a private 5G and IO-Link Wireless testbed for industrial automation, focusing on latency and deterministic communication for human-robot interaction.</t>
-        </is>
-      </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>This research is unrelated to actuarial claims reserving and offers no practical value for the IFoA General Insurance Machine Learning in Reserving Working Party.</t>
-        </is>
-      </c>
-      <c r="R197" t="b">
+          <t>The research is entirely unrelated to general insurance reserving, offering no practical value or transferable methodology for the IFoA Working Party.</t>
+        </is>
+      </c>
+      <c r="Q197" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16345,20 +16052,17 @@
       <c r="N198" t="b">
         <v>0</v>
       </c>
-      <c r="O198" t="b">
-        <v>1</v>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>This paper introduces a method for generating synthetic claims to train fact verification models, reducing reliance on manually annotated data, but it is unrelated to insurance claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>The paper introduces QACG, a framework for generating synthetic claims to train fact verification models with minimal human annotation, achieving strong zero-shot performance on the FEVER dataset.</t>
-        </is>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>Automatically generated claims can significantly reduce reliance on manually annotated data for training fact verification models, but the approach has no direct relevance to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R198" t="b">
+          <t>The QACG framework enables zero-shot fact verification using automatically generated claims from Wikipedia, with no application to reserving, loss estimation, or actuarial modeling.</t>
+        </is>
+      </c>
+      <c r="Q198" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16427,20 +16131,17 @@
       <c r="N199" t="b">
         <v>0</v>
       </c>
-      <c r="O199" t="b">
-        <v>1</v>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>This paper focuses on computing properties of Maass cusp forms in number theory and has no connection to actuarial reserving, claims development, or machine learning applications in insurance.</t>
+        </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>The paper focuses on computing properties of Maass cusp forms using Fourier coefficients and analytic number theory techniques, with no connection to actuarial reserving or insurance claims modeling.</t>
-        </is>
-      </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>This paper advances pure number theory by reconstructing Maass cusp forms from Fourier coefficients, but offers no relevance to claims reserving or actuarial practice.</t>
-        </is>
-      </c>
-      <c r="R199" t="b">
+          <t>The paper advances pure mathematical theory in automorphic forms but offers no practical value for claims reserving or actuarial modeling.</t>
+        </is>
+      </c>
+      <c r="Q199" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16509,20 +16210,17 @@
       <c r="N200" t="b">
         <v>0</v>
       </c>
-      <c r="O200" t="b">
-        <v>1</v>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>This paper evaluates a method for estimating cancer incidence from mortality data using Bayesian generalized linear mixed models, with no connection to insurance claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>The paper evaluates the IMR method for estimating cancer incidence from mortality data using Bayesian GLMMs and smoothing splines, finding &lt;10% error for most cancers under a constant IMR assumption.</t>
-        </is>
-      </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>The IMR method with a constant trend assumption yields reasonably accurate cancer incidence estimates but has no direct relevance to actuarial claims reserving.</t>
-        </is>
-      </c>
-      <c r="R200" t="b">
+          <t>The IMR method with constant trend assumptions performed best for several cancer sites, but the study has no practical relevance to general insurance reserving or loss prediction.</t>
+        </is>
+      </c>
+      <c r="Q200" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16591,20 +16289,17 @@
       <c r="N201" t="b">
         <v>0</v>
       </c>
-      <c r="O201" t="b">
-        <v>1</v>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>The paper applies Multilevel Monte Carlo methods to estimate failure probabilities in composite materials under manufacturing defects, achieving massive computational speedups but with no connection to insurance claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>The paper introduces a Multilevel Monte Carlo method to efficiently estimate failure probabilities in composite structures with manufacturing defects, achieving &gt;1000x speedup over classical Monte Carlo for rare-event simulations.</t>
-        </is>
-      </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>MLMC drastically reduces computational cost for rare-event structural failure simulations but has no direct application to actuarial claims reserving or loss modelling.</t>
-        </is>
-      </c>
-      <c r="R201" t="b">
+          <t>While computationally impressive, the paper's focus on structural engineering failure analysis offers negligible practical value for actuarial reserving research or practice.</t>
+        </is>
+      </c>
+      <c r="Q201" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16673,20 +16368,17 @@
       <c r="N202" t="b">
         <v>1</v>
       </c>
-      <c r="O202" t="b">
-        <v>1</v>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>This paper extends Mack's chain-ladder model using a continuous-time stochastic differential equation and proposes a bootstrap method that naturally captures asymmetry and non-negativity in reserve distributions.</t>
+        </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>The paper extends Mack’s chain-ladder model using a continuous-time stochastic differential equation and proposes a bootstrap method that naturally captures asymmetry and non-negativity in reserve distributions, validated via case study.</t>
-        </is>
-      </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>A continuous-time SDE framework for chain-ladder reserving enables more realistic reserve distribution estimation without ad hoc assumptions, improving uncertainty quantification.</t>
-        </is>
-      </c>
-      <c r="R202" t="b">
+          <t>The continuous-time framework improves reserve uncertainty estimation by inherently modeling claim development dynamics without requiring ad hoc assumptions.</t>
+        </is>
+      </c>
+      <c r="Q202" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16755,20 +16447,17 @@
       <c r="N203" t="b">
         <v>0</v>
       </c>
-      <c r="O203" t="b">
-        <v>1</v>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>The paper provides a theoretical framework for nonparametric inference on monotone functions, with applications to density and hazard estimation under censoring, but lacks direct connection to claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>The paper develops a general framework for nonparametric inference on monotone functions using Grenander-type estimators, with applications to monotone density and hazard estimation under censoring and covariate-marginalized regression.</t>
-        </is>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>This theoretical work extends classical nonparametric methods for monotone functions but lacks direct application or validation in claims reserving contexts.</t>
-        </is>
-      </c>
-      <c r="R203" t="b">
+          <t>While theoretically rigorous, the paper's focus on general monotone function estimation offers limited practical value for actuarial reserving without explicit application to RBNS/IBNR, claim development, or reserve uncertainty.</t>
+        </is>
+      </c>
+      <c r="Q203" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16837,20 +16526,17 @@
       <c r="N204" t="b">
         <v>0</v>
       </c>
-      <c r="O204" t="b">
-        <v>1</v>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>This paper proposes a chaotic variational autoencoder for one-class classification in insurance fraud detection, showing improved performance over standard VAEs on health and auto datasets.</t>
+        </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>The paper proposes a chaotic variational autoencoder for one-class classification to detect insurance fraud in health and auto datasets, outperforming standard VAEs with statistically significant gains.</t>
-        </is>
-      </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>This fraud detection method, while technically innovative, has no direct or transferable application to claims reserving, RBNS/IBNR estimation, or loss development modeling.</t>
-        </is>
-      </c>
-      <c r="R204" t="b">
+          <t>While technically innovative, the paper focuses on fraud detection rather than claims reserving, making it of limited practical relevance to the IFoA Working Party's core objectives.</t>
+        </is>
+      </c>
+      <c r="Q204" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16919,20 +16605,17 @@
       <c r="N205" t="b">
         <v>0</v>
       </c>
-      <c r="O205" t="b">
-        <v>1</v>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>This paper focuses on asymptotically optimal private estimation under differential privacy constraints for discrete distributions, with no connection to claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>The paper focuses on asymptotically optimal private estimation of discrete distributions under differential privacy constraints, with theoretical guarantees under mean square loss, but does not address claims reserving or actuarial applications.</t>
-        </is>
-      </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>This paper provides asymptotic optimality guarantees for private distribution estimation under differential privacy, which has no direct relevance to actuarial reserving practice.</t>
-        </is>
-      </c>
-      <c r="R205" t="b">
+          <t>The paper provides theoretical guarantees for private distribution estimation under mean square loss but offers no practical value for actuarial reserving or insurance applications.</t>
+        </is>
+      </c>
+      <c r="Q205" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17001,20 +16684,17 @@
       <c r="N206" t="b">
         <v>0</v>
       </c>
-      <c r="O206" t="b">
-        <v>1</v>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>The paper focuses on optimizing insurance pricing for profit and fairness using gradient-based methods, not on claims reserving or loss estimation.</t>
+        </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>The paper introduces OptiGrad, a gradient-based method for optimizing insurance pricing with fairness constraints, targeting profit margins and conversion rates in non-life insurance, but does not address claims reserving or loss forecasting.</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>This work focuses on pricing optimization and fairness enforcement in insurance, which is not directly relevant to claims reserving or actuarial reserve estimation.</t>
-        </is>
-      </c>
-      <c r="R206" t="b">
+          <t>This work advances pricing optimization with fairness constraints but offers no direct value to actuarial reserving research or practice.</t>
+        </is>
+      </c>
+      <c r="Q206" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17083,20 +16763,17 @@
       <c r="N207" t="b">
         <v>0</v>
       </c>
-      <c r="O207" t="b">
-        <v>1</v>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>The paper introduces a decision tree and co-attention model for explainable claim verification in social media rumor detection, not insurance claims reserving.</t>
+        </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>The paper introduces DTCA, a decision tree and co-attention model for explainable claim verification in social media contexts, using datasets like RumourEval and PHEME to detect false claims with improved F1-scores.</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>The method improves claim verification accuracy and explainability but targets social media rumor detection, not insurance claims reserving or loss development.</t>
-        </is>
-      </c>
-      <c r="R207" t="b">
+          <t>While innovative for explainable AI in rumor detection, the method has minimal direct or transferable value to actuarial reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q207" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17165,20 +16842,17 @@
       <c r="N208" t="b">
         <v>0</v>
       </c>
-      <c r="O208" t="b">
-        <v>1</v>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>The paper fits a discrete generalised Pareto distribution to non-life insurance claims data and shows it outperforms the negative binomial distribution using information criteria, but does not address reserving, claim development, or uncertainty quantification.</t>
+        </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>The paper fits a discrete generalised Pareto distribution to non-life insurance claims data from Ghana, comparing it with the negative binomial distribution using information criteria and finding superior fit.</t>
-        </is>
-      </c>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>The discrete generalised Pareto distribution outperforms the negative binomial in fitting non-life claims frequency data, suggesting potential for improved claim count modelling in reserving contexts.</t>
-        </is>
-      </c>
-      <c r="R208" t="b">
+          <t>While the discrete generalised Pareto distribution fits claims frequency better than negative binomial in this study, its relevance to actuarial reserving practice is limited due to lack of connection to reserve estimation, run-off triangles, or predictive uncertainty.</t>
+        </is>
+      </c>
+      <c r="Q208" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17242,25 +16916,22 @@
         </is>
       </c>
       <c r="M209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
       </c>
-      <c r="O209" t="b">
-        <v>1</v>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>The paper focuses on improving differential privacy for releasing statistics from heterogeneous datasets, with no direct connection to claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>The paper proposes an iterative algorithm to reduce privacy loss in differential privacy when releasing statistics from disjoint dataset subsets, under known user contribution counts, while maintaining fixed estimation error bounds.</t>
-        </is>
-      </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>The paper improves composition privacy loss for differentially private mean and variance estimation without increasing worst-case error, but offers no direct relevance to actuarial reserving or claims modelling.</t>
-        </is>
-      </c>
-      <c r="R209" t="b">
+          <t>The work advances privacy-preserving statistical release under user contribution heterogeneity but offers no practical value for actuarial reserving or loss forecasting.</t>
+        </is>
+      </c>
+      <c r="Q209" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17329,20 +17000,17 @@
       <c r="N210" t="b">
         <v>0</v>
       </c>
-      <c r="O210" t="b">
-        <v>1</v>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>The paper compares offset and ratio weighting in Tweedie models for premium estimation under variable exposure, with implications for mid-term cancellations in auto insurance.</t>
+        </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>The paper compares offset and ratio weighted regressions in Tweedie models for insurance exposure modeling, showing the offset approach is asymptotically more efficient but the ratio approach performs better financially under mid-term cancellations.</t>
-        </is>
-      </c>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t>For portfolios with mid-term cancellations, the ratio approach outperforms the offset approach in portfolio-level financial balance despite lower asymptotic efficiency.</t>
-        </is>
-      </c>
-      <c r="R210" t="b">
+          <t>While the offset approach is asymptotically more efficient, the ratio approach better maintains portfolio-level financial balance under heterogeneous or truncated exposures from policy cancellations.</t>
+        </is>
+      </c>
+      <c r="Q210" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17411,20 +17079,17 @@
       <c r="N211" t="b">
         <v>0</v>
       </c>
-      <c r="O211" t="b">
-        <v>1</v>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>The paper introduces deviance Voronoi residuals for spatio-temporal point process models applied to earthquake insurance risk, with a focus on capital adequacy and simulation-based loss estimation.</t>
+        </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>The paper introduces deviance Voronoi residuals for evaluating spatio-temporal point process models in earthquake insurance risk, proposes a new capital test formula based on provincial correlations, and includes an interactive web app for simulating losses.</t>
-        </is>
-      </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>The paper advances spatial residual diagnostics for catastrophe risk modeling but lacks direct applicability to general claims reserving or micro-level loss prediction.</t>
-        </is>
-      </c>
-      <c r="R211" t="b">
+          <t>While methodologically interesting for spatial risk modeling, the paper's focus on catastrophe capital requirements and hazard maps limits its direct applicability to general claims reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q211" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17493,20 +17158,17 @@
       <c r="N212" t="b">
         <v>0</v>
       </c>
-      <c r="O212" t="b">
-        <v>1</v>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>The paper extends cluster-weighted models to matrix-normal data, with an application to the Italian non-life insurance market, offering a structured approach to clustering multivariate time-series or spatially indexed insurance data.</t>
+        </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>The paper extends cluster-weighted models to matrix-normal data, enabling joint modeling of responses and covariates over time or space, with applications including Italian non-life insurance data.</t>
-        </is>
-      </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>Matrix normal cluster-weighted models offer a flexible framework for clustering regression data with structured covariates, potentially useful for modeling claim development patterns across time or segments in reserving contexts.</t>
-        </is>
-      </c>
-      <c r="R212" t="b">
+          <t>Matrix normal cluster-weighted models can capture complex dependencies in multi-dimensional insurance data, potentially aiding reserving by grouping similar claim development patterns while accounting for covariate structure.</t>
+        </is>
+      </c>
+      <c r="Q212" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17575,20 +17237,17 @@
       <c r="N213" t="b">
         <v>0</v>
       </c>
-      <c r="O213" t="b">
-        <v>1</v>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>The paper extends the MBBEFD distribution class to model lower-truncated and right-censored insurance claims, which are common in general insurance due to deductibles and policy limits.</t>
+        </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>The paper extends the MBBEFD class of distributions to model lower-truncated and right-censored insurance claims, addressing deductibles and policy limits, and explores how these contractual features affect distributional assumptions.</t>
-        </is>
-      </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>Extending the MBBEFD distribution family enables better modeling of truncated and censored claims, which is relevant for reserving under real-world policy constraints.</t>
-        </is>
-      </c>
-      <c r="R213" t="b">
+          <t>The extended MBBEFD family can flexibly model both unimodal skewed and monotonically decreasing claim distributions, making it potentially useful for reserving under real-world policy constraints.</t>
+        </is>
+      </c>
+      <c r="Q213" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17657,20 +17316,17 @@
       <c r="N214" t="b">
         <v>0</v>
       </c>
-      <c r="O214" t="b">
-        <v>1</v>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>The paper introduces a Tweedie-based ratemaking model that accounts for mid-term policy cancellations in auto insurance, focusing on premium penalties and exposure weighting rather than claims reserving.</t>
+        </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>The paper introduces a Tweedie-based ratemaking model that accounts for mid-term policy cancellations in auto insurance, using weighting functions and penalty structures to adjust earned premium and improve pricing fairness.</t>
-        </is>
-      </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>This work focuses on experience rating and cancellation penalties in pricing, not claims reserving, making it of limited direct relevance to the IFoA reserving working party.</t>
-        </is>
-      </c>
-      <c r="R214" t="b">
+          <t>This work advances pricing and experience rating under policy cancellation but does not address claims development, reserve estimation, or uncertainty quantification relevant to reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q214" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17739,20 +17395,17 @@
       <c r="N215" t="b">
         <v>0</v>
       </c>
-      <c r="O215" t="b">
-        <v>1</v>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>The paper addresses policy learning from adaptively collected data, focusing on regret bounds and reweighting estimators for decision-making in dynamic environments like healthcare or online systems.</t>
+        </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>The paper addresses policy learning from adaptively collected data, proposing a reweighted AIPW estimator to handle dependent samples and diminishing exploration, with theoretical guarantees and empirical validation on synthetic and benchmark datasets.</t>
-        </is>
-      </c>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>The paper develops a minimax-optimal policy learning algorithm for adaptively collected data, but it has no direct or transferable application to claims reserving or loss estimation.</t>
-        </is>
-      </c>
-      <c r="R215" t="b">
+          <t>Adaptively collected data complicates policy learning due to sample dependence and uneven treatment exposure, but a reweighted AIPW estimator can achieve minimax-optimal regret even with diminishing exploration.</t>
+        </is>
+      </c>
+      <c r="Q215" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17821,20 +17474,17 @@
       <c r="N216" t="b">
         <v>0</v>
       </c>
-      <c r="O216" t="b">
-        <v>1</v>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>The paper addresses robust policy learning under unobserved confounding in observational data, with applications to personalized medical treatment, but does not connect to claims reserving or actuarial practice.</t>
+        </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>The paper addresses learning personalized decision policies from observational data while accounting for unobserved confounding, proposing a robust method to minimize worst-case regret under uncertainty in propensity weights.</t>
-        </is>
-      </c>
-      <c r="Q216" t="inlineStr">
-        <is>
-          <t>The paper introduces a confounding-robust policy improvement framework that ensures safety and reliability when learning from observational data with hidden confounders, but it is not directly applicable to claims reserving.</t>
-        </is>
-      </c>
-      <c r="R216" t="b">
+          <t>The method ensures safe policy improvement under unobserved confounding by minimizing worst-case regret, but lacks relevance to insurance reserving or loss prediction.</t>
+        </is>
+      </c>
+      <c r="Q216" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17903,20 +17553,17 @@
       <c r="N217" t="b">
         <v>0</v>
       </c>
-      <c r="O217" t="b">
-        <v>1</v>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>The paper introduces Bayesian CART models for insurance claims frequency, focusing on pricing rather than reserving, with extensions to zero-inflated Poisson and MCMC-based tree selection.</t>
+        </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>The paper introduces Bayesian CART models for insurance claims frequency, extending to zero-inflated Poisson distributions and using MCMC for posterior tree exploration, with applications to risk grouping in pricing.</t>
-        </is>
-      </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>Bayesian CART models offer interpretable, flexible risk segmentation for claims frequency but are framed for pricing rather than reserving, limiting direct applicability to the working party’s goals.</t>
-        </is>
-      </c>
-      <c r="R217" t="b">
+          <t>While methodologically sound and interpretable, the paper's focus on pricing and risk segmentation limits its direct applicability to claims reserving tasks like IBNR estimation or run-off modelling.</t>
+        </is>
+      </c>
+      <c r="Q217" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17985,20 +17632,17 @@
       <c r="N218" t="b">
         <v>0</v>
       </c>
-      <c r="O218" t="b">
-        <v>1</v>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>This paper focuses on theoretical linear algebra and matroid intersection algorithms with no connection to actuarial reserving, claims development, or insurance loss estimation.</t>
+        </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>The paper presents a novel algorithm for solving the weighted linear matroid intersection problem using noncommutative determinant degree computation, offering an alternative implementation of Frank’s algorithm with potential efficiency gains on sparse matrices.</t>
-        </is>
-      </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>This theoretical computer science paper introduces a new algebraic approach to matroid intersection but has no practical relevance to actuarial claims reserving or machine learning in reserving.</t>
-        </is>
-      </c>
-      <c r="R218" t="b">
+          <t>The paper presents a novel but purely theoretical algorithm for weighted linear matroid intersection that offers no practical value for claims reserving or actuarial modeling.</t>
+        </is>
+      </c>
+      <c r="Q218" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18067,20 +17711,17 @@
       <c r="N219" t="b">
         <v>1</v>
       </c>
-      <c r="O219" t="b">
-        <v>1</v>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>This paper blends Mack's stochastic reserving model with Recurrent Neural Networks to improve reserve estimation accuracy and uncertainty quantification, directly addressing core actuarial reserving needs.</t>
+        </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>The paper introduces Mack-Net, a hybrid model blending Mack’s stochastic reserving method with Recurrent Neural Networks to improve reserve estimation accuracy and better quantify liability variability, aligning with regulatory and risk management needs.</t>
-        </is>
-      </c>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>Blending Mack’s model with RNNs enhances both point estimates and uncertainty quantification in general insurance reserving, offering practical value for actuarial practice.</t>
-        </is>
-      </c>
-      <c r="R219" t="b">
+          <t>Combining traditional actuarial models like Mack's with RNNs enhances both point estimates and risk measures for general insurance liabilities.</t>
+        </is>
+      </c>
+      <c r="Q219" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18149,20 +17790,17 @@
       <c r="N220" t="b">
         <v>0</v>
       </c>
-      <c r="O220" t="b">
-        <v>1</v>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>The paper proposes a nonparametric method for estimating multivariate distribution functions from truncated and censored data, tested in actuarial valuations of employee benefits under IAS 19, with potential applicability to general insurance reserving contexts.</t>
+        </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>The paper proposes a nonparametric method to estimate multivariate distribution functions for truncated and censored lifetime data, validated via simulations and real-world actuarial use in corporate liability valuation under IAS 19.</t>
-        </is>
-      </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>The method offers a practical nonparametric tool for modeling complex, censored insurance liabilities but lacks direct application to claims reserving or probabilistic reserve forecasting.</t>
-        </is>
-      </c>
-      <c r="R220" t="b">
+          <t>While the method is statistically sound and validated in actuarial practice, its direct relevance to claims reserving is limited without explicit application to RBNS/IBNR, claim development triangles, or micro-level reserving.</t>
+        </is>
+      </c>
+      <c r="Q220" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18231,20 +17869,17 @@
       <c r="N221" t="b">
         <v>0</v>
       </c>
-      <c r="O221" t="b">
-        <v>1</v>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>The paper develops a semiparametric estimator for regression with right-censored covariates, motivated by Huntington's disease research, and demonstrates robustness and efficiency under model misspecification.</t>
+        </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>The paper proposes a semiparametric estimator for modeling outcomes with right-censored covariates, demonstrated in Huntington’s disease research, offering robustness and efficiency under model misspecification.</t>
-        </is>
-      </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>The proposed estimator is doubly robust and semiparametric efficient, making it reliable even when nuisance distribution models are misspecified, though its direct applicability to claims reserving is limited.</t>
-        </is>
-      </c>
-      <c r="R221" t="b">
+          <t>The proposed estimator is doubly robust and semiparametrically efficient, making it statistically reliable even when nuisance models are misspecified, though its direct applicability to claims reserving is limited.</t>
+        </is>
+      </c>
+      <c r="Q221" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18313,20 +17948,17 @@
       <c r="N222" t="b">
         <v>1</v>
       </c>
-      <c r="O222" t="b">
-        <v>1</v>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>SynthETIC is an open-source, feature-rich simulator for generating synthetic individual insurance claims data with customizable complexity, designed to support machine learning research in reserving where real data is scarce.</t>
+        </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>The paper introduces SynthETIC, an open-source simulator for generating individual insurance claims with controllable features like settlement rates, inflation, and dependencies, enabling realistic testing of machine learning reserving models.</t>
-        </is>
-      </c>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>SynthETIC fills a critical gap by providing actuarial researchers with customizable, realistic synthetic claim data to develop and validate ML reserving methods where real data is scarce.</t>
-        </is>
-      </c>
-      <c r="R222" t="b">
+          <t>The simulator enables realistic, controlled experimentation for reserving models by allowing actuarial researchers to generate synthetic claim datasets with configurable development patterns, inflation, and dependencies—filling a critical gap in the non-life actuarial toolkit.</t>
+        </is>
+      </c>
+      <c r="Q222" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18395,20 +18027,17 @@
       <c r="N223" t="b">
         <v>0</v>
       </c>
-      <c r="O223" t="b">
-        <v>1</v>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>The paper models insurer-policyholder and insurer-insurer strategic interactions using game theory and Lotka-Volterra dynamics, focusing on premium setting rather than claims reserving or loss development.</t>
+        </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>The paper models insurer-policyholder and insurer-insurer interactions using game theory and Lotka-Volterra dynamics to study premium-setting behavior and market equilibrium, with findings that high claim exposure leads to higher premiums and inverse relationships between premiums and claims.</t>
-        </is>
-      </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>Insurers with higher claim exposure set higher premiums, leading to strategic market behaviors and equilibrium outcomes shaped by self-interest and utility trade-offs.</t>
-        </is>
-      </c>
-      <c r="R223" t="b">
+          <t>Insurers with higher claim exposure set higher premiums, but the model does not address reserve estimation, claim development, or uncertainty quantification relevant to actuarial reserving.</t>
+        </is>
+      </c>
+      <c r="Q223" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18477,20 +18106,17 @@
       <c r="N224" t="b">
         <v>0</v>
       </c>
-      <c r="O224" t="b">
-        <v>1</v>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>The paper introduces a neural network-based frequency-severity model for predicting total claim costs, with applications in pricing and pure premium estimation, validated on French auto data.</t>
+        </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>The paper introduces a neural network-based frequency-severity model for predicting total claim costs, capturing nonlinear relationships and dependency between frequency and severity, with validation on French auto data showing improved fit over existing methods.</t>
-        </is>
-      </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>A neural frequency-severity model improves prediction of total claim cost by modeling nonlinear covariate effects and frequency-severity dependence, though its primary focus is pricing rather than reserving.</t>
-        </is>
-      </c>
-      <c r="R224" t="b">
+          <t>While the model offers flexible, nonlinear modeling of frequency and severity with analytic moments, its primary focus on pricing rather than reserving limits its direct applicability to claims reserve estimation.</t>
+        </is>
+      </c>
+      <c r="Q224" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18559,20 +18185,17 @@
       <c r="N225" t="b">
         <v>0</v>
       </c>
-      <c r="O225" t="b">
-        <v>1</v>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>The paper extends regression discontinuity designs to non-Euclidean data like functional or compositional outcomes, using geodesic spaces and Fréchet means, with applications in environmental and political science.</t>
+        </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>The paper extends regression discontinuity designs to non-Euclidean outcomes like functional data and networks, using geodesic spaces and Fréchet means for causal inference, with applications in environmental and political data.</t>
-        </is>
-      </c>
-      <c r="Q225" t="inlineStr">
-        <is>
-          <t>This work generalizes causal inference methods to complex, non-Euclidean data types but has no direct or transferable application to claims reserving or actuarial loss modelling.</t>
-        </is>
-      </c>
-      <c r="R225" t="b">
+          <t>While methodologically innovative, the paper has minimal direct or transferable relevance to actuarial claims reserving, as it focuses on causal inference in non-insurance domains without addressing reserve estimation, claim development, or uncertainty quantification.</t>
+        </is>
+      </c>
+      <c r="Q225" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18641,20 +18264,17 @@
       <c r="N226" t="b">
         <v>0</v>
       </c>
-      <c r="O226" t="b">
-        <v>1</v>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>The paper adapts smooth backfitting to additive hazard models for survival analysis, with applications including actuarial reserving under censoring and truncation.</t>
+        </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>The paper adapts smooth backfitting to additive hazard models in survival analysis, accommodating censoring and truncation common in actuarial reserving, with asymptotic theory and practical implementation.</t>
-        </is>
-      </c>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>This method provides a nonparametric, projection-based estimator for additive hazard rates that remains well-defined even if the true hazard is not additive, offering potential utility in claim development modeling under censoring.</t>
-        </is>
-      </c>
-      <c r="R226" t="b">
+          <t>This method provides a nonparametric, projection-based estimator for additive hazard rates that remains well-defined even when the true hazard is not additive, offering potential for modeling claim development under complex exposure patterns.</t>
+        </is>
+      </c>
+      <c r="Q226" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18723,20 +18343,17 @@
       <c r="N227" t="b">
         <v>1</v>
       </c>
-      <c r="O227" t="b">
-        <v>1</v>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>The paper presents a stochastic, multi-line reserving model using double GLMs and hierarchical copulas to simulate loss triangles and quantify portfolio-level risk under IFRS 17, with empirical validation on car insurance data.</t>
+        </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>The paper presents a stochastic model for multi-line P&amp;C insurers to measure incurred claims risk and capital requirements, using a double GLM with hierarchical copulas to capture loss ratio dynamics and diversification benefits under IFRS 17.</t>
-        </is>
-      </c>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>The model enables joint simulation of loss triangles and quantifies portfolio-level risk and diversification benefits, offering practical value for reserving and capital allocation under modern accounting standards.</t>
-        </is>
-      </c>
-      <c r="R227" t="b">
+          <t>By integrating mean-dispersion modeling and cross-line dependence via copulas, the model enables realistic reserve uncertainty quantification and capital allocation that aligns with regulatory standards.</t>
+        </is>
+      </c>
+      <c r="Q227" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18805,20 +18422,17 @@
       <c r="N228" t="b">
         <v>0</v>
       </c>
-      <c r="O228" t="b">
-        <v>1</v>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>The paper addresses causal inference in factorial experiments, focusing on identifying single-treatment effects from multi-intervention RCTs, which is unrelated to claims reserving or actuarial modeling.</t>
+        </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>The paper examines the challenges of extrapolating single-treatment effects from factorial experiments, showing that such effects are not identifiable without strong assumptions, and proposes nonparametric bounds to assess empirical justification for effect sign inferences.</t>
-        </is>
-      </c>
-      <c r="Q228" t="inlineStr">
-        <is>
-          <t>Single-treatment causal effects cannot be reliably inferred from factorial experiments without assuming linearity or specifying causal structures via DAGs, limiting their direct applicability to actuarial reserving contexts.</t>
-        </is>
-      </c>
-      <c r="R228" t="b">
+          <t>Single-treatment effects cannot be identified from factorial experiments without strong assumptions, and nonparametric bounds are needed to justify extrapolations.</t>
+        </is>
+      </c>
+      <c r="Q228" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18882,25 +18496,22 @@
         </is>
       </c>
       <c r="M229" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N229" t="b">
-        <v>0</v>
-      </c>
-      <c r="O229" t="b">
         <v>1</v>
       </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>GEMAct is a Python package for non-life (re)insurance modeling that supports loss reserving and risk aggregation using advanced probability distributions and copulas, with practical implementations like the AEP algorithm.</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>GEMAct is a Python package for non-life (re)insurance modeling that extends scipy with actuarial-specific distributions and copulas, and implements the AEP algorithm for loss aggregation and reserving under dependency structures.</t>
-        </is>
-      </c>
-      <c r="Q229" t="inlineStr">
-        <is>
-          <t>The package provides practical tools for actuarial reserving and risk modeling through enhanced probability distributions and dependency modeling, though it lacks direct focus on machine learning or modern predictive reserving techniques.</t>
-        </is>
-      </c>
-      <c r="R229" t="b">
+          <t>The package enables actuarial practitioners to model dependent loss aggregates and reserving uncertainty using flexible, theoretically grounded tools that are directly applicable to real-world reserving problems.</t>
+        </is>
+      </c>
+      <c r="Q229" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18969,20 +18580,17 @@
       <c r="N230" t="b">
         <v>1</v>
       </c>
-      <c r="O230" t="b">
-        <v>1</v>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>The mCube model introduces a multinomial micro-level reserving framework that jointly models claim timing and payment processes for IBNR/RBNS claims, demonstrating strong empirical performance on real bodily injury data.</t>
+        </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>The paper introduces mCube, a multinomial micro-level reserving model that jointly models claim timing and payment processes for IBNR and RBNS claims, demonstrating strong performance on real bodily injury claims data with well-calibrated reserve estimates.</t>
-        </is>
-      </c>
-      <c r="Q230" t="inlineStr">
-        <is>
-          <t>mCube provides a unified, probabilistic micro-level reserving framework that accurately models both claim development timing and payment amounts, producing well-centered reserve distributions for real-world bodily injury claims.</t>
-        </is>
-      </c>
-      <c r="R230" t="b">
+          <t>mCube provides a unified, probabilistic micro-level reserving approach that accurately centers reserve estimates around true values by combining multinomial time modeling with spliced payment distributions.</t>
+        </is>
+      </c>
+      <c r="Q230" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19051,20 +18659,17 @@
       <c r="N231" t="b">
         <v>0</v>
       </c>
-      <c r="O231" t="b">
-        <v>1</v>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>The paper examines ruin probabilities in a modified Cramér-Lundberg model with time-changed claim arrivals, focusing on theoretical asymptotics rather than practical reserving methods.</t>
+        </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>The paper examines ruin probabilities in a modified Cramér-Lundberg model where claims are time-changed by a Lévy subordinator to model clustered catastrophic events, showing that such transformations increase ruin risk despite unchanged expected claim amounts.</t>
-        </is>
-      </c>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>Introducing claim clustering via time-change in the Cramér-Lundberg model increases ruin probability even when total expected claims remain constant, due to altered claim timing and severity dynamics.</t>
-        </is>
-      </c>
-      <c r="R231" t="b">
+          <t>Introducing claim clustering via subordination increases ruin probability despite unchanged expected claims, but offers no direct utility for actuarial reserving practice.</t>
+        </is>
+      </c>
+      <c r="Q231" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19133,20 +18738,17 @@
       <c r="N232" t="b">
         <v>0</v>
       </c>
-      <c r="O232" t="b">
-        <v>1</v>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>This paper addresses asset-liability management (ALM) for insurers with multiple underwriting lines using stochastic control and Lagrangian duality, but does not focus on claims reserving methodologies or reserve estimation.</t>
+        </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>The paper addresses asset-liability management (ALM) for insurers with multiple underwriting lines using Lagrangian duality, focusing on optimal investment and underwriting strategies under risk constraints and utility maximization.</t>
-        </is>
-      </c>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>This work optimizes insurer ALM under multivariate insurance risk but does not address claims reserving, reserve estimation, or predictive modelling of claim development, making it of limited practical use to the reserving working party.</t>
-        </is>
-      </c>
-      <c r="R232" t="b">
+          <t>The paper provides optimal investment-underwriting strategies under risk constraints but offers minimal direct value to actuarial reserving research or practice.</t>
+        </is>
+      </c>
+      <c r="Q232" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19215,20 +18817,17 @@
       <c r="N233" t="b">
         <v>0</v>
       </c>
-      <c r="O233" t="b">
-        <v>1</v>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>The paper focuses on runtime monitoring of neural network activation patterns for safety-critical systems like autonomous driving, with no direct application to actuarial claims reserving or loss modelling.</t>
+        </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>The paper introduces a method to monitor neural network activation patterns at runtime with provable robustness against input perturbations, using symbolic reasoning to reduce false positives in safety-critical applications like autonomous driving.</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>This work enhances runtime monitoring of DNNs for safety-critical systems by integrating formal symbolic reasoning to ensure robustness against input perturbations, but it lacks direct relevance to actuarial reserving or insurance claim modelling.</t>
-        </is>
-      </c>
-      <c r="R233" t="b">
+          <t>This work enhances robustness in DNN monitoring for autonomous systems but offers no practical value or transferability to general insurance reserving tasks.</t>
+        </is>
+      </c>
+      <c r="Q233" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19297,20 +18896,17 @@
       <c r="N234" t="b">
         <v>0</v>
       </c>
-      <c r="O234" t="b">
-        <v>1</v>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>This paper investigates Poisson's ratio in finite element models of human heel soft tissues and its impact on volume change estimation under mechanical load, with no connection to actuarial reserving or insurance claims modeling.</t>
+        </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>The study evaluates Poisson’s ratio values in finite element models of human heel fat pad under indentation, finding that no single value fits all loading conditions and that values near 0.4999 better reflect near-incompressibility under high load.</t>
-        </is>
-      </c>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>Poisson’s ratio must be carefully calibrated per loading condition in soft tissue FEA to avoid unrealistic volume deformations, as no single value universally captures near-incompressible behavior.</t>
-        </is>
-      </c>
-      <c r="R234" t="b">
+          <t>Poisson's ratio values significantly affect simulated tissue deformation accuracy, but the study has no relevance to claims reserving, loss modeling, or actuarial machine learning applications.</t>
+        </is>
+      </c>
+      <c r="Q234" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19379,20 +18975,17 @@
       <c r="N235" t="b">
         <v>1</v>
       </c>
-      <c r="O235" t="b">
-        <v>1</v>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>The paper proposes a unified occurrence and development model that addresses right-censored claim data for both pricing and reserving, with particular value in reinsurance contexts where uncertainty is high.</t>
+        </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>The paper proposes a granular occurrence and development model that unifies pricing and reserving by addressing right-censored claim data, improving upon traditional two-step methods that ignore uncertainty in best estimates, particularly beneficial for reinsurance with long delays and heavy-tailed claims.</t>
-        </is>
-      </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>A unified occurrence-and-development model resolves inconsistencies between pricing and reserving by directly modeling censored claim data, preserving uncertainty and offering practical value for portfolios with long settlement delays.</t>
-        </is>
-      </c>
-      <c r="R235" t="b">
+          <t>Bridging pricing and reserving through a granular model that accounts for reporting and settlement delays improves consistency and uncertainty handling, especially in low-frequency, high-severity lines.</t>
+        </is>
+      </c>
+      <c r="Q235" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19461,20 +19054,17 @@
       <c r="N236" t="b">
         <v>1</v>
       </c>
-      <c r="O236" t="b">
-        <v>1</v>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>This paper introduces a systematic, distribution-aware ensemble framework for loss reserving that leverages multiple stochastic models and is tailored to reserving data structures, outperforming traditional methods on both central estimates and key quantiles.</t>
+        </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>The paper introduces a systematic framework for ensembling stochastic loss reserving models, focusing on full distributional properties and tailoring to reserving-specific data features like accident and development periods. It demonstrates superior performance over traditional methods using a synthetic dataset and provides an R package for implementation.</t>
-        </is>
-      </c>
-      <c r="Q236" t="inlineStr">
-        <is>
-          <t>Ensembling stochastic reserving models by optimizing their full predictive distributions—rather than just point estimates—yields better reserve estimates and quantiles, especially under sparse or heterogeneous claim data.</t>
-        </is>
-      </c>
-      <c r="R236" t="b">
+          <t>Ensembling stochastic reserving models while preserving full predictive distributions and accounting for reserving-specific data features leads to more robust and regulator-relevant reserve estimates.</t>
+        </is>
+      </c>
+      <c r="Q236" t="b">
         <v>0</v>
       </c>
     </row>
@@ -19543,20 +19133,17 @@
       <c r="N237" t="b">
         <v>1</v>
       </c>
-      <c r="O237" t="b">
-        <v>1</v>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>The paper introduces a nonparametric, structured extension of Accelerated Failure Time models using Kolmogorov-Arnold networks to capture nonlinear covariate effects in survival analysis, with applications in clinical settings.</t>
+        </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>The paper introduces KAN-AFT, a nonparametric extension of accelerated failure time models using Kolmogorov–Arnold representations to capture nonlinear covariate effects in survival analysis, with applications in clinical settings and support for censored data.</t>
-        </is>
-      </c>
-      <c r="Q237" t="inlineStr">
-        <is>
-          <t>KAN-AFT enables flexible, interpretable modeling of nonlinear survival time relationships under censoring, offering potential transferability to actuarial claim development and reserving where time-to-event and covariate interactions matter.</t>
-        </is>
-      </c>
-      <c r="R237" t="b">
+          <t>This method offers a flexible, interpretable survival modeling framework that can capture complex nonlinear relationships while preserving the time-scale interpretability of AFT models, making it transferable to claim development and IBNR modeling in reserving.</t>
+        </is>
+      </c>
+      <c r="Q237" t="b">
         <v>0</v>
       </c>
     </row>
